--- a/BaoCao_Final/9.2.TestCaseSprint2.xlsx
+++ b/BaoCao_Final/9.2.TestCaseSprint2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\đồ án chuyên ngành\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="e:\Downloads\Document\BaoCao_Final(1)\BaoCao_Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64344A62-047C-4FC6-BC6B-4F3D0A93E9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AB2B08-F7EA-4FE5-B7CC-22CB70BADA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="803" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="803" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trường hợp kiểm thử" sheetId="12" r:id="rId1"/>
@@ -35,9 +35,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1093,55 +1090,13 @@
     <numFmt numFmtId="164" formatCode="d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF333333"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1162,13 +1117,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -1180,48 +1128,6 @@
       <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1250,40 +1156,58 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="15"/>
+      <sz val="13"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="15"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color rgb="FF333333"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1546,379 +1470,321 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="29" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="29" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1951,7 +1817,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>885265</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>3168430</xdr:rowOff>
+      <xdr:rowOff>2921901</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1995,7 +1861,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>137402</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>3819028</xdr:rowOff>
+      <xdr:rowOff>3572499</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2038,8 +1904,8 @@
     <xdr:to>
       <xdr:col>43</xdr:col>
       <xdr:colOff>20240</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>4372</xdr:rowOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>176196</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2083,7 +1949,7 @@
       <xdr:col>43</xdr:col>
       <xdr:colOff>158334</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>3731609</xdr:rowOff>
+      <xdr:rowOff>3503382</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2131,8 +1997,8 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>733550</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>133597</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>6597</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2180,8 +2046,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>297872</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>100853</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2230,7 +2096,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>1125682</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>1091044</xdr:rowOff>
+      <xdr:rowOff>559953</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2273,8 +2139,8 @@
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>437274</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>114002</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2322,8 +2188,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1143000</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>95835</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>207893</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2378,7 +2244,7 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>464342</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2428,7 +2294,7 @@
       <xdr:col>20</xdr:col>
       <xdr:colOff>253045</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
+      <xdr:rowOff>119063</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2478,7 +2344,7 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>851897</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>1893094</xdr:rowOff>
+      <xdr:rowOff>1416844</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2528,7 +2394,7 @@
       <xdr:col>22</xdr:col>
       <xdr:colOff>416719</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>1976438</xdr:rowOff>
+      <xdr:rowOff>1547813</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2583,7 +2449,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>1722088</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>935182</xdr:rowOff>
+      <xdr:rowOff>282038</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2907,229 +2773,230 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="83.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" style="71" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.44140625" style="71" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" style="71" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="83.77734375" style="71" customWidth="1"/>
+    <col min="5" max="16384" width="8.77734375" style="71"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="2" spans="1:4" ht="11.25" customHeight="1">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
     </row>
     <row r="3" spans="1:4" ht="42.75" customHeight="1">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-    </row>
-    <row r="4" spans="1:4" ht="20.25" thickBot="1">
-      <c r="A4" s="19" t="s">
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+    </row>
+    <row r="4" spans="1:4" ht="19.2" thickBot="1">
+      <c r="A4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="27" customHeight="1" thickBot="1">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A6" s="20">
+      <c r="A6" s="76">
         <v>1</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="72" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="65.25" customHeight="1" thickBot="1">
-      <c r="A7" s="20">
+      <c r="A7" s="76">
         <v>2</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="72" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="39.75" thickBot="1">
-      <c r="A8" s="20">
+    <row r="8" spans="1:4" ht="39" thickBot="1">
+      <c r="A8" s="76">
         <v>3</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="72" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="39.75" thickBot="1">
-      <c r="A9" s="20">
+    <row r="9" spans="1:4" ht="39" thickBot="1">
+      <c r="A9" s="76">
         <v>4</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="72" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="39.75" thickBot="1">
-      <c r="A10" s="20">
+    <row r="10" spans="1:4" ht="39" thickBot="1">
+      <c r="A10" s="76">
         <v>5</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="72" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="39.75" thickBot="1">
-      <c r="A11" s="20">
+    <row r="11" spans="1:4" ht="39" thickBot="1">
+      <c r="A11" s="76">
         <v>6</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="72" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="39">
-      <c r="A12" s="24">
+    <row r="12" spans="1:4" ht="38.4">
+      <c r="A12" s="77">
         <v>7</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="73" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
+      <c r="A14" s="74"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
+      <c r="A15" s="74"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
+      <c r="A16" s="74"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
+      <c r="A17" s="75"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
+      <c r="A18" s="75"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
+      <c r="A19" s="75"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
+      <c r="A20" s="75"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
+      <c r="A21" s="75"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
+      <c r="A22" s="75"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
+      <c r="A23" s="75"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
+      <c r="A24" s="75"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3137,417 +3004,419 @@
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7629BE57-428C-472B-A0E1-93D00EE6CD29}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" customWidth="1"/>
-    <col min="2" max="2" width="38.7109375" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" customWidth="1"/>
-    <col min="5" max="5" width="33" customWidth="1"/>
-    <col min="6" max="6" width="35" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" customWidth="1"/>
-    <col min="12" max="12" width="19" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="25.21875" style="27" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" style="27" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" style="27" customWidth="1"/>
+    <col min="5" max="5" width="33" style="27" customWidth="1"/>
+    <col min="6" max="6" width="35" style="27" customWidth="1"/>
+    <col min="7" max="7" width="17" style="27" customWidth="1"/>
+    <col min="8" max="8" width="19.77734375" style="27" customWidth="1"/>
+    <col min="9" max="9" width="20.21875" style="27" customWidth="1"/>
+    <col min="10" max="10" width="17.77734375" style="27" customWidth="1"/>
+    <col min="11" max="11" width="23.77734375" style="27" customWidth="1"/>
+    <col min="12" max="12" width="19" style="27" customWidth="1"/>
+    <col min="13" max="13" width="16.77734375" style="27" customWidth="1"/>
+    <col min="14" max="16384" width="8.77734375" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="91" t="s">
+      <c r="B1" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-    </row>
-    <row r="2" spans="1:6" ht="19.5">
-      <c r="A2" s="25" t="s">
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-    </row>
-    <row r="3" spans="1:6" ht="19.5">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27" t="s">
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="28"/>
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="19.5">
-      <c r="A4" s="82" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="83">
+      <c r="B4" s="70">
         <v>5</v>
       </c>
-      <c r="C4" s="83">
+      <c r="C4" s="70">
         <v>0</v>
       </c>
-      <c r="D4" s="83">
+      <c r="D4" s="70">
         <v>0</v>
       </c>
-      <c r="E4" s="83">
+      <c r="E4" s="70">
         <v>0</v>
       </c>
-      <c r="F4" s="83">
+      <c r="F4" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="19.5">
-      <c r="A5" s="82" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="83">
+      <c r="B5" s="70">
         <v>5</v>
       </c>
-      <c r="C5" s="83">
+      <c r="C5" s="70">
         <v>0</v>
       </c>
-      <c r="D5" s="83">
+      <c r="D5" s="70">
         <v>0</v>
       </c>
-      <c r="E5" s="83">
+      <c r="E5" s="70">
         <v>0</v>
       </c>
-      <c r="F5" s="83">
+      <c r="F5" s="70">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="300.75" customHeight="1"/>
-    <row r="19" spans="1:13" ht="19.5">
-      <c r="A19" s="93" t="s">
+    <row r="19" spans="1:13">
+      <c r="A19" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="93" t="s">
+      <c r="B19" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="93" t="s">
+      <c r="C19" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="93" t="s">
+      <c r="D19" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="94" t="s">
+      <c r="E19" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="93" t="s">
+      <c r="F19" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="86" t="s">
+      <c r="G19" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="86" t="s">
+      <c r="H19" s="80"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="80"/>
+      <c r="L19" s="80"/>
+      <c r="M19" s="80" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="19.5">
-      <c r="A20" s="93"/>
-      <c r="B20" s="93"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="86" t="s">
+    <row r="20" spans="1:13">
+      <c r="A20" s="87"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86" t="s">
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="87"/>
-    </row>
-    <row r="21" spans="1:13" ht="19.5">
-      <c r="A21" s="93"/>
-      <c r="B21" s="93"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="93"/>
-      <c r="G21" s="60" t="s">
+      <c r="K20" s="80"/>
+      <c r="L20" s="80"/>
+      <c r="M20" s="81"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="87"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H21" s="38" t="s">
+      <c r="H21" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="60" t="s">
+      <c r="I21" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="60" t="s">
+      <c r="J21" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K21" s="60" t="s">
+      <c r="K21" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L21" s="60" t="s">
+      <c r="L21" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M21" s="87"/>
-    </row>
-    <row r="22" spans="1:13" ht="20.25" thickBot="1">
-      <c r="A22" s="39" t="s">
+      <c r="M21" s="81"/>
+    </row>
+    <row r="22" spans="1:13" ht="17.399999999999999" thickBot="1">
+      <c r="A22" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="41"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="21"/>
     </row>
     <row r="23" spans="1:13" ht="106.5" customHeight="1" thickBot="1">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="65" t="s">
         <v>306</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="65" t="s">
         <v>301</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="65" t="s">
         <v>302</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="E23" s="42" t="s">
+      <c r="E23" s="65" t="s">
         <v>303</v>
       </c>
-      <c r="F23" s="42" t="s">
+      <c r="F23" s="65" t="s">
         <v>304</v>
       </c>
-      <c r="G23" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="44">
+      <c r="G23" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="67">
         <v>46282</v>
       </c>
-      <c r="I23" s="42" t="s">
+      <c r="I23" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="J23" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="44">
+      <c r="J23" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="67">
         <v>46282</v>
       </c>
-      <c r="L23" s="42" t="s">
+      <c r="L23" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="M23" s="42"/>
-    </row>
-    <row r="24" spans="1:13" ht="98.25" thickBot="1">
-      <c r="A24" s="42" t="s">
+      <c r="M23" s="65"/>
+    </row>
+    <row r="24" spans="1:13" ht="67.8" thickBot="1">
+      <c r="A24" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="65" t="s">
         <v>307</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="65" t="s">
         <v>308</v>
       </c>
-      <c r="D24" s="42" t="s">
+      <c r="D24" s="65" t="s">
         <v>309</v>
       </c>
-      <c r="E24" s="42" t="s">
+      <c r="E24" s="65" t="s">
         <v>310</v>
       </c>
-      <c r="F24" s="42" t="s">
+      <c r="F24" s="65" t="s">
         <v>311</v>
       </c>
-      <c r="G24" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="44">
+      <c r="G24" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="67">
         <v>46282</v>
       </c>
-      <c r="I24" s="42" t="s">
+      <c r="I24" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="J24" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="44">
+      <c r="J24" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="67">
         <v>46282</v>
       </c>
-      <c r="L24" s="42" t="s">
+      <c r="L24" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="M24" s="42"/>
-    </row>
-    <row r="25" spans="1:13" ht="98.25" thickBot="1">
-      <c r="A25" s="42" t="s">
+      <c r="M24" s="65"/>
+    </row>
+    <row r="25" spans="1:13" ht="67.8" thickBot="1">
+      <c r="A25" s="65" t="s">
         <v>312</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="65" t="s">
         <v>313</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="65" t="s">
         <v>314</v>
       </c>
-      <c r="D25" s="42" t="s">
+      <c r="D25" s="65" t="s">
         <v>315</v>
       </c>
-      <c r="E25" s="42" t="s">
+      <c r="E25" s="65" t="s">
         <v>316</v>
       </c>
-      <c r="F25" s="42" t="s">
+      <c r="F25" s="65" t="s">
         <v>317</v>
       </c>
-      <c r="G25" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="44">
+      <c r="G25" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="67">
         <v>46282</v>
       </c>
-      <c r="I25" s="42" t="s">
+      <c r="I25" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="J25" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="44">
+      <c r="J25" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="67">
         <v>46282</v>
       </c>
-      <c r="L25" s="42" t="s">
+      <c r="L25" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="M25" s="42"/>
-    </row>
-    <row r="26" spans="1:13" ht="20.25" thickBot="1">
-      <c r="A26" s="88" t="s">
+      <c r="M25" s="65"/>
+    </row>
+    <row r="26" spans="1:13" ht="17.399999999999999" thickBot="1">
+      <c r="A26" s="82" t="s">
         <v>331</v>
       </c>
-      <c r="B26" s="89"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="89"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="89"/>
-      <c r="K26" s="89"/>
-      <c r="L26" s="89"/>
-      <c r="M26" s="90"/>
-    </row>
-    <row r="27" spans="1:13" ht="98.25" thickBot="1">
-      <c r="A27" s="42" t="s">
+      <c r="B26" s="83"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="83"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="83"/>
+      <c r="J26" s="83"/>
+      <c r="K26" s="83"/>
+      <c r="L26" s="83"/>
+      <c r="M26" s="84"/>
+    </row>
+    <row r="27" spans="1:13" ht="67.8" thickBot="1">
+      <c r="A27" s="65" t="s">
         <v>318</v>
       </c>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="65" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="65" t="s">
         <v>320</v>
       </c>
-      <c r="D27" s="42" t="s">
+      <c r="D27" s="65" t="s">
         <v>321</v>
       </c>
-      <c r="E27" s="42" t="s">
+      <c r="E27" s="65" t="s">
         <v>322</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="65" t="s">
         <v>323</v>
       </c>
-      <c r="G27" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H27" s="44">
+      <c r="G27" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="67">
         <v>46282</v>
       </c>
-      <c r="I27" s="42" t="s">
+      <c r="I27" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="J27" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="44">
+      <c r="J27" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="67">
         <v>46282</v>
       </c>
-      <c r="L27" s="42" t="s">
+      <c r="L27" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="M27" s="45"/>
-    </row>
-    <row r="28" spans="1:13" ht="98.25" thickBot="1">
-      <c r="A28" s="42" t="s">
+      <c r="M27" s="44"/>
+    </row>
+    <row r="28" spans="1:13" ht="67.8" thickBot="1">
+      <c r="A28" s="65" t="s">
         <v>324</v>
       </c>
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="65" t="s">
         <v>325</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="65" t="s">
         <v>326</v>
       </c>
-      <c r="D28" s="42" t="s">
+      <c r="D28" s="65" t="s">
         <v>327</v>
       </c>
-      <c r="E28" s="42" t="s">
+      <c r="E28" s="65" t="s">
         <v>328</v>
       </c>
-      <c r="F28" s="42" t="s">
+      <c r="F28" s="65" t="s">
         <v>329</v>
       </c>
-      <c r="G28" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H28" s="44">
+      <c r="G28" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="67">
         <v>46282</v>
       </c>
-      <c r="I28" s="42" t="s">
+      <c r="I28" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" s="44">
+      <c r="J28" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="67">
         <v>46282</v>
       </c>
-      <c r="L28" s="42" t="s">
+      <c r="L28" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="M28" s="45"/>
+      <c r="M28" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -3566,1130 +3435,916 @@
     <mergeCell ref="A26:M26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N77"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="51.5703125" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="39.42578125" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.77734375" style="27" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" style="27" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" style="27" customWidth="1"/>
+    <col min="4" max="4" width="39.44140625" style="27" customWidth="1"/>
+    <col min="5" max="5" width="29.5546875" style="27" customWidth="1"/>
+    <col min="6" max="6" width="28.77734375" style="27" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" style="27" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" style="27" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" style="27" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.21875" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-    </row>
-    <row r="2" spans="1:12" ht="19.5">
-      <c r="A2" s="25" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-    </row>
-    <row r="3" spans="1:12" ht="20.25" thickBot="1">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27" t="s">
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+    </row>
+    <row r="3" spans="1:12" ht="17.399999999999999" thickBot="1">
+      <c r="A3" s="28"/>
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-    </row>
-    <row r="4" spans="1:12" ht="20.25" thickBot="1">
-      <c r="A4" s="29" t="s">
+      <c r="G3" s="61"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+    </row>
+    <row r="4" spans="1:12" ht="17.399999999999999" thickBot="1">
+      <c r="A4" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="63">
         <v>5</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="63">
         <v>0</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="63">
         <v>0</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="63">
         <v>0</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="64">
         <v>5</v>
       </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-    </row>
-    <row r="5" spans="1:12" ht="20.25" thickBot="1">
-      <c r="A5" s="29" t="s">
+      <c r="G4" s="60"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+    </row>
+    <row r="5" spans="1:12" ht="17.399999999999999" thickBot="1">
+      <c r="A5" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="63">
         <v>5</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="63">
         <v>0</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="63">
         <v>0</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="63">
         <v>0</v>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="64">
         <v>5</v>
       </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-    </row>
-    <row r="6" spans="1:12" ht="199.5" customHeight="1">
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-    </row>
+      <c r="G5" s="60"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+    </row>
+    <row r="6" spans="1:12" ht="199.5" customHeight="1"/>
     <row r="31" spans="1:13" ht="42.75" customHeight="1">
-      <c r="A31" s="93" t="s">
+      <c r="A31" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="93" t="s">
+      <c r="B31" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="93" t="s">
+      <c r="C31" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="93" t="s">
+      <c r="D31" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="94" t="s">
+      <c r="E31" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="93" t="s">
+      <c r="F31" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="86" t="s">
+      <c r="G31" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="86"/>
-      <c r="I31" s="86"/>
-      <c r="J31" s="86"/>
-      <c r="K31" s="86"/>
-      <c r="L31" s="86"/>
-      <c r="M31" s="86" t="s">
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="80"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="80"/>
+      <c r="M31" s="80" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="19.5">
-      <c r="A32" s="93"/>
-      <c r="B32" s="93"/>
-      <c r="C32" s="93"/>
-      <c r="D32" s="93"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="93"/>
-      <c r="G32" s="86" t="s">
+    <row r="32" spans="1:13">
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86" t="s">
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="86"/>
-      <c r="L32" s="86"/>
-      <c r="M32" s="87"/>
-    </row>
-    <row r="33" spans="1:14" ht="19.5">
-      <c r="A33" s="93"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="93"/>
-      <c r="E33" s="94"/>
-      <c r="F33" s="93"/>
-      <c r="G33" s="37" t="s">
+      <c r="K32" s="80"/>
+      <c r="L32" s="80"/>
+      <c r="M32" s="81"/>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="38" t="s">
+      <c r="H33" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="37" t="s">
+      <c r="I33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="37" t="s">
+      <c r="J33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="37" t="s">
+      <c r="K33" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="37" t="s">
+      <c r="L33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="87"/>
+      <c r="M33" s="81"/>
     </row>
     <row r="34" spans="1:14" ht="66.75" customHeight="1" thickBot="1">
-      <c r="A34" s="39" t="s">
+      <c r="A34" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="40"/>
-      <c r="L34" s="40"/>
-      <c r="M34" s="41"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="21"/>
     </row>
     <row r="35" spans="1:14" ht="94.5" customHeight="1" thickBot="1">
-      <c r="A35" s="42" t="s">
+      <c r="A35" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="43" t="s">
+      <c r="B35" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42" t="s">
+      <c r="C35" s="65"/>
+      <c r="D35" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="E35" s="42" t="s">
+      <c r="E35" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="F35" s="42" t="s">
+      <c r="F35" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="G35" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="44">
+      <c r="G35" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="67">
         <v>46282</v>
       </c>
-      <c r="I35" s="42" t="s">
+      <c r="I35" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="J35" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="44">
+      <c r="J35" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="67">
         <v>46282</v>
       </c>
-      <c r="L35" s="42" t="s">
+      <c r="L35" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="M35" s="42"/>
-    </row>
-    <row r="36" spans="1:14" ht="78.75" thickBot="1">
-      <c r="A36" s="42" t="s">
+      <c r="M35" s="65"/>
+    </row>
+    <row r="36" spans="1:14" ht="67.8" thickBot="1">
+      <c r="A36" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="43" t="s">
+      <c r="B36" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42" t="s">
+      <c r="C36" s="65"/>
+      <c r="D36" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E36" s="42" t="s">
+      <c r="E36" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="F36" s="42" t="s">
+      <c r="F36" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="G36" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="44">
+      <c r="G36" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="67">
         <v>46282</v>
       </c>
-      <c r="I36" s="42" t="s">
+      <c r="I36" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="J36" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="44">
+      <c r="J36" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="67">
         <v>46282</v>
       </c>
-      <c r="L36" s="42" t="s">
+      <c r="L36" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="M36" s="42"/>
-    </row>
-    <row r="37" spans="1:14" ht="59.25" thickBot="1">
-      <c r="A37" s="42" t="s">
+      <c r="M36" s="65"/>
+    </row>
+    <row r="37" spans="1:14" ht="51" thickBot="1">
+      <c r="A37" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="43" t="s">
+      <c r="B37" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="42"/>
-      <c r="D37" s="42" t="s">
+      <c r="C37" s="65"/>
+      <c r="D37" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="42" t="s">
+      <c r="E37" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="F37" s="42" t="s">
+      <c r="F37" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="G37" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="44">
+      <c r="G37" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="67">
         <v>46282</v>
       </c>
-      <c r="I37" s="42" t="s">
+      <c r="I37" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="J37" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" s="44">
+      <c r="J37" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="67">
         <v>46282</v>
       </c>
-      <c r="L37" s="42" t="s">
+      <c r="L37" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="M37" s="42"/>
-    </row>
-    <row r="38" spans="1:14" ht="78.75" thickBot="1">
-      <c r="A38" s="42" t="s">
+      <c r="M37" s="65"/>
+    </row>
+    <row r="38" spans="1:14" ht="51" thickBot="1">
+      <c r="A38" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="43" t="s">
+      <c r="B38" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="C38" s="42"/>
-      <c r="D38" s="42" t="s">
+      <c r="C38" s="65"/>
+      <c r="D38" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E38" s="42" t="s">
+      <c r="E38" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="F38" s="42" t="s">
+      <c r="F38" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="G38" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="44">
+      <c r="G38" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="67">
         <v>46282</v>
       </c>
-      <c r="I38" s="42" t="s">
+      <c r="I38" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="J38" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="44">
+      <c r="J38" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="67">
         <v>46282</v>
       </c>
-      <c r="L38" s="42" t="s">
+      <c r="L38" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="M38" s="42"/>
-    </row>
-    <row r="39" spans="1:14" ht="78.75" thickBot="1">
-      <c r="A39" s="42" t="s">
+      <c r="M38" s="65"/>
+    </row>
+    <row r="39" spans="1:14" ht="51" thickBot="1">
+      <c r="A39" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="B39" s="43" t="s">
+      <c r="B39" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C39" s="42"/>
-      <c r="D39" s="42" t="s">
+      <c r="C39" s="65"/>
+      <c r="D39" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E39" s="42" t="s">
+      <c r="E39" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="F39" s="42" t="s">
+      <c r="F39" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="G39" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="44">
+      <c r="G39" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="67">
         <v>46282</v>
       </c>
-      <c r="I39" s="42" t="s">
+      <c r="I39" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="J39" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="44">
+      <c r="J39" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="67">
         <v>46282</v>
       </c>
-      <c r="L39" s="42" t="s">
+      <c r="L39" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="M39" s="42"/>
-    </row>
-    <row r="40" spans="1:14" ht="59.25" thickBot="1">
-      <c r="A40" s="42" t="s">
+      <c r="M39" s="65"/>
+    </row>
+    <row r="40" spans="1:14" ht="51" thickBot="1">
+      <c r="A40" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="43" t="s">
+      <c r="B40" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42" t="s">
+      <c r="C40" s="65"/>
+      <c r="D40" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="E40" s="42" t="s">
+      <c r="E40" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="F40" s="42" t="s">
+      <c r="F40" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="G40" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="44">
+      <c r="G40" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="67">
         <v>46282</v>
       </c>
-      <c r="I40" s="42" t="s">
+      <c r="I40" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="J40" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="44">
+      <c r="J40" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="67">
         <v>46282</v>
       </c>
-      <c r="L40" s="42" t="s">
+      <c r="L40" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="M40" s="42"/>
-    </row>
-    <row r="41" spans="1:14" ht="78.75" thickBot="1">
-      <c r="A41" s="42" t="s">
+      <c r="M40" s="65"/>
+    </row>
+    <row r="41" spans="1:14" ht="51" thickBot="1">
+      <c r="A41" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="43" t="s">
+      <c r="B41" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42" t="s">
+      <c r="C41" s="65"/>
+      <c r="D41" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="E41" s="42" t="s">
+      <c r="E41" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="F41" s="42" t="s">
+      <c r="F41" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="G41" s="42" t="s">
+      <c r="G41" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="H41" s="44">
+      <c r="H41" s="67">
         <v>46282</v>
       </c>
-      <c r="I41" s="42" t="s">
+      <c r="I41" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="J41" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" s="44">
+      <c r="J41" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="67">
         <v>46283</v>
       </c>
-      <c r="L41" s="42" t="s">
+      <c r="L41" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="M41" s="42" t="s">
+      <c r="M41" s="65" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="20.25" thickBot="1">
-      <c r="A42" s="88" t="s">
+    <row r="42" spans="1:14" ht="17.399999999999999" thickBot="1">
+      <c r="A42" s="82" t="s">
         <v>332</v>
       </c>
-      <c r="B42" s="89"/>
-      <c r="C42" s="89"/>
-      <c r="D42" s="89"/>
-      <c r="E42" s="89"/>
-      <c r="F42" s="89"/>
-      <c r="G42" s="89"/>
-      <c r="H42" s="89"/>
-      <c r="I42" s="89"/>
-      <c r="J42" s="89"/>
-      <c r="K42" s="89"/>
-      <c r="L42" s="89"/>
-      <c r="M42" s="90"/>
+      <c r="B42" s="83"/>
+      <c r="C42" s="83"/>
+      <c r="D42" s="83"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="83"/>
+      <c r="H42" s="83"/>
+      <c r="I42" s="83"/>
+      <c r="J42" s="83"/>
+      <c r="K42" s="83"/>
+      <c r="L42" s="83"/>
+      <c r="M42" s="84"/>
       <c r="N42" s="1"/>
     </row>
     <row r="43" spans="1:14" ht="127.5" customHeight="1" thickBot="1">
-      <c r="A43" s="42" t="s">
+      <c r="A43" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="B43" s="42" t="s">
+      <c r="B43" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="C43" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="D43" s="42" t="s">
+      <c r="D43" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E43" s="42" t="s">
+      <c r="E43" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="F43" s="42" t="s">
+      <c r="F43" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="G43" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" s="44">
+      <c r="G43" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="67">
         <v>46282</v>
       </c>
-      <c r="I43" s="42" t="s">
+      <c r="I43" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="J43" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="44">
+      <c r="J43" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="67">
         <v>46282</v>
       </c>
-      <c r="L43" s="42" t="s">
+      <c r="L43" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="M43" s="45"/>
-    </row>
-    <row r="44" spans="1:14" ht="59.25" thickBot="1">
-      <c r="A44" s="42" t="s">
+      <c r="M43" s="44"/>
+    </row>
+    <row r="44" spans="1:14" ht="51" thickBot="1">
+      <c r="A44" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="42" t="s">
+      <c r="B44" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="42" t="s">
+      <c r="C44" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="D44" s="42" t="s">
+      <c r="D44" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="E44" s="42" t="s">
+      <c r="E44" s="65" t="s">
         <v>100</v>
       </c>
-      <c r="F44" s="42" t="s">
+      <c r="F44" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="G44" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" s="44">
+      <c r="G44" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="67">
         <v>46282</v>
       </c>
-      <c r="I44" s="42" t="s">
+      <c r="I44" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="J44" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="44">
+      <c r="J44" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="67">
         <v>46282</v>
       </c>
-      <c r="L44" s="42" t="s">
+      <c r="L44" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="M44" s="45"/>
+      <c r="M44" s="44"/>
     </row>
     <row r="45" spans="1:14" ht="165" customHeight="1" thickBot="1">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="42" t="s">
+      <c r="B45" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="42" t="s">
+      <c r="D45" s="65" t="s">
         <v>103</v>
       </c>
-      <c r="E45" s="42" t="s">
+      <c r="E45" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="42" t="s">
+      <c r="F45" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="G45" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="44">
+      <c r="G45" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="67">
         <v>46282</v>
       </c>
-      <c r="I45" s="42" t="s">
+      <c r="I45" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="J45" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K45" s="44">
+      <c r="J45" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" s="67">
         <v>46282</v>
       </c>
-      <c r="L45" s="42" t="s">
+      <c r="L45" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="M45" s="45"/>
+      <c r="M45" s="44"/>
     </row>
     <row r="46" spans="1:14" ht="165" customHeight="1" thickBot="1">
-      <c r="A46" s="42" t="s">
+      <c r="A46" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="B46" s="42" t="s">
+      <c r="B46" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="C46" s="42" t="s">
+      <c r="C46" s="65" t="s">
         <v>106</v>
       </c>
-      <c r="D46" s="42" t="s">
+      <c r="D46" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="E46" s="42" t="s">
+      <c r="E46" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="F46" s="42" t="s">
+      <c r="F46" s="65" t="s">
         <v>108</v>
       </c>
-      <c r="G46" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H46" s="44">
+      <c r="G46" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H46" s="67">
         <v>46282</v>
       </c>
-      <c r="I46" s="42" t="s">
+      <c r="I46" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="J46" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K46" s="44">
+      <c r="J46" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" s="67">
         <v>46282</v>
       </c>
-      <c r="L46" s="42" t="s">
+      <c r="L46" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="M46" s="45"/>
-    </row>
-    <row r="49" spans="1:13">
-      <c r="A49" s="31"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="31"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="31"/>
-      <c r="K49" s="31"/>
-      <c r="L49" s="31"/>
-      <c r="M49" s="31"/>
-    </row>
-    <row r="50" spans="1:13">
-      <c r="A50" s="31"/>
-      <c r="B50" s="31"/>
-      <c r="C50" s="31"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="31"/>
-      <c r="I50" s="31"/>
-      <c r="J50" s="31"/>
-      <c r="K50" s="31"/>
-      <c r="L50" s="31"/>
-      <c r="M50" s="31"/>
-    </row>
-    <row r="51" spans="1:13">
-      <c r="A51" s="31"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="31"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="31"/>
-      <c r="I51" s="31"/>
-      <c r="J51" s="31"/>
-      <c r="K51" s="31"/>
-      <c r="L51" s="31"/>
-      <c r="M51" s="31"/>
-    </row>
-    <row r="52" spans="1:13">
-      <c r="A52" s="31"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
-      <c r="H52" s="31"/>
-      <c r="I52" s="31"/>
-      <c r="J52" s="31"/>
-      <c r="K52" s="31"/>
-      <c r="L52" s="31"/>
-      <c r="M52" s="31"/>
-    </row>
-    <row r="53" spans="1:13">
-      <c r="A53" s="31"/>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-    </row>
-    <row r="54" spans="1:13">
-      <c r="A54" s="31"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="32"/>
-      <c r="K54" s="32"/>
-      <c r="L54" s="31"/>
-      <c r="M54" s="31"/>
-    </row>
-    <row r="55" spans="1:13">
-      <c r="A55" s="31"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="32"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
-      <c r="F55" s="33"/>
-      <c r="G55" s="33"/>
-      <c r="H55" s="33"/>
-      <c r="I55" s="33"/>
-      <c r="J55" s="33"/>
-      <c r="K55" s="33"/>
-      <c r="L55" s="31"/>
-      <c r="M55" s="31"/>
-    </row>
-    <row r="56" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A56" s="31"/>
-      <c r="B56" s="31"/>
-      <c r="C56" s="95"/>
-      <c r="D56" s="95"/>
-      <c r="E56" s="95"/>
-      <c r="F56" s="95"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="95"/>
-      <c r="J56" s="95"/>
-      <c r="K56" s="95"/>
-      <c r="L56" s="31"/>
-      <c r="M56" s="31"/>
-    </row>
-    <row r="57" spans="1:13">
-      <c r="A57" s="31"/>
-      <c r="B57" s="31"/>
-      <c r="C57" s="95"/>
-      <c r="D57" s="95"/>
-      <c r="E57" s="95"/>
-      <c r="F57" s="95"/>
-      <c r="G57" s="34"/>
-      <c r="H57" s="34"/>
-      <c r="I57" s="95"/>
-      <c r="J57" s="95"/>
-      <c r="K57" s="95"/>
-      <c r="L57" s="31"/>
-      <c r="M57" s="31"/>
-    </row>
-    <row r="58" spans="1:13" ht="57" customHeight="1">
-      <c r="A58" s="31"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="95"/>
-      <c r="D58" s="95"/>
-      <c r="E58" s="95"/>
-      <c r="F58" s="95"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="95"/>
-      <c r="J58" s="95"/>
-      <c r="K58" s="95"/>
-      <c r="L58" s="31"/>
-      <c r="M58" s="31"/>
-    </row>
-    <row r="59" spans="1:13">
-      <c r="A59" s="31"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="33"/>
-      <c r="H59" s="33"/>
-      <c r="I59" s="33"/>
-      <c r="J59" s="33"/>
-      <c r="K59" s="33"/>
-      <c r="L59" s="31"/>
-      <c r="M59" s="31"/>
-    </row>
-    <row r="60" spans="1:13">
-      <c r="A60" s="31"/>
-      <c r="B60" s="31"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="33"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="33"/>
-      <c r="J60" s="33"/>
-      <c r="K60" s="33"/>
-      <c r="L60" s="31"/>
-      <c r="M60" s="31"/>
-    </row>
-    <row r="61" spans="1:13">
-      <c r="A61" s="31"/>
-      <c r="B61" s="31"/>
-      <c r="C61" s="95"/>
-      <c r="D61" s="95"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="95"/>
-      <c r="G61" s="23"/>
-      <c r="H61" s="23"/>
-      <c r="I61" s="95"/>
-      <c r="J61" s="95"/>
-      <c r="K61" s="95"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="31"/>
-    </row>
-    <row r="62" spans="1:13">
-      <c r="A62" s="31"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="95"/>
-      <c r="D62" s="95"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="95"/>
-      <c r="G62" s="34"/>
-      <c r="H62" s="34"/>
-      <c r="I62" s="95"/>
-      <c r="J62" s="95"/>
-      <c r="K62" s="95"/>
-      <c r="L62" s="31"/>
-      <c r="M62" s="31"/>
-    </row>
-    <row r="63" spans="1:13">
-      <c r="A63" s="31"/>
-      <c r="B63" s="31"/>
-      <c r="C63" s="95"/>
-      <c r="D63" s="95"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="95"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="23"/>
-      <c r="I63" s="95"/>
-      <c r="J63" s="95"/>
-      <c r="K63" s="95"/>
-      <c r="L63" s="31"/>
-      <c r="M63" s="31"/>
-    </row>
-    <row r="64" spans="1:13">
-      <c r="A64" s="31"/>
-      <c r="B64" s="31"/>
-      <c r="C64" s="95"/>
-      <c r="D64" s="95"/>
-      <c r="E64" s="34"/>
-      <c r="F64" s="95"/>
-      <c r="G64" s="34"/>
-      <c r="H64" s="34"/>
-      <c r="I64" s="95"/>
-      <c r="J64" s="95"/>
-      <c r="K64" s="95"/>
-      <c r="L64" s="31"/>
-      <c r="M64" s="31"/>
-    </row>
-    <row r="65" spans="1:13">
-      <c r="A65" s="31"/>
-      <c r="B65" s="31"/>
-      <c r="C65" s="95"/>
-      <c r="D65" s="95"/>
-      <c r="E65" s="23"/>
-      <c r="F65" s="95"/>
-      <c r="G65" s="23"/>
-      <c r="H65" s="23"/>
-      <c r="I65" s="95"/>
-      <c r="J65" s="95"/>
-      <c r="K65" s="95"/>
-      <c r="L65" s="31"/>
-      <c r="M65" s="31"/>
-    </row>
-    <row r="66" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A66" s="31"/>
-      <c r="B66" s="31"/>
-      <c r="C66" s="95"/>
-      <c r="D66" s="95"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="95"/>
-      <c r="G66" s="34"/>
-      <c r="H66" s="34"/>
-      <c r="I66" s="95"/>
-      <c r="J66" s="95"/>
-      <c r="K66" s="95"/>
-      <c r="L66" s="31"/>
-      <c r="M66" s="31"/>
-    </row>
-    <row r="67" spans="1:13">
-      <c r="A67" s="31"/>
-      <c r="B67" s="31"/>
-      <c r="C67" s="95"/>
-      <c r="D67" s="95"/>
-      <c r="E67" s="34"/>
-      <c r="F67" s="95"/>
-      <c r="G67" s="23"/>
-      <c r="H67" s="23"/>
-      <c r="I67" s="95"/>
-      <c r="J67" s="95"/>
-      <c r="K67" s="95"/>
-      <c r="L67" s="31"/>
-      <c r="M67" s="31"/>
-    </row>
-    <row r="68" spans="1:13" ht="40.5" customHeight="1">
-      <c r="A68" s="31"/>
-      <c r="B68" s="31"/>
-      <c r="C68" s="95"/>
-      <c r="D68" s="95"/>
-      <c r="E68" s="23"/>
-      <c r="F68" s="95"/>
-      <c r="G68" s="95"/>
-      <c r="H68" s="95"/>
-      <c r="I68" s="95"/>
-      <c r="J68" s="95"/>
-      <c r="K68" s="95"/>
-      <c r="L68" s="31"/>
-      <c r="M68" s="31"/>
-    </row>
-    <row r="69" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A69" s="31"/>
-      <c r="B69" s="31"/>
-      <c r="C69" s="95"/>
-      <c r="D69" s="95"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="95"/>
-      <c r="G69" s="95"/>
-      <c r="H69" s="95"/>
-      <c r="I69" s="95"/>
-      <c r="J69" s="95"/>
-      <c r="K69" s="95"/>
-      <c r="L69" s="31"/>
-      <c r="M69" s="31"/>
-    </row>
-    <row r="70" spans="1:13">
-      <c r="A70" s="31"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="95"/>
-      <c r="D70" s="95"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="95"/>
-      <c r="G70" s="95"/>
-      <c r="H70" s="95"/>
-      <c r="I70" s="95"/>
-      <c r="J70" s="95"/>
-      <c r="K70" s="95"/>
-      <c r="L70" s="31"/>
-      <c r="M70" s="31"/>
-    </row>
-    <row r="71" spans="1:13" ht="42.75" customHeight="1">
-      <c r="A71" s="31"/>
-      <c r="B71" s="31"/>
-      <c r="C71" s="95"/>
-      <c r="D71" s="95"/>
-      <c r="E71" s="23"/>
-      <c r="F71" s="95"/>
-      <c r="G71" s="95"/>
-      <c r="H71" s="95"/>
-      <c r="I71" s="95"/>
-      <c r="J71" s="95"/>
-      <c r="K71" s="95"/>
-      <c r="L71" s="31"/>
-      <c r="M71" s="31"/>
-    </row>
-    <row r="72" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A72" s="31"/>
-      <c r="B72" s="31"/>
-      <c r="C72" s="95"/>
-      <c r="D72" s="95"/>
-      <c r="E72" s="34"/>
-      <c r="F72" s="95"/>
-      <c r="G72" s="95"/>
-      <c r="H72" s="95"/>
-      <c r="I72" s="95"/>
-      <c r="J72" s="95"/>
-      <c r="K72" s="95"/>
-      <c r="L72" s="31"/>
-      <c r="M72" s="31"/>
-    </row>
-    <row r="73" spans="1:13">
-      <c r="A73" s="31"/>
-      <c r="B73" s="31"/>
-      <c r="C73" s="95"/>
-      <c r="D73" s="95"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="95"/>
-      <c r="G73" s="95"/>
-      <c r="H73" s="95"/>
-      <c r="I73" s="95"/>
-      <c r="J73" s="95"/>
-      <c r="K73" s="95"/>
-      <c r="L73" s="31"/>
-      <c r="M73" s="31"/>
-    </row>
-    <row r="74" spans="1:13" ht="42.75" customHeight="1">
-      <c r="A74" s="31"/>
-      <c r="B74" s="31"/>
-      <c r="C74" s="95"/>
-      <c r="D74" s="95"/>
-      <c r="E74" s="34"/>
-      <c r="F74" s="95"/>
-      <c r="G74" s="95"/>
-      <c r="H74" s="95"/>
-      <c r="I74" s="95"/>
-      <c r="J74" s="95"/>
-      <c r="K74" s="95"/>
-      <c r="L74" s="31"/>
-      <c r="M74" s="31"/>
-    </row>
-    <row r="75" spans="1:13">
-      <c r="A75" s="31"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="95"/>
-      <c r="D75" s="95"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="95"/>
-      <c r="G75" s="95"/>
-      <c r="H75" s="95"/>
-      <c r="I75" s="95"/>
-      <c r="J75" s="95"/>
-      <c r="K75" s="95"/>
-      <c r="L75" s="31"/>
-      <c r="M75" s="31"/>
-    </row>
-    <row r="76" spans="1:13">
-      <c r="A76" s="31"/>
-      <c r="B76" s="31"/>
-      <c r="C76" s="31"/>
-      <c r="D76" s="31"/>
-      <c r="E76" s="31"/>
-      <c r="F76" s="31"/>
-      <c r="G76" s="31"/>
-      <c r="H76" s="31"/>
-      <c r="I76" s="31"/>
-      <c r="J76" s="31"/>
-      <c r="K76" s="31"/>
-      <c r="L76" s="31"/>
-      <c r="M76" s="31"/>
-    </row>
-    <row r="77" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A77" s="31"/>
-      <c r="B77" s="31"/>
-      <c r="C77" s="31"/>
-      <c r="D77" s="31"/>
-      <c r="E77" s="31"/>
-      <c r="F77" s="31"/>
-      <c r="G77" s="31"/>
-      <c r="H77" s="31"/>
-      <c r="I77" s="31"/>
-      <c r="J77" s="31"/>
-      <c r="K77" s="31"/>
-      <c r="L77" s="31"/>
-      <c r="M77" s="31"/>
-    </row>
+      <c r="M46" s="44"/>
+    </row>
+    <row r="54" spans="3:11">
+      <c r="C54" s="60"/>
+      <c r="D54" s="60"/>
+      <c r="E54" s="60"/>
+      <c r="F54" s="60"/>
+      <c r="G54" s="60"/>
+      <c r="H54" s="60"/>
+      <c r="I54" s="60"/>
+      <c r="J54" s="60"/>
+      <c r="K54" s="60"/>
+    </row>
+    <row r="55" spans="3:11">
+      <c r="C55" s="60"/>
+      <c r="D55" s="61"/>
+      <c r="E55" s="61"/>
+      <c r="F55" s="61"/>
+      <c r="G55" s="61"/>
+      <c r="H55" s="61"/>
+      <c r="I55" s="61"/>
+      <c r="J55" s="61"/>
+      <c r="K55" s="61"/>
+    </row>
+    <row r="56" spans="3:11" ht="28.5" customHeight="1">
+      <c r="C56" s="89"/>
+      <c r="D56" s="89"/>
+      <c r="E56" s="89"/>
+      <c r="F56" s="89"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="89"/>
+      <c r="J56" s="89"/>
+      <c r="K56" s="89"/>
+    </row>
+    <row r="57" spans="3:11">
+      <c r="C57" s="89"/>
+      <c r="D57" s="89"/>
+      <c r="E57" s="89"/>
+      <c r="F57" s="89"/>
+      <c r="G57" s="68"/>
+      <c r="H57" s="68"/>
+      <c r="I57" s="89"/>
+      <c r="J57" s="89"/>
+      <c r="K57" s="89"/>
+    </row>
+    <row r="58" spans="3:11" ht="57" customHeight="1">
+      <c r="C58" s="89"/>
+      <c r="D58" s="89"/>
+      <c r="E58" s="89"/>
+      <c r="F58" s="89"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57"/>
+      <c r="I58" s="89"/>
+      <c r="J58" s="89"/>
+      <c r="K58" s="89"/>
+    </row>
+    <row r="59" spans="3:11">
+      <c r="C59" s="61"/>
+      <c r="D59" s="61"/>
+      <c r="E59" s="61"/>
+      <c r="F59" s="61"/>
+      <c r="G59" s="61"/>
+      <c r="H59" s="61"/>
+      <c r="I59" s="61"/>
+      <c r="J59" s="61"/>
+      <c r="K59" s="61"/>
+    </row>
+    <row r="60" spans="3:11">
+      <c r="C60" s="60"/>
+      <c r="D60" s="61"/>
+      <c r="E60" s="61"/>
+      <c r="F60" s="61"/>
+      <c r="G60" s="61"/>
+      <c r="H60" s="61"/>
+      <c r="I60" s="61"/>
+      <c r="J60" s="61"/>
+      <c r="K60" s="61"/>
+    </row>
+    <row r="61" spans="3:11">
+      <c r="C61" s="89"/>
+      <c r="D61" s="89"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="89"/>
+      <c r="G61" s="57"/>
+      <c r="H61" s="57"/>
+      <c r="I61" s="89"/>
+      <c r="J61" s="89"/>
+      <c r="K61" s="89"/>
+    </row>
+    <row r="62" spans="3:11">
+      <c r="C62" s="89"/>
+      <c r="D62" s="89"/>
+      <c r="E62" s="68"/>
+      <c r="F62" s="89"/>
+      <c r="G62" s="68"/>
+      <c r="H62" s="68"/>
+      <c r="I62" s="89"/>
+      <c r="J62" s="89"/>
+      <c r="K62" s="89"/>
+    </row>
+    <row r="63" spans="3:11">
+      <c r="C63" s="89"/>
+      <c r="D63" s="89"/>
+      <c r="E63" s="57"/>
+      <c r="F63" s="89"/>
+      <c r="G63" s="57"/>
+      <c r="H63" s="57"/>
+      <c r="I63" s="89"/>
+      <c r="J63" s="89"/>
+      <c r="K63" s="89"/>
+    </row>
+    <row r="64" spans="3:11">
+      <c r="C64" s="89"/>
+      <c r="D64" s="89"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="89"/>
+      <c r="G64" s="68"/>
+      <c r="H64" s="68"/>
+      <c r="I64" s="89"/>
+      <c r="J64" s="89"/>
+      <c r="K64" s="89"/>
+    </row>
+    <row r="65" spans="3:11">
+      <c r="C65" s="89"/>
+      <c r="D65" s="89"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="89"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="89"/>
+      <c r="J65" s="89"/>
+      <c r="K65" s="89"/>
+    </row>
+    <row r="66" spans="3:11" ht="28.5" customHeight="1">
+      <c r="C66" s="89"/>
+      <c r="D66" s="89"/>
+      <c r="E66" s="68"/>
+      <c r="F66" s="89"/>
+      <c r="G66" s="68"/>
+      <c r="H66" s="68"/>
+      <c r="I66" s="89"/>
+      <c r="J66" s="89"/>
+      <c r="K66" s="89"/>
+    </row>
+    <row r="67" spans="3:11">
+      <c r="C67" s="89"/>
+      <c r="D67" s="89"/>
+      <c r="E67" s="68"/>
+      <c r="F67" s="89"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="89"/>
+      <c r="J67" s="89"/>
+      <c r="K67" s="89"/>
+    </row>
+    <row r="68" spans="3:11" ht="40.5" customHeight="1">
+      <c r="C68" s="89"/>
+      <c r="D68" s="89"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="89"/>
+      <c r="G68" s="89"/>
+      <c r="H68" s="89"/>
+      <c r="I68" s="89"/>
+      <c r="J68" s="89"/>
+      <c r="K68" s="89"/>
+    </row>
+    <row r="69" spans="3:11" ht="28.5" customHeight="1">
+      <c r="C69" s="89"/>
+      <c r="D69" s="89"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="89"/>
+      <c r="G69" s="89"/>
+      <c r="H69" s="89"/>
+      <c r="I69" s="89"/>
+      <c r="J69" s="89"/>
+      <c r="K69" s="89"/>
+    </row>
+    <row r="70" spans="3:11">
+      <c r="C70" s="89"/>
+      <c r="D70" s="89"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="89"/>
+      <c r="G70" s="89"/>
+      <c r="H70" s="89"/>
+      <c r="I70" s="89"/>
+      <c r="J70" s="89"/>
+      <c r="K70" s="89"/>
+    </row>
+    <row r="71" spans="3:11" ht="42.75" customHeight="1">
+      <c r="C71" s="89"/>
+      <c r="D71" s="89"/>
+      <c r="E71" s="57"/>
+      <c r="F71" s="89"/>
+      <c r="G71" s="89"/>
+      <c r="H71" s="89"/>
+      <c r="I71" s="89"/>
+      <c r="J71" s="89"/>
+      <c r="K71" s="89"/>
+    </row>
+    <row r="72" spans="3:11" ht="28.5" customHeight="1">
+      <c r="C72" s="89"/>
+      <c r="D72" s="89"/>
+      <c r="E72" s="68"/>
+      <c r="F72" s="89"/>
+      <c r="G72" s="89"/>
+      <c r="H72" s="89"/>
+      <c r="I72" s="89"/>
+      <c r="J72" s="89"/>
+      <c r="K72" s="89"/>
+    </row>
+    <row r="73" spans="3:11">
+      <c r="C73" s="89"/>
+      <c r="D73" s="89"/>
+      <c r="E73" s="57"/>
+      <c r="F73" s="89"/>
+      <c r="G73" s="89"/>
+      <c r="H73" s="89"/>
+      <c r="I73" s="89"/>
+      <c r="J73" s="89"/>
+      <c r="K73" s="89"/>
+    </row>
+    <row r="74" spans="3:11" ht="42.75" customHeight="1">
+      <c r="C74" s="89"/>
+      <c r="D74" s="89"/>
+      <c r="E74" s="68"/>
+      <c r="F74" s="89"/>
+      <c r="G74" s="89"/>
+      <c r="H74" s="89"/>
+      <c r="I74" s="89"/>
+      <c r="J74" s="89"/>
+      <c r="K74" s="89"/>
+    </row>
+    <row r="75" spans="3:11">
+      <c r="C75" s="89"/>
+      <c r="D75" s="89"/>
+      <c r="E75" s="57"/>
+      <c r="F75" s="89"/>
+      <c r="G75" s="89"/>
+      <c r="H75" s="89"/>
+      <c r="I75" s="89"/>
+      <c r="J75" s="89"/>
+      <c r="K75" s="89"/>
+    </row>
+    <row r="77" spans="3:11" ht="28.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="B1:F1"/>
@@ -4736,393 +4391,395 @@
     <mergeCell ref="H68:H70"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R67"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.77734375" style="27" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" style="27" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" style="27" customWidth="1"/>
+    <col min="4" max="4" width="21.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5546875" style="27" customWidth="1"/>
+    <col min="6" max="6" width="28.77734375" style="27" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" style="27" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" style="27" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" style="27" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.21875" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="103"/>
-    </row>
-    <row r="2" spans="1:6" ht="23.25">
-      <c r="A2" s="9" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="95"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="92" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="106"/>
-    </row>
-    <row r="3" spans="1:6" ht="18.75">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11" t="s">
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="96"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="28"/>
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="28">
         <v>8</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="28">
         <v>1</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="28">
         <v>0</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="28">
         <v>0</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="28">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18.75">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="30">
         <v>9</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="28">
         <v>0</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="28">
         <v>0</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="28">
         <v>0</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="28">
         <f>B5</f>
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="17.25">
-      <c r="A31" s="101" t="s">
+    <row r="31" spans="1:13">
+      <c r="A31" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="101" t="s">
+      <c r="B31" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="101" t="s">
+      <c r="C31" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="101" t="s">
+      <c r="D31" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="102" t="s">
+      <c r="E31" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="101" t="s">
+      <c r="F31" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="107" t="s">
+      <c r="G31" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="107"/>
-      <c r="I31" s="107"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="107"/>
-      <c r="L31" s="107"/>
-      <c r="M31" s="108" t="s">
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="80"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="80"/>
+      <c r="M31" s="80" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="17.25">
-      <c r="A32" s="101"/>
-      <c r="B32" s="101"/>
-      <c r="C32" s="101"/>
-      <c r="D32" s="101"/>
-      <c r="E32" s="102"/>
-      <c r="F32" s="101"/>
-      <c r="G32" s="107" t="s">
+    <row r="32" spans="1:13">
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="107"/>
-      <c r="I32" s="107"/>
-      <c r="J32" s="107" t="s">
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="107"/>
-      <c r="L32" s="107"/>
-      <c r="M32" s="109"/>
-    </row>
-    <row r="33" spans="1:18" ht="16.5">
-      <c r="A33" s="101"/>
-      <c r="B33" s="101"/>
-      <c r="C33" s="101"/>
-      <c r="D33" s="101"/>
-      <c r="E33" s="102"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="15" t="s">
+      <c r="K32" s="80"/>
+      <c r="L32" s="80"/>
+      <c r="M32" s="81"/>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="I33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="J33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="15" t="s">
+      <c r="K33" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="15" t="s">
+      <c r="L33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="109"/>
-    </row>
-    <row r="34" spans="1:18" ht="17.25" thickBot="1">
-      <c r="A34" s="100" t="s">
+      <c r="M33" s="81"/>
+    </row>
+    <row r="34" spans="1:18" ht="17.399999999999999" thickBot="1">
+      <c r="A34" s="94" t="s">
         <v>334</v>
       </c>
-      <c r="B34" s="100"/>
-      <c r="C34" s="100"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="100"/>
-      <c r="G34" s="100"/>
-      <c r="H34" s="100"/>
-      <c r="I34" s="100"/>
-      <c r="J34" s="100"/>
-      <c r="K34" s="100"/>
-      <c r="L34" s="100"/>
-      <c r="M34" s="100"/>
-    </row>
-    <row r="35" spans="1:18" ht="43.5" thickBot="1">
-      <c r="A35" s="46" t="s">
+      <c r="B34" s="94"/>
+      <c r="C34" s="94"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="94"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="94"/>
+      <c r="J34" s="94"/>
+      <c r="K34" s="94"/>
+      <c r="L34" s="94"/>
+      <c r="M34" s="94"/>
+    </row>
+    <row r="35" spans="1:18" ht="51" thickBot="1">
+      <c r="A35" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="46" t="s">
+      <c r="B35" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46" t="s">
+      <c r="C35" s="47"/>
+      <c r="D35" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="E35" s="46" t="s">
+      <c r="E35" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="F35" s="46" t="s">
+      <c r="F35" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="G35" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="47">
+      <c r="G35" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="48">
         <v>46282</v>
       </c>
-      <c r="I35" s="46" t="s">
+      <c r="I35" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="J35" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="47">
+      <c r="J35" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="48">
         <v>46282</v>
       </c>
-      <c r="L35" s="46" t="s">
+      <c r="L35" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="M35" s="46"/>
-    </row>
-    <row r="36" spans="1:18" ht="43.5" thickBot="1">
-      <c r="A36" s="46" t="s">
+      <c r="M35" s="47"/>
+    </row>
+    <row r="36" spans="1:18" ht="51" thickBot="1">
+      <c r="A36" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46" t="s">
+      <c r="C36" s="47"/>
+      <c r="D36" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="E36" s="46" t="s">
+      <c r="E36" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="F36" s="46" t="s">
+      <c r="F36" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="G36" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="47">
+      <c r="G36" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="48">
         <v>46282</v>
       </c>
-      <c r="I36" s="46" t="s">
+      <c r="I36" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="J36" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="47">
+      <c r="J36" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="48">
         <v>46282</v>
       </c>
-      <c r="L36" s="46" t="s">
+      <c r="L36" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="M36" s="46"/>
-    </row>
-    <row r="37" spans="1:18" ht="57.75" thickBot="1">
-      <c r="A37" s="46" t="s">
+      <c r="M36" s="47"/>
+    </row>
+    <row r="37" spans="1:18" ht="67.8" thickBot="1">
+      <c r="A37" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="B37" s="46" t="s">
+      <c r="B37" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46" t="s">
+      <c r="C37" s="47"/>
+      <c r="D37" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="E37" s="46" t="s">
+      <c r="E37" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="F37" s="46" t="s">
+      <c r="F37" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="47">
+      <c r="G37" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="48">
         <v>46282</v>
       </c>
-      <c r="I37" s="46" t="s">
+      <c r="I37" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="J37" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" s="47">
+      <c r="J37" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="48">
         <v>46282</v>
       </c>
-      <c r="L37" s="46" t="s">
+      <c r="L37" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="M37" s="46"/>
-    </row>
-    <row r="38" spans="1:18" ht="43.5" thickBot="1">
-      <c r="A38" s="46" t="s">
+      <c r="M37" s="47"/>
+    </row>
+    <row r="38" spans="1:18" ht="67.8" thickBot="1">
+      <c r="A38" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="B38" s="46" t="s">
+      <c r="B38" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46" t="s">
+      <c r="C38" s="47"/>
+      <c r="D38" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="E38" s="46" t="s">
+      <c r="E38" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="F38" s="46" t="s">
+      <c r="F38" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="G38" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="47">
+      <c r="G38" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="48">
         <v>46282</v>
       </c>
-      <c r="I38" s="46" t="s">
+      <c r="I38" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="J38" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="47">
+      <c r="J38" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="48">
         <v>46282</v>
       </c>
-      <c r="L38" s="46" t="s">
+      <c r="L38" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="M38" s="46"/>
-    </row>
-    <row r="39" spans="1:18" ht="43.5" thickBot="1">
-      <c r="A39" s="46" t="s">
+      <c r="M38" s="47"/>
+    </row>
+    <row r="39" spans="1:18" ht="51" thickBot="1">
+      <c r="A39" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="B39" s="46" t="s">
+      <c r="B39" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46" t="s">
+      <c r="C39" s="47"/>
+      <c r="D39" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="E39" s="46" t="s">
+      <c r="E39" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="F39" s="46" t="s">
+      <c r="F39" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="G39" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="47">
+      <c r="G39" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="48">
         <v>46282</v>
       </c>
-      <c r="I39" s="46" t="s">
+      <c r="I39" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="J39" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="47">
+      <c r="J39" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="48">
         <v>46282</v>
       </c>
-      <c r="L39" s="46" t="s">
+      <c r="L39" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="M39" s="46"/>
-    </row>
-    <row r="40" spans="1:18" ht="17.25" thickBot="1">
+      <c r="M39" s="47"/>
+    </row>
+    <row r="40" spans="1:18" ht="17.399999999999999" thickBot="1">
       <c r="A40" s="49" t="s">
         <v>333</v>
       </c>
@@ -5141,462 +4798,462 @@
       <c r="N40" s="1"/>
     </row>
     <row r="41" spans="1:18" ht="77.25" customHeight="1" thickBot="1">
-      <c r="A41" s="48" t="s">
+      <c r="A41" s="52" t="s">
         <v>134</v>
       </c>
-      <c r="B41" s="48" t="s">
+      <c r="B41" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="C41" s="53" t="s">
+      <c r="C41" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="D41" s="48" t="s">
+      <c r="D41" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="E41" s="48" t="s">
+      <c r="E41" s="52" t="s">
         <v>137</v>
       </c>
-      <c r="F41" s="48" t="s">
+      <c r="F41" s="52" t="s">
         <v>138</v>
       </c>
-      <c r="G41" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="H41" s="52">
+      <c r="G41" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="53">
         <v>46282</v>
       </c>
-      <c r="I41" s="48" t="s">
+      <c r="I41" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="J41" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" s="52">
+      <c r="J41" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="53">
         <v>46282</v>
       </c>
-      <c r="L41" s="48" t="s">
+      <c r="L41" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="M41" s="48"/>
+      <c r="M41" s="52"/>
     </row>
     <row r="42" spans="1:18" ht="65.25" customHeight="1" thickBot="1">
-      <c r="A42" s="48" t="s">
+      <c r="A42" s="52" t="s">
         <v>139</v>
       </c>
-      <c r="B42" s="48" t="s">
+      <c r="B42" s="52" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="53" t="s">
+      <c r="C42" s="52" t="s">
         <v>156</v>
       </c>
-      <c r="D42" s="48" t="s">
+      <c r="D42" s="52" t="s">
         <v>141</v>
       </c>
-      <c r="E42" s="48" t="s">
+      <c r="E42" s="52" t="s">
         <v>142</v>
       </c>
-      <c r="F42" s="48" t="s">
+      <c r="F42" s="52" t="s">
         <v>143</v>
       </c>
-      <c r="G42" s="48" t="s">
+      <c r="G42" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="H42" s="52">
+      <c r="H42" s="53">
         <v>46282</v>
       </c>
-      <c r="I42" s="48" t="s">
+      <c r="I42" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="J42" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="K42" s="52">
+      <c r="J42" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="53">
         <v>46283</v>
       </c>
-      <c r="L42" s="48" t="s">
+      <c r="L42" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="M42" s="48" t="s">
+      <c r="M42" s="52" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="66" customHeight="1" thickBot="1">
-      <c r="A43" s="48" t="s">
+      <c r="A43" s="52" t="s">
         <v>145</v>
       </c>
-      <c r="B43" s="48" t="s">
+      <c r="B43" s="52" t="s">
         <v>146</v>
       </c>
-      <c r="C43" s="54" t="s">
+      <c r="C43" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="D43" s="48" t="s">
+      <c r="D43" s="52" t="s">
         <v>147</v>
       </c>
-      <c r="E43" s="48" t="s">
+      <c r="E43" s="52" t="s">
         <v>148</v>
       </c>
-      <c r="F43" s="48" t="s">
+      <c r="F43" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="G43" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" s="52">
+      <c r="G43" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="53">
         <v>46282</v>
       </c>
-      <c r="I43" s="48" t="s">
+      <c r="I43" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="J43" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="52">
+      <c r="J43" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="53">
         <v>46282</v>
       </c>
-      <c r="L43" s="48" t="s">
+      <c r="L43" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="M43" s="48"/>
+      <c r="M43" s="52"/>
     </row>
     <row r="44" spans="1:18" ht="58.5" customHeight="1">
-      <c r="A44" s="55" t="s">
+      <c r="A44" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="B44" s="55" t="s">
+      <c r="B44" s="54" t="s">
         <v>151</v>
       </c>
-      <c r="C44" s="55" t="s">
+      <c r="C44" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="D44" s="55" t="s">
+      <c r="D44" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="E44" s="55" t="s">
+      <c r="E44" s="54" t="s">
         <v>153</v>
       </c>
-      <c r="F44" s="55" t="s">
+      <c r="F44" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="G44" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" s="56">
+      <c r="G44" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="55">
         <v>46282</v>
       </c>
-      <c r="I44" s="55" t="s">
+      <c r="I44" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="J44" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="56">
+      <c r="J44" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="55">
         <v>46282</v>
       </c>
-      <c r="L44" s="55" t="s">
+      <c r="L44" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="M44" s="55"/>
+      <c r="M44" s="54"/>
     </row>
     <row r="48" spans="1:18">
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="22"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="22"/>
-      <c r="N48" s="22"/>
-      <c r="O48" s="22"/>
-      <c r="P48" s="22"/>
-      <c r="Q48" s="22"/>
-      <c r="R48" s="22"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="56"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="56"/>
+      <c r="J48" s="56"/>
+      <c r="K48" s="56"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="56"/>
+      <c r="N48" s="56"/>
+      <c r="O48" s="56"/>
+      <c r="P48" s="56"/>
+      <c r="Q48" s="56"/>
+      <c r="R48" s="56"/>
     </row>
     <row r="49" spans="6:18">
-      <c r="F49" s="22"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="23"/>
-      <c r="O49" s="23"/>
-      <c r="P49" s="23"/>
-      <c r="Q49" s="23"/>
-      <c r="R49" s="23"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="57"/>
+      <c r="K49" s="57"/>
+      <c r="L49" s="57"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="57"/>
+      <c r="O49" s="57"/>
+      <c r="P49" s="57"/>
+      <c r="Q49" s="57"/>
+      <c r="R49" s="57"/>
     </row>
     <row r="50" spans="6:18">
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="23"/>
-      <c r="J50" s="23"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="23"/>
-      <c r="M50" s="57"/>
-      <c r="N50" s="23"/>
-      <c r="O50" s="23"/>
-      <c r="P50" s="57"/>
-      <c r="Q50" s="23"/>
-      <c r="R50" s="23"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="57"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="57"/>
+      <c r="J50" s="57"/>
+      <c r="K50" s="57"/>
+      <c r="L50" s="57"/>
+      <c r="M50" s="58"/>
+      <c r="N50" s="57"/>
+      <c r="O50" s="57"/>
+      <c r="P50" s="58"/>
+      <c r="Q50" s="57"/>
+      <c r="R50" s="57"/>
     </row>
     <row r="51" spans="6:18">
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="23"/>
-      <c r="J51" s="23"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="23"/>
-      <c r="M51" s="57"/>
-      <c r="N51" s="23"/>
-      <c r="O51" s="23"/>
-      <c r="P51" s="57"/>
-      <c r="Q51" s="23"/>
-      <c r="R51" s="23"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="57"/>
+      <c r="L51" s="57"/>
+      <c r="M51" s="58"/>
+      <c r="N51" s="57"/>
+      <c r="O51" s="57"/>
+      <c r="P51" s="58"/>
+      <c r="Q51" s="57"/>
+      <c r="R51" s="57"/>
     </row>
     <row r="52" spans="6:18">
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
-      <c r="J52" s="23"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="23"/>
-      <c r="M52" s="57"/>
-      <c r="N52" s="23"/>
-      <c r="O52" s="23"/>
-      <c r="P52" s="57"/>
-      <c r="Q52" s="23"/>
-      <c r="R52" s="23"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="57"/>
+      <c r="K52" s="57"/>
+      <c r="L52" s="57"/>
+      <c r="M52" s="58"/>
+      <c r="N52" s="57"/>
+      <c r="O52" s="57"/>
+      <c r="P52" s="58"/>
+      <c r="Q52" s="57"/>
+      <c r="R52" s="57"/>
     </row>
     <row r="53" spans="6:18">
-      <c r="F53" s="23"/>
-      <c r="G53" s="23"/>
-      <c r="H53" s="23"/>
-      <c r="I53" s="23"/>
-      <c r="J53" s="23"/>
-      <c r="K53" s="23"/>
-      <c r="L53" s="23"/>
-      <c r="M53" s="57"/>
-      <c r="N53" s="23"/>
-      <c r="O53" s="23"/>
-      <c r="P53" s="57"/>
-      <c r="Q53" s="23"/>
-      <c r="R53" s="23"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="57"/>
+      <c r="K53" s="57"/>
+      <c r="L53" s="57"/>
+      <c r="M53" s="58"/>
+      <c r="N53" s="57"/>
+      <c r="O53" s="57"/>
+      <c r="P53" s="58"/>
+      <c r="Q53" s="57"/>
+      <c r="R53" s="57"/>
     </row>
     <row r="54" spans="6:18">
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="23"/>
-      <c r="J54" s="23"/>
-      <c r="K54" s="23"/>
-      <c r="L54" s="23"/>
-      <c r="M54" s="57"/>
-      <c r="N54" s="23"/>
-      <c r="O54" s="23"/>
-      <c r="P54" s="57"/>
-      <c r="Q54" s="23"/>
-      <c r="R54" s="23"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="57"/>
+      <c r="H54" s="57"/>
+      <c r="I54" s="57"/>
+      <c r="J54" s="57"/>
+      <c r="K54" s="57"/>
+      <c r="L54" s="57"/>
+      <c r="M54" s="58"/>
+      <c r="N54" s="57"/>
+      <c r="O54" s="57"/>
+      <c r="P54" s="58"/>
+      <c r="Q54" s="57"/>
+      <c r="R54" s="57"/>
     </row>
     <row r="55" spans="6:18">
-      <c r="F55" s="22"/>
-      <c r="G55" s="23"/>
-      <c r="H55" s="23"/>
-      <c r="I55" s="23"/>
-      <c r="J55" s="23"/>
-      <c r="K55" s="23"/>
-      <c r="L55" s="23"/>
-      <c r="M55" s="23"/>
-      <c r="N55" s="23"/>
-      <c r="O55" s="23"/>
-      <c r="P55" s="23"/>
-      <c r="Q55" s="23"/>
-      <c r="R55" s="23"/>
+      <c r="F55" s="56"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="57"/>
+      <c r="L55" s="57"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="57"/>
+      <c r="O55" s="57"/>
+      <c r="P55" s="57"/>
+      <c r="Q55" s="57"/>
+      <c r="R55" s="57"/>
     </row>
     <row r="56" spans="6:18" ht="84" customHeight="1">
-      <c r="F56" s="110"/>
-      <c r="G56" s="110"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="110"/>
-      <c r="J56" s="110"/>
-      <c r="K56" s="110"/>
-      <c r="L56" s="110"/>
-      <c r="M56" s="111"/>
-      <c r="N56" s="110"/>
-      <c r="O56" s="110"/>
-      <c r="P56" s="111"/>
-      <c r="Q56" s="110"/>
-      <c r="R56" s="110"/>
+      <c r="F56" s="97"/>
+      <c r="G56" s="97"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="97"/>
+      <c r="J56" s="97"/>
+      <c r="K56" s="97"/>
+      <c r="L56" s="97"/>
+      <c r="M56" s="98"/>
+      <c r="N56" s="97"/>
+      <c r="O56" s="97"/>
+      <c r="P56" s="98"/>
+      <c r="Q56" s="97"/>
+      <c r="R56" s="97"/>
     </row>
     <row r="57" spans="6:18">
-      <c r="F57" s="110"/>
-      <c r="G57" s="110"/>
-      <c r="H57" s="58"/>
-      <c r="I57" s="110"/>
-      <c r="J57" s="110"/>
-      <c r="K57" s="110"/>
-      <c r="L57" s="110"/>
-      <c r="M57" s="111"/>
-      <c r="N57" s="110"/>
-      <c r="O57" s="110"/>
-      <c r="P57" s="111"/>
-      <c r="Q57" s="110"/>
-      <c r="R57" s="110"/>
+      <c r="F57" s="97"/>
+      <c r="G57" s="97"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="97"/>
+      <c r="J57" s="97"/>
+      <c r="K57" s="97"/>
+      <c r="L57" s="97"/>
+      <c r="M57" s="98"/>
+      <c r="N57" s="97"/>
+      <c r="O57" s="97"/>
+      <c r="P57" s="98"/>
+      <c r="Q57" s="97"/>
+      <c r="R57" s="97"/>
     </row>
     <row r="58" spans="6:18">
-      <c r="F58" s="110"/>
-      <c r="G58" s="110"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="110"/>
-      <c r="J58" s="110"/>
-      <c r="K58" s="110"/>
-      <c r="L58" s="110"/>
-      <c r="M58" s="111"/>
-      <c r="N58" s="110"/>
-      <c r="O58" s="110"/>
-      <c r="P58" s="111"/>
-      <c r="Q58" s="110"/>
-      <c r="R58" s="110"/>
+      <c r="F58" s="97"/>
+      <c r="G58" s="97"/>
+      <c r="H58" s="57"/>
+      <c r="I58" s="97"/>
+      <c r="J58" s="97"/>
+      <c r="K58" s="97"/>
+      <c r="L58" s="97"/>
+      <c r="M58" s="98"/>
+      <c r="N58" s="97"/>
+      <c r="O58" s="97"/>
+      <c r="P58" s="98"/>
+      <c r="Q58" s="97"/>
+      <c r="R58" s="97"/>
     </row>
     <row r="59" spans="6:18" ht="55.5" customHeight="1">
-      <c r="F59" s="110"/>
-      <c r="G59" s="110"/>
-      <c r="H59" s="23"/>
-      <c r="I59" s="110"/>
-      <c r="J59" s="110"/>
-      <c r="K59" s="110"/>
-      <c r="L59" s="110"/>
-      <c r="M59" s="111"/>
-      <c r="N59" s="110"/>
-      <c r="O59" s="110"/>
-      <c r="P59" s="111"/>
-      <c r="Q59" s="110"/>
-      <c r="R59" s="110"/>
+      <c r="F59" s="97"/>
+      <c r="G59" s="97"/>
+      <c r="H59" s="57"/>
+      <c r="I59" s="97"/>
+      <c r="J59" s="97"/>
+      <c r="K59" s="97"/>
+      <c r="L59" s="97"/>
+      <c r="M59" s="98"/>
+      <c r="N59" s="97"/>
+      <c r="O59" s="97"/>
+      <c r="P59" s="98"/>
+      <c r="Q59" s="97"/>
+      <c r="R59" s="97"/>
     </row>
     <row r="60" spans="6:18">
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="58"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="110"/>
-      <c r="L60" s="110"/>
-      <c r="M60" s="111"/>
-      <c r="N60" s="110"/>
-      <c r="O60" s="110"/>
-      <c r="P60" s="111"/>
-      <c r="Q60" s="110"/>
-      <c r="R60" s="110"/>
+      <c r="F60" s="97"/>
+      <c r="G60" s="97"/>
+      <c r="H60" s="59"/>
+      <c r="I60" s="97"/>
+      <c r="J60" s="97"/>
+      <c r="K60" s="97"/>
+      <c r="L60" s="97"/>
+      <c r="M60" s="98"/>
+      <c r="N60" s="97"/>
+      <c r="O60" s="97"/>
+      <c r="P60" s="98"/>
+      <c r="Q60" s="97"/>
+      <c r="R60" s="97"/>
     </row>
     <row r="61" spans="6:18">
-      <c r="F61" s="110"/>
-      <c r="G61" s="110"/>
-      <c r="H61" s="23"/>
-      <c r="I61" s="110"/>
-      <c r="J61" s="110"/>
-      <c r="K61" s="110"/>
-      <c r="L61" s="110"/>
-      <c r="M61" s="111"/>
-      <c r="N61" s="110"/>
-      <c r="O61" s="110"/>
-      <c r="P61" s="111"/>
-      <c r="Q61" s="110"/>
-      <c r="R61" s="110"/>
+      <c r="F61" s="97"/>
+      <c r="G61" s="97"/>
+      <c r="H61" s="57"/>
+      <c r="I61" s="97"/>
+      <c r="J61" s="97"/>
+      <c r="K61" s="97"/>
+      <c r="L61" s="97"/>
+      <c r="M61" s="98"/>
+      <c r="N61" s="97"/>
+      <c r="O61" s="97"/>
+      <c r="P61" s="98"/>
+      <c r="Q61" s="97"/>
+      <c r="R61" s="97"/>
     </row>
     <row r="62" spans="6:18" ht="84" customHeight="1">
-      <c r="F62" s="110"/>
-      <c r="G62" s="110"/>
-      <c r="H62" s="23"/>
-      <c r="I62" s="110"/>
-      <c r="J62" s="110"/>
-      <c r="K62" s="110"/>
-      <c r="L62" s="110"/>
-      <c r="M62" s="111"/>
-      <c r="N62" s="110"/>
-      <c r="O62" s="110"/>
-      <c r="P62" s="111"/>
-      <c r="Q62" s="110"/>
-      <c r="R62" s="110"/>
+      <c r="F62" s="97"/>
+      <c r="G62" s="97"/>
+      <c r="H62" s="57"/>
+      <c r="I62" s="97"/>
+      <c r="J62" s="97"/>
+      <c r="K62" s="97"/>
+      <c r="L62" s="97"/>
+      <c r="M62" s="98"/>
+      <c r="N62" s="97"/>
+      <c r="O62" s="97"/>
+      <c r="P62" s="98"/>
+      <c r="Q62" s="97"/>
+      <c r="R62" s="97"/>
     </row>
     <row r="63" spans="6:18">
-      <c r="F63" s="110"/>
-      <c r="G63" s="110"/>
-      <c r="H63" s="58"/>
-      <c r="I63" s="110"/>
-      <c r="J63" s="110"/>
-      <c r="K63" s="110"/>
-      <c r="L63" s="110"/>
-      <c r="M63" s="111"/>
-      <c r="N63" s="110"/>
-      <c r="O63" s="110"/>
-      <c r="P63" s="111"/>
-      <c r="Q63" s="110"/>
-      <c r="R63" s="110"/>
+      <c r="F63" s="97"/>
+      <c r="G63" s="97"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="97"/>
+      <c r="J63" s="97"/>
+      <c r="K63" s="97"/>
+      <c r="L63" s="97"/>
+      <c r="M63" s="98"/>
+      <c r="N63" s="97"/>
+      <c r="O63" s="97"/>
+      <c r="P63" s="98"/>
+      <c r="Q63" s="97"/>
+      <c r="R63" s="97"/>
     </row>
     <row r="64" spans="6:18">
-      <c r="F64" s="110"/>
-      <c r="G64" s="110"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="110"/>
-      <c r="J64" s="110"/>
-      <c r="K64" s="110"/>
-      <c r="L64" s="110"/>
-      <c r="M64" s="111"/>
-      <c r="N64" s="110"/>
-      <c r="O64" s="110"/>
-      <c r="P64" s="111"/>
-      <c r="Q64" s="110"/>
-      <c r="R64" s="110"/>
+      <c r="F64" s="97"/>
+      <c r="G64" s="97"/>
+      <c r="H64" s="57"/>
+      <c r="I64" s="97"/>
+      <c r="J64" s="97"/>
+      <c r="K64" s="97"/>
+      <c r="L64" s="97"/>
+      <c r="M64" s="98"/>
+      <c r="N64" s="97"/>
+      <c r="O64" s="97"/>
+      <c r="P64" s="98"/>
+      <c r="Q64" s="97"/>
+      <c r="R64" s="97"/>
     </row>
     <row r="65" spans="6:18" ht="69.75" customHeight="1">
-      <c r="F65" s="110"/>
-      <c r="G65" s="110"/>
-      <c r="H65" s="23"/>
-      <c r="I65" s="110"/>
-      <c r="J65" s="110"/>
-      <c r="K65" s="110"/>
-      <c r="L65" s="110"/>
-      <c r="M65" s="111"/>
-      <c r="N65" s="110"/>
-      <c r="O65" s="110"/>
-      <c r="P65" s="111"/>
-      <c r="Q65" s="110"/>
-      <c r="R65" s="110"/>
+      <c r="F65" s="97"/>
+      <c r="G65" s="97"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="97"/>
+      <c r="J65" s="97"/>
+      <c r="K65" s="97"/>
+      <c r="L65" s="97"/>
+      <c r="M65" s="98"/>
+      <c r="N65" s="97"/>
+      <c r="O65" s="97"/>
+      <c r="P65" s="98"/>
+      <c r="Q65" s="97"/>
+      <c r="R65" s="97"/>
     </row>
     <row r="66" spans="6:18">
-      <c r="F66" s="110"/>
-      <c r="G66" s="110"/>
-      <c r="H66" s="58"/>
-      <c r="I66" s="110"/>
-      <c r="J66" s="110"/>
-      <c r="K66" s="110"/>
-      <c r="L66" s="110"/>
-      <c r="M66" s="111"/>
-      <c r="N66" s="110"/>
-      <c r="O66" s="110"/>
-      <c r="P66" s="111"/>
-      <c r="Q66" s="110"/>
-      <c r="R66" s="110"/>
+      <c r="F66" s="97"/>
+      <c r="G66" s="97"/>
+      <c r="H66" s="59"/>
+      <c r="I66" s="97"/>
+      <c r="J66" s="97"/>
+      <c r="K66" s="97"/>
+      <c r="L66" s="97"/>
+      <c r="M66" s="98"/>
+      <c r="N66" s="97"/>
+      <c r="O66" s="97"/>
+      <c r="P66" s="98"/>
+      <c r="Q66" s="97"/>
+      <c r="R66" s="97"/>
     </row>
     <row r="67" spans="6:18">
-      <c r="F67" s="110"/>
-      <c r="G67" s="110"/>
-      <c r="H67" s="23"/>
-      <c r="I67" s="110"/>
-      <c r="J67" s="110"/>
-      <c r="K67" s="110"/>
-      <c r="L67" s="110"/>
-      <c r="M67" s="111"/>
-      <c r="N67" s="110"/>
-      <c r="O67" s="110"/>
-      <c r="P67" s="111"/>
-      <c r="Q67" s="110"/>
-      <c r="R67" s="110"/>
+      <c r="F67" s="97"/>
+      <c r="G67" s="97"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="97"/>
+      <c r="J67" s="97"/>
+      <c r="K67" s="97"/>
+      <c r="L67" s="97"/>
+      <c r="M67" s="98"/>
+      <c r="N67" s="97"/>
+      <c r="O67" s="97"/>
+      <c r="P67" s="98"/>
+      <c r="Q67" s="97"/>
+      <c r="R67" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="61">
@@ -5663,345 +5320,347 @@
     <mergeCell ref="E31:E33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N44"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.77734375" style="27" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" style="27" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" style="27" customWidth="1"/>
+    <col min="4" max="4" width="21.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5546875" style="27" customWidth="1"/>
+    <col min="6" max="6" width="28.77734375" style="27" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" style="27" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" style="27" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" style="27" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.21875" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="91" t="s">
+      <c r="B1" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-    </row>
-    <row r="2" spans="1:6" ht="23.25">
-      <c r="A2" s="9" t="s">
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-    </row>
-    <row r="3" spans="1:6" ht="18.75">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11" t="s">
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="28"/>
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="28">
         <v>3</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="28">
         <v>0</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="28">
         <v>0</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="28">
         <v>0</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="28">
         <f>B4</f>
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18.75">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="30">
         <v>3</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="30">
         <v>0</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="30">
         <v>0</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="30">
         <v>0</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="28">
         <f>B5</f>
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="114.75" customHeight="1"/>
     <row r="30" spans="1:13" ht="118.5" customHeight="1"/>
-    <row r="31" spans="1:13" ht="17.25">
-      <c r="A31" s="115" t="s">
+    <row r="31" spans="1:13">
+      <c r="A31" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="115" t="s">
+      <c r="B31" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="115" t="s">
+      <c r="C31" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="115" t="s">
+      <c r="D31" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="116" t="s">
+      <c r="E31" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="115" t="s">
+      <c r="F31" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="107" t="s">
+      <c r="G31" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="107"/>
-      <c r="I31" s="107"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="107"/>
-      <c r="L31" s="107"/>
-      <c r="M31" s="108" t="s">
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="80"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="80"/>
+      <c r="M31" s="80" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="17.25">
-      <c r="A32" s="115"/>
-      <c r="B32" s="115"/>
-      <c r="C32" s="115"/>
-      <c r="D32" s="115"/>
-      <c r="E32" s="116"/>
-      <c r="F32" s="115"/>
-      <c r="G32" s="107" t="s">
+    <row r="32" spans="1:13">
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="107"/>
-      <c r="I32" s="107"/>
-      <c r="J32" s="107" t="s">
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="107"/>
-      <c r="L32" s="107"/>
-      <c r="M32" s="121"/>
-    </row>
-    <row r="33" spans="1:14" ht="15.75">
-      <c r="A33" s="115"/>
-      <c r="B33" s="115"/>
-      <c r="C33" s="115"/>
-      <c r="D33" s="115"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="115"/>
-      <c r="G33" s="17" t="s">
+      <c r="K32" s="80"/>
+      <c r="L32" s="80"/>
+      <c r="M32" s="81"/>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="18" t="s">
+      <c r="H33" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="17" t="s">
+      <c r="J33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="17" t="s">
+      <c r="K33" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="17" t="s">
+      <c r="L33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="121"/>
-    </row>
-    <row r="34" spans="1:14" ht="15.75">
-      <c r="A34" s="117" t="s">
+      <c r="M33" s="81"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="102" t="s">
         <v>268</v>
       </c>
-      <c r="B34" s="118"/>
-      <c r="C34" s="118"/>
-      <c r="D34" s="118"/>
-      <c r="E34" s="118"/>
-      <c r="F34" s="118"/>
-      <c r="G34" s="118"/>
-      <c r="H34" s="118"/>
-      <c r="I34" s="118"/>
-      <c r="J34" s="118"/>
-      <c r="K34" s="118"/>
-      <c r="L34" s="118"/>
-      <c r="M34" s="119"/>
-    </row>
-    <row r="35" spans="1:14" ht="115.5">
-      <c r="A35" s="3" t="s">
+      <c r="B34" s="103"/>
+      <c r="C34" s="103"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
+      <c r="J34" s="103"/>
+      <c r="K34" s="103"/>
+      <c r="L34" s="103"/>
+      <c r="M34" s="104"/>
+    </row>
+    <row r="35" spans="1:14" ht="117.6">
+      <c r="A35" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="C35" s="81" t="s">
+      <c r="C35" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="D35" s="74" t="s">
+      <c r="D35" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="33" t="s">
         <v>255</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="6">
+      <c r="G35" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="35">
         <v>46283</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="I35" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="J35" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="6">
+      <c r="J35" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="35">
         <v>46283</v>
       </c>
-      <c r="L35" s="7" t="s">
+      <c r="L35" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="M35" s="8"/>
-    </row>
-    <row r="36" spans="1:14" ht="16.5">
-      <c r="A36" s="112" t="s">
+      <c r="M35" s="37"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="99" t="s">
         <v>269</v>
       </c>
-      <c r="B36" s="113"/>
-      <c r="C36" s="113"/>
-      <c r="D36" s="113"/>
-      <c r="E36" s="113"/>
-      <c r="F36" s="113"/>
-      <c r="G36" s="113"/>
-      <c r="H36" s="113"/>
-      <c r="I36" s="113"/>
-      <c r="J36" s="113"/>
-      <c r="K36" s="113"/>
-      <c r="L36" s="113"/>
-      <c r="M36" s="114"/>
-    </row>
-    <row r="37" spans="1:14" ht="99">
-      <c r="A37" s="4" t="s">
+      <c r="B36" s="100"/>
+      <c r="C36" s="100"/>
+      <c r="D36" s="100"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="100"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="100"/>
+      <c r="J36" s="100"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="101"/>
+    </row>
+    <row r="37" spans="1:14" ht="100.8">
+      <c r="A37" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="33" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="33" t="s">
         <v>267</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="33" t="s">
         <v>258</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="6">
+      <c r="G37" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="35">
         <v>46283</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="I37" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="J37" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" s="6">
+      <c r="J37" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="35">
         <v>46283</v>
       </c>
-      <c r="L37" s="7" t="s">
+      <c r="L37" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="M37" s="8"/>
+      <c r="M37" s="37"/>
     </row>
     <row r="38" spans="1:14" ht="112.5" customHeight="1">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="33" t="s">
         <v>261</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="33" t="s">
         <v>263</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="33" t="s">
         <v>264</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="38" t="s">
         <v>265</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="38" t="s">
         <v>266</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="6">
+      <c r="G38" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="35">
         <v>46283</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="I38" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="J38" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="6">
+      <c r="J38" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="35">
         <v>46283</v>
       </c>
-      <c r="L38" s="7" t="s">
+      <c r="L38" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="M38" s="8"/>
-    </row>
-    <row r="39" spans="1:14" ht="16.5">
+      <c r="M38" s="37"/>
+    </row>
+    <row r="39" spans="1:14">
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="1:14" ht="179.25" customHeight="1"/>
@@ -6031,615 +5690,617 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N45"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
-    <col min="4" max="4" width="34.7109375" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.77734375" style="27" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" style="27" customWidth="1"/>
+    <col min="3" max="3" width="44" style="27" customWidth="1"/>
+    <col min="4" max="4" width="34.77734375" style="27" customWidth="1"/>
+    <col min="5" max="5" width="29.5546875" style="27" customWidth="1"/>
+    <col min="6" max="6" width="28.77734375" style="27" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" style="27" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" style="27" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" style="27" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.21875" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="91" t="s">
+      <c r="B1" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-    </row>
-    <row r="2" spans="1:6" ht="23.25">
-      <c r="A2" s="9" t="s">
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="86" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-    </row>
-    <row r="3" spans="1:6" ht="18.75">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11" t="s">
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="28"/>
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="28">
         <v>7</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="28">
         <v>1</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="28">
         <v>0</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="28">
         <v>0</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="28">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18.75">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="30">
         <v>8</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="28">
         <v>0</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="28">
         <v>0</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="28">
         <v>0</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="28">
         <f>B5</f>
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="75.75" customHeight="1"/>
-    <row r="31" spans="1:13" ht="19.5">
-      <c r="A31" s="93" t="s">
+    <row r="31" spans="1:13">
+      <c r="A31" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="93" t="s">
+      <c r="B31" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="93" t="s">
+      <c r="C31" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="93" t="s">
+      <c r="D31" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="94" t="s">
+      <c r="E31" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="93" t="s">
+      <c r="F31" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="124" t="s">
+      <c r="G31" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="124"/>
-      <c r="I31" s="124"/>
-      <c r="J31" s="124"/>
-      <c r="K31" s="124"/>
-      <c r="L31" s="124"/>
-      <c r="M31" s="124" t="s">
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="80"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="80"/>
+      <c r="M31" s="80" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="19.5">
-      <c r="A32" s="93"/>
-      <c r="B32" s="93"/>
-      <c r="C32" s="93"/>
-      <c r="D32" s="93"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="93"/>
-      <c r="G32" s="124" t="s">
+    <row r="32" spans="1:13">
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="124"/>
-      <c r="I32" s="124"/>
-      <c r="J32" s="124" t="s">
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="124"/>
-      <c r="L32" s="124"/>
-      <c r="M32" s="125"/>
-    </row>
-    <row r="33" spans="1:14" ht="19.5">
-      <c r="A33" s="93"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="93"/>
-      <c r="E33" s="94"/>
-      <c r="F33" s="93"/>
-      <c r="G33" s="59" t="s">
+      <c r="K32" s="80"/>
+      <c r="L32" s="80"/>
+      <c r="M32" s="81"/>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="38" t="s">
+      <c r="H33" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="59" t="s">
+      <c r="I33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="59" t="s">
+      <c r="J33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="59" t="s">
+      <c r="K33" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="59" t="s">
+      <c r="L33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="125"/>
-    </row>
-    <row r="34" spans="1:14" ht="19.5">
-      <c r="A34" s="123" t="s">
+      <c r="M33" s="81"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="94" t="s">
         <v>335</v>
       </c>
-      <c r="B34" s="123"/>
-      <c r="C34" s="123"/>
-      <c r="D34" s="123"/>
-      <c r="E34" s="123"/>
-      <c r="F34" s="123"/>
-      <c r="G34" s="123"/>
-      <c r="H34" s="123"/>
-      <c r="I34" s="123"/>
-      <c r="J34" s="123"/>
-      <c r="K34" s="123"/>
-      <c r="L34" s="123"/>
-      <c r="M34" s="123"/>
+      <c r="B34" s="94"/>
+      <c r="C34" s="94"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="94"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="94"/>
+      <c r="J34" s="94"/>
+      <c r="K34" s="94"/>
+      <c r="L34" s="94"/>
+      <c r="M34" s="94"/>
     </row>
     <row r="35" spans="1:14" ht="127.5" customHeight="1">
-      <c r="A35" s="62" t="s">
+      <c r="A35" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="B35" s="62" t="s">
+      <c r="B35" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C35" s="63" t="s">
+      <c r="C35" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="D35" s="63" t="s">
+      <c r="D35" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="E35" s="64" t="s">
+      <c r="E35" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="F35" s="64" t="s">
+      <c r="F35" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="G35" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="66">
+      <c r="G35" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="35">
         <v>46283</v>
       </c>
-      <c r="I35" s="67" t="s">
+      <c r="I35" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="J35" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="66">
+      <c r="J35" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="35">
         <v>46283</v>
       </c>
-      <c r="L35" s="67" t="s">
+      <c r="L35" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="M35" s="68"/>
+      <c r="M35" s="37"/>
     </row>
     <row r="36" spans="1:14" ht="96" customHeight="1">
-      <c r="A36" s="62" t="s">
+      <c r="A36" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="B36" s="62" t="s">
+      <c r="B36" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="C36" s="63" t="s">
+      <c r="C36" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="D36" s="70" t="s">
+      <c r="D36" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="E36" s="64" t="s">
+      <c r="E36" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="F36" s="64" t="s">
+      <c r="F36" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="G36" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="66">
+      <c r="G36" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="35">
         <v>46283</v>
       </c>
-      <c r="I36" s="67" t="s">
+      <c r="I36" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="J36" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="66">
+      <c r="J36" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="35">
         <v>46283</v>
       </c>
-      <c r="L36" s="67" t="s">
+      <c r="L36" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="M36" s="68"/>
-    </row>
-    <row r="37" spans="1:14" ht="78">
-      <c r="A37" s="62" t="s">
+      <c r="M36" s="37"/>
+    </row>
+    <row r="37" spans="1:14" ht="50.4">
+      <c r="A37" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="B37" s="62" t="s">
+      <c r="B37" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="C37" s="70" t="s">
+      <c r="C37" s="45" t="s">
         <v>173</v>
       </c>
-      <c r="D37" s="69" t="s">
+      <c r="D37" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="E37" s="64" t="s">
+      <c r="E37" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="F37" s="64" t="s">
+      <c r="F37" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="G37" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="66">
+      <c r="G37" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="35">
         <v>46283</v>
       </c>
-      <c r="I37" s="67" t="s">
+      <c r="I37" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="J37" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" s="66">
+      <c r="J37" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="35">
         <v>46283</v>
       </c>
-      <c r="L37" s="67" t="s">
+      <c r="L37" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="M37" s="68"/>
+      <c r="M37" s="37"/>
     </row>
     <row r="38" spans="1:14" ht="120.75" customHeight="1">
-      <c r="A38" s="62" t="s">
+      <c r="A38" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="B38" s="62" t="s">
+      <c r="B38" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="C38" s="70" t="s">
+      <c r="C38" s="45" t="s">
         <v>179</v>
       </c>
-      <c r="D38" s="71" t="s">
+      <c r="D38" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="E38" s="64" t="s">
+      <c r="E38" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="F38" s="64" t="s">
+      <c r="F38" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="G38" s="65" t="s">
+      <c r="G38" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="H38" s="66">
+      <c r="H38" s="35">
         <v>46283</v>
       </c>
-      <c r="I38" s="67" t="s">
+      <c r="I38" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="J38" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="66">
+      <c r="J38" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="35">
         <v>46283</v>
       </c>
-      <c r="L38" s="67" t="s">
+      <c r="L38" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="M38" s="68"/>
-    </row>
-    <row r="39" spans="1:14" ht="19.5">
-      <c r="A39" s="122" t="s">
+      <c r="M38" s="37"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="105" t="s">
         <v>336</v>
       </c>
-      <c r="B39" s="122"/>
-      <c r="C39" s="122"/>
-      <c r="D39" s="122"/>
-      <c r="E39" s="122"/>
-      <c r="F39" s="122"/>
-      <c r="G39" s="122"/>
-      <c r="H39" s="122"/>
-      <c r="I39" s="122"/>
-      <c r="J39" s="122"/>
-      <c r="K39" s="122"/>
-      <c r="L39" s="122"/>
-      <c r="M39" s="122"/>
+      <c r="B39" s="105"/>
+      <c r="C39" s="105"/>
+      <c r="D39" s="105"/>
+      <c r="E39" s="105"/>
+      <c r="F39" s="105"/>
+      <c r="G39" s="105"/>
+      <c r="H39" s="105"/>
+      <c r="I39" s="105"/>
+      <c r="J39" s="105"/>
+      <c r="K39" s="105"/>
+      <c r="L39" s="105"/>
+      <c r="M39" s="105"/>
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="1:14" ht="198" customHeight="1">
-      <c r="A40" s="64" t="s">
+      <c r="A40" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="B40" s="64" t="s">
+      <c r="B40" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="C40" s="64" t="s">
+      <c r="C40" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="D40" s="64" t="s">
+      <c r="D40" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="E40" s="63" t="s">
+      <c r="E40" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="F40" s="63" t="s">
+      <c r="F40" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="G40" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="66">
+      <c r="G40" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="35">
         <v>46283</v>
       </c>
-      <c r="I40" s="67" t="s">
+      <c r="I40" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="J40" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="66">
+      <c r="J40" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="35">
         <v>46283</v>
       </c>
-      <c r="L40" s="67" t="s">
+      <c r="L40" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="M40" s="68"/>
+      <c r="M40" s="37"/>
     </row>
     <row r="41" spans="1:14" ht="230.25" customHeight="1">
-      <c r="A41" s="64" t="s">
+      <c r="A41" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="64" t="s">
+      <c r="C41" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="D41" s="64" t="s">
+      <c r="D41" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="E41" s="63" t="s">
+      <c r="E41" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="F41" s="63" t="s">
+      <c r="F41" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="G41" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H41" s="66">
+      <c r="G41" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="35">
         <v>46283</v>
       </c>
-      <c r="I41" s="67" t="s">
+      <c r="I41" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="J41" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" s="66">
+      <c r="J41" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="35">
         <v>46283</v>
       </c>
-      <c r="L41" s="67" t="s">
+      <c r="L41" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="M41" s="68"/>
+      <c r="M41" s="37"/>
     </row>
     <row r="42" spans="1:14" ht="234" customHeight="1">
-      <c r="A42" s="64" t="s">
+      <c r="A42" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="B42" s="64" t="s">
+      <c r="B42" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="C42" s="64" t="s">
+      <c r="C42" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="D42" s="64" t="s">
+      <c r="D42" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="E42" s="63" t="s">
+      <c r="E42" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="F42" s="63" t="s">
+      <c r="F42" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="G42" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H42" s="66">
+      <c r="G42" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="35">
         <v>46283</v>
       </c>
-      <c r="I42" s="67" t="s">
+      <c r="I42" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="J42" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K42" s="66">
+      <c r="J42" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="35">
         <v>46283</v>
       </c>
-      <c r="L42" s="67" t="s">
+      <c r="L42" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="M42" s="68"/>
+      <c r="M42" s="37"/>
     </row>
     <row r="43" spans="1:14" ht="218.25" customHeight="1">
-      <c r="A43" s="64" t="s">
+      <c r="A43" s="33" t="s">
         <v>199</v>
       </c>
-      <c r="B43" s="64" t="s">
+      <c r="B43" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="C43" s="64" t="s">
+      <c r="C43" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="D43" s="64" t="s">
+      <c r="D43" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="E43" s="63" t="s">
+      <c r="E43" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="F43" s="63" t="s">
+      <c r="F43" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="G43" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" s="66">
+      <c r="G43" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="35">
         <v>46283</v>
       </c>
-      <c r="I43" s="67" t="s">
+      <c r="I43" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="J43" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="66">
+      <c r="J43" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="35">
         <v>46283</v>
       </c>
-      <c r="L43" s="67" t="s">
+      <c r="L43" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="M43" s="68"/>
+      <c r="M43" s="37"/>
     </row>
     <row r="44" spans="1:14" ht="248.25" customHeight="1">
-      <c r="A44" s="64" t="s">
+      <c r="A44" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="B44" s="64" t="s">
+      <c r="B44" s="33" t="s">
         <v>206</v>
       </c>
-      <c r="C44" s="64" t="s">
+      <c r="C44" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D44" s="64" t="s">
+      <c r="D44" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="E44" s="63" t="s">
+      <c r="E44" s="38" t="s">
         <v>209</v>
       </c>
-      <c r="F44" s="63" t="s">
+      <c r="F44" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="G44" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" s="66">
+      <c r="G44" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="35">
         <v>46283</v>
       </c>
-      <c r="I44" s="67" t="s">
+      <c r="I44" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="J44" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="66">
+      <c r="J44" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="35">
         <v>46283</v>
       </c>
-      <c r="L44" s="67" t="s">
+      <c r="L44" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="M44" s="68"/>
-    </row>
-    <row r="45" spans="1:14" ht="156">
-      <c r="A45" s="64" t="s">
+      <c r="M44" s="37"/>
+    </row>
+    <row r="45" spans="1:14" ht="100.8">
+      <c r="A45" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="B45" s="64" t="s">
+      <c r="B45" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="C45" s="73" t="s">
+      <c r="C45" s="46" t="s">
         <v>213</v>
       </c>
-      <c r="D45" s="73" t="s">
+      <c r="D45" s="46" t="s">
         <v>214</v>
       </c>
-      <c r="E45" s="72" t="s">
+      <c r="E45" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="F45" s="72" t="s">
+      <c r="F45" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="G45" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="66">
+      <c r="G45" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="35">
         <v>46283</v>
       </c>
-      <c r="I45" s="67" t="s">
+      <c r="I45" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="J45" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K45" s="66">
+      <c r="J45" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" s="35">
         <v>46283</v>
       </c>
-      <c r="L45" s="67" t="s">
+      <c r="L45" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="M45" s="68"/>
+      <c r="M45" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -6665,7 +6326,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6673,446 +6334,443 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N42"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.77734375" style="27" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" style="27" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" style="27" customWidth="1"/>
+    <col min="4" max="4" width="21.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5546875" style="27" customWidth="1"/>
+    <col min="6" max="6" width="28.77734375" style="27" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" style="27" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" style="27" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" style="27" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.21875" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="91" t="s">
+      <c r="B1" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-    </row>
-    <row r="2" spans="1:6" ht="23.25">
-      <c r="A2" s="9" t="s">
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-    </row>
-    <row r="3" spans="1:6" ht="18.75">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11" t="s">
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="28"/>
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="28">
         <v>5</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="28">
         <v>0</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="28">
         <v>0</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="28">
         <v>0</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="28">
         <f>B4</f>
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18.75">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="30">
         <v>5</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="30">
         <v>0</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="30">
         <v>0</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="30">
         <v>0</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="28">
         <f>B5</f>
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="330.75" customHeight="1"/>
     <row r="30" spans="1:13" ht="171" customHeight="1"/>
-    <row r="31" spans="1:13" ht="17.25">
-      <c r="A31" s="115" t="s">
+    <row r="31" spans="1:13">
+      <c r="A31" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="115" t="s">
+      <c r="B31" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="115" t="s">
+      <c r="C31" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="115" t="s">
+      <c r="D31" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="116" t="s">
+      <c r="E31" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="115" t="s">
+      <c r="F31" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="107" t="s">
+      <c r="G31" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="107"/>
-      <c r="I31" s="107"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="107"/>
-      <c r="L31" s="107"/>
-      <c r="M31" s="108" t="s">
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="80"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="80"/>
+      <c r="M31" s="80" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="17.25">
-      <c r="A32" s="115"/>
-      <c r="B32" s="115"/>
-      <c r="C32" s="115"/>
-      <c r="D32" s="115"/>
-      <c r="E32" s="116"/>
-      <c r="F32" s="115"/>
-      <c r="G32" s="107" t="s">
+    <row r="32" spans="1:13">
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="107"/>
-      <c r="I32" s="107"/>
-      <c r="J32" s="107" t="s">
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="107"/>
-      <c r="L32" s="107"/>
-      <c r="M32" s="121"/>
-    </row>
-    <row r="33" spans="1:14" ht="15.75">
-      <c r="A33" s="115"/>
-      <c r="B33" s="115"/>
-      <c r="C33" s="115"/>
-      <c r="D33" s="115"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="115"/>
-      <c r="G33" s="17" t="s">
+      <c r="K32" s="80"/>
+      <c r="L32" s="80"/>
+      <c r="M32" s="81"/>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="18" t="s">
+      <c r="H33" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="17" t="s">
+      <c r="J33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="17" t="s">
+      <c r="K33" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="17" t="s">
+      <c r="L33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="121"/>
+      <c r="M33" s="81"/>
     </row>
     <row r="34" spans="1:14" ht="38.25" customHeight="1">
-      <c r="A34" s="117" t="s">
+      <c r="A34" s="102" t="s">
         <v>219</v>
       </c>
-      <c r="B34" s="118"/>
-      <c r="C34" s="118"/>
-      <c r="D34" s="118"/>
-      <c r="E34" s="118"/>
-      <c r="F34" s="118"/>
-      <c r="G34" s="118"/>
-      <c r="H34" s="118"/>
-      <c r="I34" s="118"/>
-      <c r="J34" s="118"/>
-      <c r="K34" s="118"/>
-      <c r="L34" s="118"/>
-      <c r="M34" s="119"/>
-    </row>
-    <row r="35" spans="1:14" ht="99">
-      <c r="A35" s="3" t="s">
+      <c r="B34" s="103"/>
+      <c r="C34" s="103"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
+      <c r="J34" s="103"/>
+      <c r="K34" s="103"/>
+      <c r="L34" s="103"/>
+      <c r="M34" s="104"/>
+    </row>
+    <row r="35" spans="1:14" ht="100.8">
+      <c r="A35" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="C35" s="74" t="s">
+      <c r="C35" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="D35" s="74" t="s">
+      <c r="D35" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="33" t="s">
         <v>221</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="G35" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="66">
+      <c r="G35" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="35">
         <v>46283</v>
       </c>
-      <c r="I35" s="67" t="s">
+      <c r="I35" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="J35" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="66">
+      <c r="J35" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="35">
         <v>46283</v>
       </c>
-      <c r="L35" s="67" t="s">
+      <c r="L35" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="M35" s="8"/>
-    </row>
-    <row r="36" spans="1:14" ht="82.5">
-      <c r="A36" s="3" t="s">
+      <c r="M35" s="37"/>
+    </row>
+    <row r="36" spans="1:14" ht="84">
+      <c r="A36" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="C36" s="74" t="s">
+      <c r="C36" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="D36" s="74" t="s">
+      <c r="D36" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="33" t="s">
         <v>229</v>
       </c>
-      <c r="G36" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="66">
+      <c r="G36" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="35">
         <v>46283</v>
       </c>
-      <c r="I36" s="67" t="s">
+      <c r="I36" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="J36" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="66">
+      <c r="J36" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="35">
         <v>46283</v>
       </c>
-      <c r="L36" s="67" t="s">
+      <c r="L36" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="M36" s="8"/>
-    </row>
-    <row r="37" spans="1:14" ht="99">
-      <c r="A37" s="3" t="s">
+      <c r="M36" s="37"/>
+    </row>
+    <row r="37" spans="1:14" ht="100.8">
+      <c r="A37" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="C37" s="74" t="s">
+      <c r="C37" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="D37" s="61" t="s">
+      <c r="D37" s="37" t="s">
         <v>233</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="33" t="s">
         <v>234</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="33" t="s">
         <v>235</v>
       </c>
-      <c r="G37" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="66">
+      <c r="G37" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="35">
         <v>46283</v>
       </c>
-      <c r="I37" s="67" t="s">
+      <c r="I37" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="J37" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" s="66">
+      <c r="J37" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="35">
         <v>46283</v>
       </c>
-      <c r="L37" s="67" t="s">
+      <c r="L37" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="M37" s="8"/>
+      <c r="M37" s="37"/>
     </row>
     <row r="38" spans="1:14" ht="50.25" customHeight="1">
-      <c r="A38" s="126" t="s">
+      <c r="A38" s="82" t="s">
         <v>236</v>
       </c>
-      <c r="B38" s="127"/>
-      <c r="C38" s="127"/>
-      <c r="D38" s="127"/>
-      <c r="E38" s="127"/>
-      <c r="F38" s="127"/>
-      <c r="G38" s="127"/>
-      <c r="H38" s="127"/>
-      <c r="I38" s="127"/>
-      <c r="J38" s="127"/>
-      <c r="K38" s="127"/>
-      <c r="L38" s="127"/>
-      <c r="M38" s="128"/>
+      <c r="B38" s="83"/>
+      <c r="C38" s="83"/>
+      <c r="D38" s="83"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="83"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="83"/>
+      <c r="K38" s="83"/>
+      <c r="L38" s="83"/>
+      <c r="M38" s="84"/>
       <c r="N38" s="1"/>
     </row>
     <row r="39" spans="1:14" ht="193.5" customHeight="1">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="33" t="s">
         <v>237</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="33" t="s">
         <v>239</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="33" t="s">
         <v>240</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="33" t="s">
         <v>241</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="G39" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="66">
+      <c r="G39" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="35">
         <v>46283</v>
       </c>
-      <c r="I39" s="67" t="s">
+      <c r="I39" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="J39" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="66">
+      <c r="J39" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="35">
         <v>46283</v>
       </c>
-      <c r="L39" s="67" t="s">
+      <c r="L39" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="M39" s="8"/>
+      <c r="M39" s="37"/>
     </row>
     <row r="40" spans="1:14" ht="168.75" customHeight="1">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="33" t="s">
         <v>238</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="33" t="s">
         <v>244</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="33" t="s">
         <v>245</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="38" t="s">
         <v>246</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="38" t="s">
         <v>247</v>
       </c>
-      <c r="G40" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="66">
+      <c r="G40" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="35">
         <v>46283</v>
       </c>
-      <c r="I40" s="67" t="s">
+      <c r="I40" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="J40" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="66">
+      <c r="J40" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="35">
         <v>46283</v>
       </c>
-      <c r="L40" s="67" t="s">
+      <c r="L40" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="M40" s="8"/>
+      <c r="M40" s="37"/>
     </row>
     <row r="41" spans="1:14" ht="168.75" customHeight="1">
-      <c r="A41" s="31"/>
-      <c r="B41" s="76"/>
-      <c r="D41" s="75"/>
-      <c r="E41" s="75"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="77"/>
-      <c r="I41" s="78"/>
-      <c r="J41" s="79"/>
-      <c r="K41" s="77"/>
-      <c r="L41" s="78"/>
-      <c r="M41" s="79"/>
-      <c r="N41" s="80"/>
+      <c r="B41" s="39"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="41"/>
+      <c r="L41" s="42"/>
+      <c r="M41" s="43"/>
     </row>
     <row r="42" spans="1:14" ht="171" customHeight="1">
-      <c r="A42" s="31"/>
-      <c r="B42" s="75"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="75"/>
-      <c r="E42" s="75"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="78"/>
-      <c r="J42" s="79"/>
-      <c r="K42" s="77"/>
-      <c r="L42" s="78"/>
-      <c r="M42" s="79"/>
-      <c r="N42" s="80"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="41"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -7138,132 +6796,134 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.77734375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" style="15" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" style="15" customWidth="1"/>
+    <col min="4" max="4" width="21.21875" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5546875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="28.77734375" style="15" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" style="15" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" style="15" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" style="15" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" style="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.21875" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="91" t="s">
+      <c r="B1" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-    </row>
-    <row r="2" spans="1:6" ht="23.25">
-      <c r="A2" s="9" t="s">
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="106" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-    </row>
-    <row r="3" spans="1:6" ht="18.75">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="16">
         <v>5</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="16">
         <v>0</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="16">
         <v>0</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="16">
         <v>0</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="16">
         <f>B4</f>
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18.75">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="24">
         <v>5</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="24">
         <v>0</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="24">
         <v>0</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="24">
         <v>0</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="16">
         <f>B5</f>
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="84.75" customHeight="1"/>
-    <row r="31" spans="1:13" ht="17.25">
-      <c r="A31" s="115" t="s">
+    <row r="31" spans="1:13">
+      <c r="A31" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="115" t="s">
+      <c r="B31" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="115" t="s">
+      <c r="C31" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="115" t="s">
+      <c r="D31" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="116" t="s">
+      <c r="E31" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="115" t="s">
+      <c r="F31" s="87" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="107" t="s">
@@ -7274,17 +6934,17 @@
       <c r="J31" s="107"/>
       <c r="K31" s="107"/>
       <c r="L31" s="107"/>
-      <c r="M31" s="108" t="s">
+      <c r="M31" s="107" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="17.25">
-      <c r="A32" s="115"/>
-      <c r="B32" s="115"/>
-      <c r="C32" s="115"/>
-      <c r="D32" s="115"/>
-      <c r="E32" s="116"/>
-      <c r="F32" s="115"/>
+    <row r="32" spans="1:13">
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="87"/>
       <c r="G32" s="107" t="s">
         <v>20</v>
       </c>
@@ -7295,63 +6955,63 @@
       </c>
       <c r="K32" s="107"/>
       <c r="L32" s="107"/>
-      <c r="M32" s="121"/>
-    </row>
-    <row r="33" spans="1:14" ht="15.75">
-      <c r="A33" s="115"/>
-      <c r="B33" s="115"/>
-      <c r="C33" s="115"/>
-      <c r="D33" s="115"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="115"/>
-      <c r="G33" s="17" t="s">
+      <c r="M32" s="108"/>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="18" t="s">
+      <c r="H33" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="17" t="s">
+      <c r="J33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="17" t="s">
+      <c r="K33" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="17" t="s">
+      <c r="L33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="121"/>
-    </row>
-    <row r="34" spans="1:14" ht="15.75">
-      <c r="A34" s="130" t="s">
+      <c r="M33" s="108"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="94" t="s">
         <v>299</v>
       </c>
-      <c r="B34" s="130"/>
-      <c r="C34" s="130"/>
-      <c r="D34" s="130"/>
-      <c r="E34" s="130"/>
-      <c r="F34" s="130"/>
-      <c r="G34" s="130"/>
-      <c r="H34" s="130"/>
-      <c r="I34" s="130"/>
-      <c r="J34" s="130"/>
-      <c r="K34" s="130"/>
-      <c r="L34" s="130"/>
-      <c r="M34" s="130"/>
-    </row>
-    <row r="35" spans="1:14" ht="82.5">
+      <c r="B34" s="94"/>
+      <c r="C34" s="94"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="94"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="94"/>
+      <c r="J34" s="94"/>
+      <c r="K34" s="94"/>
+      <c r="L34" s="94"/>
+      <c r="M34" s="94"/>
+    </row>
+    <row r="35" spans="1:14" ht="84">
       <c r="A35" s="3" t="s">
         <v>270</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C35" s="81" t="s">
+      <c r="C35" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="D35" s="74" t="s">
+      <c r="D35" s="12" t="s">
         <v>272</v>
       </c>
       <c r="E35" s="4" t="s">
@@ -7360,37 +7020,37 @@
       <c r="F35" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="G35" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="66">
+      <c r="G35" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="6">
         <v>46283</v>
       </c>
-      <c r="I35" s="67" t="s">
+      <c r="I35" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J35" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="66">
+      <c r="J35" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="6">
         <v>46283</v>
       </c>
-      <c r="L35" s="67" t="s">
+      <c r="L35" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="M35" s="8"/>
-    </row>
-    <row r="36" spans="1:14" ht="66">
+      <c r="M35" s="25"/>
+    </row>
+    <row r="36" spans="1:14" ht="67.2">
       <c r="A36" s="3" t="s">
         <v>276</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C36" s="74" t="s">
+      <c r="C36" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="D36" s="74" t="s">
+      <c r="D36" s="12" t="s">
         <v>279</v>
       </c>
       <c r="E36" s="4" t="s">
@@ -7399,42 +7059,42 @@
       <c r="F36" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="G36" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="66">
+      <c r="G36" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="6">
         <v>46283</v>
       </c>
-      <c r="I36" s="67" t="s">
+      <c r="I36" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="J36" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="66">
+      <c r="J36" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="6">
         <v>46283</v>
       </c>
-      <c r="L36" s="67" t="s">
+      <c r="L36" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="M36" s="8"/>
-    </row>
-    <row r="37" spans="1:14" ht="16.5">
-      <c r="A37" s="129" t="s">
+      <c r="M36" s="25"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="105" t="s">
         <v>300</v>
       </c>
-      <c r="B37" s="129"/>
-      <c r="C37" s="129"/>
-      <c r="D37" s="129"/>
-      <c r="E37" s="129"/>
-      <c r="F37" s="129"/>
-      <c r="G37" s="129"/>
-      <c r="H37" s="129"/>
-      <c r="I37" s="129"/>
-      <c r="J37" s="129"/>
-      <c r="K37" s="129"/>
-      <c r="L37" s="129"/>
-      <c r="M37" s="129"/>
+      <c r="B37" s="105"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="105"/>
+      <c r="F37" s="105"/>
+      <c r="G37" s="105"/>
+      <c r="H37" s="105"/>
+      <c r="I37" s="105"/>
+      <c r="J37" s="105"/>
+      <c r="K37" s="105"/>
+      <c r="L37" s="105"/>
+      <c r="M37" s="105"/>
       <c r="N37" s="1"/>
     </row>
     <row r="38" spans="1:14" ht="186" customHeight="1">
@@ -7456,25 +7116,25 @@
       <c r="F38" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="G38" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="66">
+      <c r="G38" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="6">
         <v>46283</v>
       </c>
-      <c r="I38" s="67" t="s">
+      <c r="I38" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J38" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="66">
+      <c r="J38" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="6">
         <v>46283</v>
       </c>
-      <c r="L38" s="67" t="s">
+      <c r="L38" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="M38" s="8"/>
+      <c r="M38" s="25"/>
     </row>
     <row r="39" spans="1:14" ht="134.25" customHeight="1">
       <c r="A39" s="4" t="s">
@@ -7495,25 +7155,25 @@
       <c r="F39" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="G39" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="66">
+      <c r="G39" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="6">
         <v>46283</v>
       </c>
-      <c r="I39" s="67" t="s">
+      <c r="I39" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="J39" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="66">
+      <c r="J39" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="6">
         <v>46283</v>
       </c>
-      <c r="L39" s="67" t="s">
+      <c r="L39" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="M39" s="8"/>
+      <c r="M39" s="25"/>
     </row>
     <row r="40" spans="1:14" ht="156" customHeight="1">
       <c r="A40" s="4" t="s">
@@ -7534,25 +7194,25 @@
       <c r="F40" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G40" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="66">
+      <c r="G40" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="6">
         <v>46283</v>
       </c>
-      <c r="I40" s="67" t="s">
+      <c r="I40" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="J40" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="66">
+      <c r="J40" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="6">
         <v>46283</v>
       </c>
-      <c r="L40" s="67" t="s">
+      <c r="L40" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="M40" s="8"/>
+      <c r="M40" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -7578,6 +7238,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/BaoCao_Final/9.2.TestCaseSprint2.xlsx
+++ b/BaoCao_Final/9.2.TestCaseSprint2.xlsx
@@ -3229,7 +3229,7 @@
         <v>17</v>
       </c>
       <c r="H23" s="67">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="I23" s="65" t="s">
         <v>63</v>
@@ -3238,7 +3238,7 @@
         <v>17</v>
       </c>
       <c r="K23" s="67">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="L23" s="65" t="s">
         <v>63</v>
@@ -3268,7 +3268,7 @@
         <v>17</v>
       </c>
       <c r="H24" s="67">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="I24" s="65" t="s">
         <v>63</v>
@@ -3277,7 +3277,7 @@
         <v>17</v>
       </c>
       <c r="K24" s="67">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="L24" s="65" t="s">
         <v>63</v>
@@ -3307,7 +3307,7 @@
         <v>17</v>
       </c>
       <c r="H25" s="67">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="I25" s="65" t="s">
         <v>63</v>
@@ -3316,7 +3316,7 @@
         <v>17</v>
       </c>
       <c r="K25" s="67">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="L25" s="65" t="s">
         <v>63</v>
@@ -3363,7 +3363,7 @@
         <v>17</v>
       </c>
       <c r="H27" s="67">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="I27" s="65" t="s">
         <v>63</v>
@@ -3372,7 +3372,7 @@
         <v>17</v>
       </c>
       <c r="K27" s="67">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="L27" s="65" t="s">
         <v>63</v>
@@ -3402,7 +3402,7 @@
         <v>17</v>
       </c>
       <c r="H28" s="67">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="I28" s="65" t="s">
         <v>52</v>
@@ -3411,7 +3411,7 @@
         <v>17</v>
       </c>
       <c r="K28" s="67">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="L28" s="65" t="s">
         <v>52</v>
@@ -3688,7 +3688,7 @@
         <v>17</v>
       </c>
       <c r="H35" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="I35" s="65" t="s">
         <v>63</v>
@@ -3697,7 +3697,7 @@
         <v>17</v>
       </c>
       <c r="K35" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="L35" s="65" t="s">
         <v>63</v>
@@ -3725,7 +3725,7 @@
         <v>17</v>
       </c>
       <c r="H36" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="I36" s="65" t="s">
         <v>63</v>
@@ -3734,7 +3734,7 @@
         <v>17</v>
       </c>
       <c r="K36" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="L36" s="65" t="s">
         <v>63</v>
@@ -3762,7 +3762,7 @@
         <v>17</v>
       </c>
       <c r="H37" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="I37" s="65" t="s">
         <v>63</v>
@@ -3771,7 +3771,7 @@
         <v>17</v>
       </c>
       <c r="K37" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="L37" s="65" t="s">
         <v>63</v>
@@ -3799,7 +3799,7 @@
         <v>17</v>
       </c>
       <c r="H38" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="I38" s="65" t="s">
         <v>63</v>
@@ -3808,7 +3808,7 @@
         <v>17</v>
       </c>
       <c r="K38" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="L38" s="65" t="s">
         <v>63</v>
@@ -3836,7 +3836,7 @@
         <v>17</v>
       </c>
       <c r="H39" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="I39" s="65" t="s">
         <v>63</v>
@@ -3845,7 +3845,7 @@
         <v>17</v>
       </c>
       <c r="K39" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="L39" s="65" t="s">
         <v>63</v>
@@ -3873,7 +3873,7 @@
         <v>17</v>
       </c>
       <c r="H40" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="I40" s="65" t="s">
         <v>52</v>
@@ -3882,7 +3882,7 @@
         <v>17</v>
       </c>
       <c r="K40" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="L40" s="65" t="s">
         <v>52</v>
@@ -3910,7 +3910,7 @@
         <v>80</v>
       </c>
       <c r="H41" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="I41" s="65" t="s">
         <v>52</v>
@@ -3919,7 +3919,7 @@
         <v>17</v>
       </c>
       <c r="K41" s="67">
-        <v>46283</v>
+        <v>46269</v>
       </c>
       <c r="L41" s="65" t="s">
         <v>52</v>
@@ -3969,7 +3969,7 @@
         <v>17</v>
       </c>
       <c r="H43" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="I43" s="65" t="s">
         <v>63</v>
@@ -3978,7 +3978,7 @@
         <v>17</v>
       </c>
       <c r="K43" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="L43" s="65" t="s">
         <v>63</v>
@@ -4008,7 +4008,7 @@
         <v>17</v>
       </c>
       <c r="H44" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="I44" s="65" t="s">
         <v>52</v>
@@ -4017,7 +4017,7 @@
         <v>17</v>
       </c>
       <c r="K44" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="L44" s="65" t="s">
         <v>52</v>
@@ -4047,7 +4047,7 @@
         <v>17</v>
       </c>
       <c r="H45" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="I45" s="65" t="s">
         <v>52</v>
@@ -4056,7 +4056,7 @@
         <v>17</v>
       </c>
       <c r="K45" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="L45" s="65" t="s">
         <v>52</v>
@@ -4086,7 +4086,7 @@
         <v>17</v>
       </c>
       <c r="H46" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="I46" s="65" t="s">
         <v>63</v>
@@ -4095,7 +4095,7 @@
         <v>17</v>
       </c>
       <c r="K46" s="67">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="L46" s="65" t="s">
         <v>63</v>
@@ -4615,7 +4615,7 @@
         <v>17</v>
       </c>
       <c r="H35" s="48">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="I35" s="47" t="s">
         <v>114</v>
@@ -4624,7 +4624,7 @@
         <v>17</v>
       </c>
       <c r="K35" s="48">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="L35" s="47" t="s">
         <v>114</v>
@@ -4652,7 +4652,7 @@
         <v>17</v>
       </c>
       <c r="H36" s="48">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="I36" s="47" t="s">
         <v>114</v>
@@ -4661,7 +4661,7 @@
         <v>17</v>
       </c>
       <c r="K36" s="48">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="L36" s="47" t="s">
         <v>114</v>
@@ -4689,7 +4689,7 @@
         <v>17</v>
       </c>
       <c r="H37" s="48">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="I37" s="47" t="s">
         <v>63</v>
@@ -4698,7 +4698,7 @@
         <v>17</v>
       </c>
       <c r="K37" s="48">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="L37" s="47" t="s">
         <v>63</v>
@@ -4726,7 +4726,7 @@
         <v>17</v>
       </c>
       <c r="H38" s="48">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="I38" s="47" t="s">
         <v>63</v>
@@ -4735,7 +4735,7 @@
         <v>17</v>
       </c>
       <c r="K38" s="48">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="L38" s="47" t="s">
         <v>63</v>
@@ -4763,7 +4763,7 @@
         <v>17</v>
       </c>
       <c r="H39" s="48">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="I39" s="47" t="s">
         <v>114</v>
@@ -4772,7 +4772,7 @@
         <v>17</v>
       </c>
       <c r="K39" s="48">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="L39" s="47" t="s">
         <v>114</v>
@@ -4820,7 +4820,7 @@
         <v>17</v>
       </c>
       <c r="H41" s="53">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="I41" s="52" t="s">
         <v>63</v>
@@ -4829,7 +4829,7 @@
         <v>17</v>
       </c>
       <c r="K41" s="53">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="L41" s="52" t="s">
         <v>63</v>
@@ -4859,7 +4859,7 @@
         <v>80</v>
       </c>
       <c r="H42" s="53">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="I42" s="52" t="s">
         <v>114</v>
@@ -4868,7 +4868,7 @@
         <v>17</v>
       </c>
       <c r="K42" s="53">
-        <v>46283</v>
+        <v>46271</v>
       </c>
       <c r="L42" s="52" t="s">
         <v>114</v>
@@ -4900,7 +4900,7 @@
         <v>17</v>
       </c>
       <c r="H43" s="53">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="I43" s="52" t="s">
         <v>63</v>
@@ -4909,7 +4909,7 @@
         <v>17</v>
       </c>
       <c r="K43" s="53">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="L43" s="52" t="s">
         <v>63</v>
@@ -4939,7 +4939,7 @@
         <v>17</v>
       </c>
       <c r="H44" s="55">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="I44" s="54" t="s">
         <v>114</v>
@@ -4948,7 +4948,7 @@
         <v>17</v>
       </c>
       <c r="K44" s="55">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="L44" s="54" t="s">
         <v>114</v>
@@ -5549,7 +5549,7 @@
         <v>17</v>
       </c>
       <c r="H35" s="35">
-        <v>46283</v>
+        <v>46277</v>
       </c>
       <c r="I35" s="36" t="s">
         <v>52</v>
@@ -5558,7 +5558,7 @@
         <v>17</v>
       </c>
       <c r="K35" s="35">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="L35" s="36" t="s">
         <v>52</v>
@@ -5605,7 +5605,7 @@
         <v>17</v>
       </c>
       <c r="H37" s="35">
-        <v>46283</v>
+        <v>46277</v>
       </c>
       <c r="I37" s="36" t="s">
         <v>114</v>
@@ -5614,7 +5614,7 @@
         <v>17</v>
       </c>
       <c r="K37" s="35">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="L37" s="36" t="s">
         <v>114</v>
@@ -5644,7 +5644,7 @@
         <v>17</v>
       </c>
       <c r="H38" s="35">
-        <v>46283</v>
+        <v>46277</v>
       </c>
       <c r="I38" s="36" t="s">
         <v>63</v>
@@ -5653,7 +5653,7 @@
         <v>17</v>
       </c>
       <c r="K38" s="35">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="L38" s="36" t="s">
         <v>63</v>
@@ -5917,7 +5917,7 @@
         <v>17</v>
       </c>
       <c r="H35" s="35">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="I35" s="36" t="s">
         <v>63</v>
@@ -5926,7 +5926,7 @@
         <v>17</v>
       </c>
       <c r="K35" s="35">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="L35" s="36" t="s">
         <v>63</v>
@@ -5956,7 +5956,7 @@
         <v>17</v>
       </c>
       <c r="H36" s="35">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="I36" s="36" t="s">
         <v>63</v>
@@ -5965,7 +5965,7 @@
         <v>17</v>
       </c>
       <c r="K36" s="35">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="L36" s="36" t="s">
         <v>63</v>
@@ -5995,7 +5995,7 @@
         <v>17</v>
       </c>
       <c r="H37" s="35">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="I37" s="36" t="s">
         <v>63</v>
@@ -6004,7 +6004,7 @@
         <v>17</v>
       </c>
       <c r="K37" s="35">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="L37" s="36" t="s">
         <v>63</v>
@@ -6034,7 +6034,7 @@
         <v>80</v>
       </c>
       <c r="H38" s="35">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="I38" s="36" t="s">
         <v>63</v>
@@ -6043,7 +6043,7 @@
         <v>17</v>
       </c>
       <c r="K38" s="35">
-        <v>46283</v>
+        <v>46274</v>
       </c>
       <c r="L38" s="36" t="s">
         <v>63</v>
@@ -6091,7 +6091,7 @@
         <v>17</v>
       </c>
       <c r="H40" s="35">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="I40" s="36" t="s">
         <v>52</v>
@@ -6100,7 +6100,7 @@
         <v>17</v>
       </c>
       <c r="K40" s="35">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="L40" s="36" t="s">
         <v>52</v>
@@ -6130,7 +6130,7 @@
         <v>17</v>
       </c>
       <c r="H41" s="35">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="I41" s="36" t="s">
         <v>52</v>
@@ -6139,7 +6139,7 @@
         <v>17</v>
       </c>
       <c r="K41" s="35">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="L41" s="36" t="s">
         <v>52</v>
@@ -6169,7 +6169,7 @@
         <v>17</v>
       </c>
       <c r="H42" s="35">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="I42" s="36" t="s">
         <v>63</v>
@@ -6178,7 +6178,7 @@
         <v>17</v>
       </c>
       <c r="K42" s="35">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="L42" s="36" t="s">
         <v>63</v>
@@ -6208,7 +6208,7 @@
         <v>17</v>
       </c>
       <c r="H43" s="35">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="I43" s="36" t="s">
         <v>114</v>
@@ -6217,7 +6217,7 @@
         <v>17</v>
       </c>
       <c r="K43" s="35">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="L43" s="36" t="s">
         <v>114</v>
@@ -6247,7 +6247,7 @@
         <v>17</v>
       </c>
       <c r="H44" s="35">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="I44" s="36" t="s">
         <v>114</v>
@@ -6256,7 +6256,7 @@
         <v>17</v>
       </c>
       <c r="K44" s="35">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="L44" s="36" t="s">
         <v>114</v>
@@ -6286,7 +6286,7 @@
         <v>17</v>
       </c>
       <c r="H45" s="35">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="I45" s="36" t="s">
         <v>114</v>
@@ -6295,7 +6295,7 @@
         <v>17</v>
       </c>
       <c r="K45" s="35">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="L45" s="36" t="s">
         <v>114</v>
@@ -6555,7 +6555,7 @@
         <v>17</v>
       </c>
       <c r="H35" s="35">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="I35" s="36" t="s">
         <v>63</v>
@@ -6564,7 +6564,7 @@
         <v>17</v>
       </c>
       <c r="K35" s="35">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="L35" s="36" t="s">
         <v>63</v>
@@ -6594,7 +6594,7 @@
         <v>17</v>
       </c>
       <c r="H36" s="35">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="I36" s="36" t="s">
         <v>63</v>
@@ -6603,7 +6603,7 @@
         <v>17</v>
       </c>
       <c r="K36" s="35">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="L36" s="36" t="s">
         <v>63</v>
@@ -6633,7 +6633,7 @@
         <v>17</v>
       </c>
       <c r="H37" s="35">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="I37" s="36" t="s">
         <v>52</v>
@@ -6642,7 +6642,7 @@
         <v>17</v>
       </c>
       <c r="K37" s="35">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="L37" s="36" t="s">
         <v>52</v>
@@ -6690,7 +6690,7 @@
         <v>17</v>
       </c>
       <c r="H39" s="35">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="I39" s="36" t="s">
         <v>52</v>
@@ -6699,7 +6699,7 @@
         <v>17</v>
       </c>
       <c r="K39" s="35">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="L39" s="36" t="s">
         <v>52</v>
@@ -6729,7 +6729,7 @@
         <v>17</v>
       </c>
       <c r="H40" s="35">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="I40" s="36" t="s">
         <v>114</v>
@@ -6738,7 +6738,7 @@
         <v>17</v>
       </c>
       <c r="K40" s="35">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="L40" s="36" t="s">
         <v>114</v>
@@ -7024,7 +7024,7 @@
         <v>17</v>
       </c>
       <c r="H35" s="6">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>63</v>
@@ -7033,7 +7033,7 @@
         <v>17</v>
       </c>
       <c r="K35" s="6">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>63</v>
@@ -7063,7 +7063,7 @@
         <v>17</v>
       </c>
       <c r="H36" s="6">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>52</v>
@@ -7072,7 +7072,7 @@
         <v>17</v>
       </c>
       <c r="K36" s="6">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="L36" s="7" t="s">
         <v>52</v>
@@ -7120,7 +7120,7 @@
         <v>17</v>
       </c>
       <c r="H38" s="6">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>63</v>
@@ -7129,7 +7129,7 @@
         <v>17</v>
       </c>
       <c r="K38" s="6">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="L38" s="7" t="s">
         <v>63</v>
@@ -7159,7 +7159,7 @@
         <v>17</v>
       </c>
       <c r="H39" s="6">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="I39" s="7" t="s">
         <v>52</v>
@@ -7168,7 +7168,7 @@
         <v>17</v>
       </c>
       <c r="K39" s="6">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="L39" s="7" t="s">
         <v>52</v>
@@ -7198,7 +7198,7 @@
         <v>17</v>
       </c>
       <c r="H40" s="6">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>52</v>
@@ -7207,7 +7207,7 @@
         <v>17</v>
       </c>
       <c r="K40" s="6">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="L40" s="7" t="s">
         <v>52</v>

--- a/BaoCao_Final/9.2.TestCaseSprint2.xlsx
+++ b/BaoCao_Final/9.2.TestCaseSprint2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="e:\Downloads\Document\BaoCao_Final(1)\BaoCao_Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AB2B08-F7EA-4FE5-B7CC-22CB70BADA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D0A980-714D-447D-9DA1-D6F917AD368A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="803" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1699,6 +1699,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1714,47 +1726,35 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3003,7 +3003,7 @@
     <mergeCell ref="A1:D2"/>
     <mergeCell ref="B3:D3"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
@@ -3033,25 +3033,25 @@
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="28"/>
@@ -3113,62 +3113,62 @@
     </row>
     <row r="18" spans="1:13" ht="300.75" customHeight="1"/>
     <row r="19" spans="1:13">
-      <c r="A19" s="87" t="s">
+      <c r="A19" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="87" t="s">
+      <c r="B19" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="87" t="s">
+      <c r="C19" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="87" t="s">
+      <c r="D19" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="88" t="s">
+      <c r="E19" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="87" t="s">
+      <c r="F19" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="80" t="s">
+      <c r="G19" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="80"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="80"/>
-      <c r="L19" s="80"/>
-      <c r="M19" s="80" t="s">
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="87"/>
-      <c r="B20" s="87"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="87"/>
-      <c r="G20" s="80" t="s">
+      <c r="A20" s="82"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="80"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80" t="s">
+      <c r="H20" s="84"/>
+      <c r="I20" s="84"/>
+      <c r="J20" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="K20" s="80"/>
-      <c r="L20" s="80"/>
-      <c r="M20" s="81"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="85"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="87"/>
-      <c r="B21" s="87"/>
-      <c r="C21" s="87"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="87"/>
+      <c r="A21" s="82"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="82"/>
       <c r="G21" s="8" t="s">
         <v>14</v>
       </c>
@@ -3187,7 +3187,7 @@
       <c r="L21" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M21" s="81"/>
+      <c r="M21" s="85"/>
     </row>
     <row r="22" spans="1:13" ht="17.399999999999999" thickBot="1">
       <c r="A22" s="19" t="s">
@@ -3324,21 +3324,21 @@
       <c r="M25" s="65"/>
     </row>
     <row r="26" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A26" s="82" t="s">
+      <c r="A26" s="86" t="s">
         <v>331</v>
       </c>
-      <c r="B26" s="83"/>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="83"/>
-      <c r="J26" s="83"/>
-      <c r="K26" s="83"/>
-      <c r="L26" s="83"/>
-      <c r="M26" s="84"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="87"/>
+      <c r="J26" s="87"/>
+      <c r="K26" s="87"/>
+      <c r="L26" s="87"/>
+      <c r="M26" s="88"/>
     </row>
     <row r="27" spans="1:13" ht="67.8" thickBot="1">
       <c r="A27" s="65" t="s">
@@ -3420,6 +3420,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="G19:L19"/>
+    <mergeCell ref="M19:M21"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="A26:M26"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A19:A21"/>
@@ -3428,13 +3433,8 @@
     <mergeCell ref="D19:D21"/>
     <mergeCell ref="E19:E21"/>
     <mergeCell ref="F19:F21"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="M19:M21"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="A26:M26"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -3465,13 +3465,13 @@
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
       <c r="H1" s="60"/>
       <c r="I1" s="60"/>
       <c r="J1" s="60"/>
@@ -3482,13 +3482,13 @@
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
       <c r="G2" s="60"/>
       <c r="H2" s="60"/>
       <c r="I2" s="61"/>
@@ -3574,62 +3574,62 @@
     </row>
     <row r="6" spans="1:12" ht="199.5" customHeight="1"/>
     <row r="31" spans="1:13" ht="42.75" customHeight="1">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="87" t="s">
+      <c r="B31" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="87" t="s">
+      <c r="C31" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="87" t="s">
+      <c r="D31" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="88" t="s">
+      <c r="E31" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="87" t="s">
+      <c r="F31" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="80" t="s">
+      <c r="G31" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="80"/>
-      <c r="M31" s="80" t="s">
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="87"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="87"/>
-      <c r="G32" s="80" t="s">
+      <c r="A32" s="82"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80" t="s">
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80"/>
-      <c r="M32" s="81"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="85"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="87"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="87"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="87"/>
+      <c r="A33" s="82"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="82"/>
       <c r="G33" s="8" t="s">
         <v>14</v>
       </c>
@@ -3648,7 +3648,7 @@
       <c r="L33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="81"/>
+      <c r="M33" s="85"/>
     </row>
     <row r="34" spans="1:14" ht="66.75" customHeight="1" thickBot="1">
       <c r="A34" s="19" t="s">
@@ -3929,21 +3929,21 @@
       </c>
     </row>
     <row r="42" spans="1:14" ht="17.399999999999999" thickBot="1">
-      <c r="A42" s="82" t="s">
+      <c r="A42" s="86" t="s">
         <v>332</v>
       </c>
-      <c r="B42" s="83"/>
-      <c r="C42" s="83"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83"/>
-      <c r="J42" s="83"/>
-      <c r="K42" s="83"/>
-      <c r="L42" s="83"/>
-      <c r="M42" s="84"/>
+      <c r="B42" s="87"/>
+      <c r="C42" s="87"/>
+      <c r="D42" s="87"/>
+      <c r="E42" s="87"/>
+      <c r="F42" s="87"/>
+      <c r="G42" s="87"/>
+      <c r="H42" s="87"/>
+      <c r="I42" s="87"/>
+      <c r="J42" s="87"/>
+      <c r="K42" s="87"/>
+      <c r="L42" s="87"/>
+      <c r="M42" s="88"/>
       <c r="N42" s="1"/>
     </row>
     <row r="43" spans="1:14" ht="127.5" customHeight="1" thickBot="1">
@@ -4125,37 +4125,37 @@
       <c r="K55" s="61"/>
     </row>
     <row r="56" spans="3:11" ht="28.5" customHeight="1">
-      <c r="C56" s="89"/>
-      <c r="D56" s="89"/>
-      <c r="E56" s="89"/>
-      <c r="F56" s="89"/>
+      <c r="C56" s="93"/>
+      <c r="D56" s="93"/>
+      <c r="E56" s="93"/>
+      <c r="F56" s="93"/>
       <c r="G56" s="57"/>
       <c r="H56" s="57"/>
-      <c r="I56" s="89"/>
-      <c r="J56" s="89"/>
-      <c r="K56" s="89"/>
+      <c r="I56" s="93"/>
+      <c r="J56" s="93"/>
+      <c r="K56" s="93"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="89"/>
-      <c r="D57" s="89"/>
-      <c r="E57" s="89"/>
-      <c r="F57" s="89"/>
+      <c r="C57" s="93"/>
+      <c r="D57" s="93"/>
+      <c r="E57" s="93"/>
+      <c r="F57" s="93"/>
       <c r="G57" s="68"/>
       <c r="H57" s="68"/>
-      <c r="I57" s="89"/>
-      <c r="J57" s="89"/>
-      <c r="K57" s="89"/>
+      <c r="I57" s="93"/>
+      <c r="J57" s="93"/>
+      <c r="K57" s="93"/>
     </row>
     <row r="58" spans="3:11" ht="57" customHeight="1">
-      <c r="C58" s="89"/>
-      <c r="D58" s="89"/>
-      <c r="E58" s="89"/>
-      <c r="F58" s="89"/>
+      <c r="C58" s="93"/>
+      <c r="D58" s="93"/>
+      <c r="E58" s="93"/>
+      <c r="F58" s="93"/>
       <c r="G58" s="57"/>
       <c r="H58" s="57"/>
-      <c r="I58" s="89"/>
-      <c r="J58" s="89"/>
-      <c r="K58" s="89"/>
+      <c r="I58" s="93"/>
+      <c r="J58" s="93"/>
+      <c r="K58" s="93"/>
     </row>
     <row r="59" spans="3:11">
       <c r="C59" s="61"/>
@@ -4180,199 +4180,173 @@
       <c r="K60" s="61"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="89"/>
-      <c r="D61" s="89"/>
+      <c r="C61" s="93"/>
+      <c r="D61" s="93"/>
       <c r="E61" s="57"/>
-      <c r="F61" s="89"/>
+      <c r="F61" s="93"/>
       <c r="G61" s="57"/>
       <c r="H61" s="57"/>
-      <c r="I61" s="89"/>
-      <c r="J61" s="89"/>
-      <c r="K61" s="89"/>
+      <c r="I61" s="93"/>
+      <c r="J61" s="93"/>
+      <c r="K61" s="93"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="89"/>
-      <c r="D62" s="89"/>
+      <c r="C62" s="93"/>
+      <c r="D62" s="93"/>
       <c r="E62" s="68"/>
-      <c r="F62" s="89"/>
+      <c r="F62" s="93"/>
       <c r="G62" s="68"/>
       <c r="H62" s="68"/>
-      <c r="I62" s="89"/>
-      <c r="J62" s="89"/>
-      <c r="K62" s="89"/>
+      <c r="I62" s="93"/>
+      <c r="J62" s="93"/>
+      <c r="K62" s="93"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="89"/>
-      <c r="D63" s="89"/>
+      <c r="C63" s="93"/>
+      <c r="D63" s="93"/>
       <c r="E63" s="57"/>
-      <c r="F63" s="89"/>
+      <c r="F63" s="93"/>
       <c r="G63" s="57"/>
       <c r="H63" s="57"/>
-      <c r="I63" s="89"/>
-      <c r="J63" s="89"/>
-      <c r="K63" s="89"/>
+      <c r="I63" s="93"/>
+      <c r="J63" s="93"/>
+      <c r="K63" s="93"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="89"/>
-      <c r="D64" s="89"/>
+      <c r="C64" s="93"/>
+      <c r="D64" s="93"/>
       <c r="E64" s="68"/>
-      <c r="F64" s="89"/>
+      <c r="F64" s="93"/>
       <c r="G64" s="68"/>
       <c r="H64" s="68"/>
-      <c r="I64" s="89"/>
-      <c r="J64" s="89"/>
-      <c r="K64" s="89"/>
+      <c r="I64" s="93"/>
+      <c r="J64" s="93"/>
+      <c r="K64" s="93"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="89"/>
-      <c r="D65" s="89"/>
+      <c r="C65" s="93"/>
+      <c r="D65" s="93"/>
       <c r="E65" s="57"/>
-      <c r="F65" s="89"/>
+      <c r="F65" s="93"/>
       <c r="G65" s="57"/>
       <c r="H65" s="57"/>
-      <c r="I65" s="89"/>
-      <c r="J65" s="89"/>
-      <c r="K65" s="89"/>
+      <c r="I65" s="93"/>
+      <c r="J65" s="93"/>
+      <c r="K65" s="93"/>
     </row>
     <row r="66" spans="3:11" ht="28.5" customHeight="1">
-      <c r="C66" s="89"/>
-      <c r="D66" s="89"/>
+      <c r="C66" s="93"/>
+      <c r="D66" s="93"/>
       <c r="E66" s="68"/>
-      <c r="F66" s="89"/>
+      <c r="F66" s="93"/>
       <c r="G66" s="68"/>
       <c r="H66" s="68"/>
-      <c r="I66" s="89"/>
-      <c r="J66" s="89"/>
-      <c r="K66" s="89"/>
+      <c r="I66" s="93"/>
+      <c r="J66" s="93"/>
+      <c r="K66" s="93"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="89"/>
-      <c r="D67" s="89"/>
+      <c r="C67" s="93"/>
+      <c r="D67" s="93"/>
       <c r="E67" s="68"/>
-      <c r="F67" s="89"/>
+      <c r="F67" s="93"/>
       <c r="G67" s="57"/>
       <c r="H67" s="57"/>
-      <c r="I67" s="89"/>
-      <c r="J67" s="89"/>
-      <c r="K67" s="89"/>
+      <c r="I67" s="93"/>
+      <c r="J67" s="93"/>
+      <c r="K67" s="93"/>
     </row>
     <row r="68" spans="3:11" ht="40.5" customHeight="1">
-      <c r="C68" s="89"/>
-      <c r="D68" s="89"/>
+      <c r="C68" s="93"/>
+      <c r="D68" s="93"/>
       <c r="E68" s="57"/>
-      <c r="F68" s="89"/>
-      <c r="G68" s="89"/>
-      <c r="H68" s="89"/>
-      <c r="I68" s="89"/>
-      <c r="J68" s="89"/>
-      <c r="K68" s="89"/>
+      <c r="F68" s="93"/>
+      <c r="G68" s="93"/>
+      <c r="H68" s="93"/>
+      <c r="I68" s="93"/>
+      <c r="J68" s="93"/>
+      <c r="K68" s="93"/>
     </row>
     <row r="69" spans="3:11" ht="28.5" customHeight="1">
-      <c r="C69" s="89"/>
-      <c r="D69" s="89"/>
+      <c r="C69" s="93"/>
+      <c r="D69" s="93"/>
       <c r="E69" s="68"/>
-      <c r="F69" s="89"/>
-      <c r="G69" s="89"/>
-      <c r="H69" s="89"/>
-      <c r="I69" s="89"/>
-      <c r="J69" s="89"/>
-      <c r="K69" s="89"/>
+      <c r="F69" s="93"/>
+      <c r="G69" s="93"/>
+      <c r="H69" s="93"/>
+      <c r="I69" s="93"/>
+      <c r="J69" s="93"/>
+      <c r="K69" s="93"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="89"/>
-      <c r="D70" s="89"/>
+      <c r="C70" s="93"/>
+      <c r="D70" s="93"/>
       <c r="E70" s="57"/>
-      <c r="F70" s="89"/>
-      <c r="G70" s="89"/>
-      <c r="H70" s="89"/>
-      <c r="I70" s="89"/>
-      <c r="J70" s="89"/>
-      <c r="K70" s="89"/>
+      <c r="F70" s="93"/>
+      <c r="G70" s="93"/>
+      <c r="H70" s="93"/>
+      <c r="I70" s="93"/>
+      <c r="J70" s="93"/>
+      <c r="K70" s="93"/>
     </row>
     <row r="71" spans="3:11" ht="42.75" customHeight="1">
-      <c r="C71" s="89"/>
-      <c r="D71" s="89"/>
+      <c r="C71" s="93"/>
+      <c r="D71" s="93"/>
       <c r="E71" s="57"/>
-      <c r="F71" s="89"/>
-      <c r="G71" s="89"/>
-      <c r="H71" s="89"/>
-      <c r="I71" s="89"/>
-      <c r="J71" s="89"/>
-      <c r="K71" s="89"/>
+      <c r="F71" s="93"/>
+      <c r="G71" s="93"/>
+      <c r="H71" s="93"/>
+      <c r="I71" s="93"/>
+      <c r="J71" s="93"/>
+      <c r="K71" s="93"/>
     </row>
     <row r="72" spans="3:11" ht="28.5" customHeight="1">
-      <c r="C72" s="89"/>
-      <c r="D72" s="89"/>
+      <c r="C72" s="93"/>
+      <c r="D72" s="93"/>
       <c r="E72" s="68"/>
-      <c r="F72" s="89"/>
-      <c r="G72" s="89"/>
-      <c r="H72" s="89"/>
-      <c r="I72" s="89"/>
-      <c r="J72" s="89"/>
-      <c r="K72" s="89"/>
+      <c r="F72" s="93"/>
+      <c r="G72" s="93"/>
+      <c r="H72" s="93"/>
+      <c r="I72" s="93"/>
+      <c r="J72" s="93"/>
+      <c r="K72" s="93"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="89"/>
-      <c r="D73" s="89"/>
+      <c r="C73" s="93"/>
+      <c r="D73" s="93"/>
       <c r="E73" s="57"/>
-      <c r="F73" s="89"/>
-      <c r="G73" s="89"/>
-      <c r="H73" s="89"/>
-      <c r="I73" s="89"/>
-      <c r="J73" s="89"/>
-      <c r="K73" s="89"/>
+      <c r="F73" s="93"/>
+      <c r="G73" s="93"/>
+      <c r="H73" s="93"/>
+      <c r="I73" s="93"/>
+      <c r="J73" s="93"/>
+      <c r="K73" s="93"/>
     </row>
     <row r="74" spans="3:11" ht="42.75" customHeight="1">
-      <c r="C74" s="89"/>
-      <c r="D74" s="89"/>
+      <c r="C74" s="93"/>
+      <c r="D74" s="93"/>
       <c r="E74" s="68"/>
-      <c r="F74" s="89"/>
-      <c r="G74" s="89"/>
-      <c r="H74" s="89"/>
-      <c r="I74" s="89"/>
-      <c r="J74" s="89"/>
-      <c r="K74" s="89"/>
+      <c r="F74" s="93"/>
+      <c r="G74" s="93"/>
+      <c r="H74" s="93"/>
+      <c r="I74" s="93"/>
+      <c r="J74" s="93"/>
+      <c r="K74" s="93"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="89"/>
-      <c r="D75" s="89"/>
+      <c r="C75" s="93"/>
+      <c r="D75" s="93"/>
       <c r="E75" s="57"/>
-      <c r="F75" s="89"/>
-      <c r="G75" s="89"/>
-      <c r="H75" s="89"/>
-      <c r="I75" s="89"/>
-      <c r="J75" s="89"/>
-      <c r="K75" s="89"/>
+      <c r="F75" s="93"/>
+      <c r="G75" s="93"/>
+      <c r="H75" s="93"/>
+      <c r="I75" s="93"/>
+      <c r="J75" s="93"/>
+      <c r="K75" s="93"/>
     </row>
     <row r="77" spans="3:11" ht="28.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="M31:M33"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="A42:M42"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="J56:J58"/>
-    <mergeCell ref="K56:K58"/>
-    <mergeCell ref="C61:C67"/>
-    <mergeCell ref="D61:D67"/>
-    <mergeCell ref="F61:F67"/>
-    <mergeCell ref="I61:I67"/>
-    <mergeCell ref="J61:J67"/>
-    <mergeCell ref="K61:K67"/>
-    <mergeCell ref="I56:I58"/>
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="D56:D58"/>
-    <mergeCell ref="E56:E58"/>
-    <mergeCell ref="F56:F58"/>
     <mergeCell ref="I68:I70"/>
     <mergeCell ref="J68:J70"/>
     <mergeCell ref="K68:K70"/>
@@ -4389,8 +4363,34 @@
     <mergeCell ref="F68:F70"/>
     <mergeCell ref="G68:G70"/>
     <mergeCell ref="H68:H70"/>
+    <mergeCell ref="J56:J58"/>
+    <mergeCell ref="K56:K58"/>
+    <mergeCell ref="C61:C67"/>
+    <mergeCell ref="D61:D67"/>
+    <mergeCell ref="F61:F67"/>
+    <mergeCell ref="I61:I67"/>
+    <mergeCell ref="J61:J67"/>
+    <mergeCell ref="K61:K67"/>
+    <mergeCell ref="I56:I58"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="D56:D58"/>
+    <mergeCell ref="E56:E58"/>
+    <mergeCell ref="F56:F58"/>
+    <mergeCell ref="A42:M42"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G31:L31"/>
+    <mergeCell ref="M31:M33"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="F31:F33"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -4421,25 +4421,25 @@
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="95"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="96"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="91" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="96"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="97"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="28"/>
@@ -4501,62 +4501,62 @@
       </c>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="87" t="s">
+      <c r="B31" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="87" t="s">
+      <c r="C31" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="87" t="s">
+      <c r="D31" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="88" t="s">
+      <c r="E31" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="87" t="s">
+      <c r="F31" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="80" t="s">
+      <c r="G31" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="80"/>
-      <c r="M31" s="80" t="s">
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="87"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="87"/>
-      <c r="G32" s="80" t="s">
+      <c r="A32" s="82"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80" t="s">
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80"/>
-      <c r="M32" s="81"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="85"/>
     </row>
     <row r="33" spans="1:18">
-      <c r="A33" s="87"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="87"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="87"/>
+      <c r="A33" s="82"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="82"/>
       <c r="G33" s="8" t="s">
         <v>14</v>
       </c>
@@ -4575,24 +4575,24 @@
       <c r="L33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="81"/>
+      <c r="M33" s="85"/>
     </row>
     <row r="34" spans="1:18" ht="17.399999999999999" thickBot="1">
-      <c r="A34" s="94" t="s">
+      <c r="A34" s="98" t="s">
         <v>334</v>
       </c>
-      <c r="B34" s="94"/>
-      <c r="C34" s="94"/>
-      <c r="D34" s="94"/>
-      <c r="E34" s="94"/>
-      <c r="F34" s="94"/>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="94"/>
-      <c r="K34" s="94"/>
-      <c r="L34" s="94"/>
-      <c r="M34" s="94"/>
+      <c r="B34" s="98"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98"/>
+      <c r="H34" s="98"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98"/>
+      <c r="K34" s="98"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="98"/>
     </row>
     <row r="35" spans="1:18" ht="51" thickBot="1">
       <c r="A35" s="47" t="s">
@@ -5076,187 +5076,232 @@
       <c r="R55" s="57"/>
     </row>
     <row r="56" spans="6:18" ht="84" customHeight="1">
-      <c r="F56" s="97"/>
-      <c r="G56" s="97"/>
+      <c r="F56" s="94"/>
+      <c r="G56" s="94"/>
       <c r="H56" s="57"/>
-      <c r="I56" s="97"/>
-      <c r="J56" s="97"/>
-      <c r="K56" s="97"/>
-      <c r="L56" s="97"/>
-      <c r="M56" s="98"/>
-      <c r="N56" s="97"/>
-      <c r="O56" s="97"/>
-      <c r="P56" s="98"/>
-      <c r="Q56" s="97"/>
-      <c r="R56" s="97"/>
+      <c r="I56" s="94"/>
+      <c r="J56" s="94"/>
+      <c r="K56" s="94"/>
+      <c r="L56" s="94"/>
+      <c r="M56" s="95"/>
+      <c r="N56" s="94"/>
+      <c r="O56" s="94"/>
+      <c r="P56" s="95"/>
+      <c r="Q56" s="94"/>
+      <c r="R56" s="94"/>
     </row>
     <row r="57" spans="6:18">
-      <c r="F57" s="97"/>
-      <c r="G57" s="97"/>
+      <c r="F57" s="94"/>
+      <c r="G57" s="94"/>
       <c r="H57" s="59"/>
-      <c r="I57" s="97"/>
-      <c r="J57" s="97"/>
-      <c r="K57" s="97"/>
-      <c r="L57" s="97"/>
-      <c r="M57" s="98"/>
-      <c r="N57" s="97"/>
-      <c r="O57" s="97"/>
-      <c r="P57" s="98"/>
-      <c r="Q57" s="97"/>
-      <c r="R57" s="97"/>
+      <c r="I57" s="94"/>
+      <c r="J57" s="94"/>
+      <c r="K57" s="94"/>
+      <c r="L57" s="94"/>
+      <c r="M57" s="95"/>
+      <c r="N57" s="94"/>
+      <c r="O57" s="94"/>
+      <c r="P57" s="95"/>
+      <c r="Q57" s="94"/>
+      <c r="R57" s="94"/>
     </row>
     <row r="58" spans="6:18">
-      <c r="F58" s="97"/>
-      <c r="G58" s="97"/>
+      <c r="F58" s="94"/>
+      <c r="G58" s="94"/>
       <c r="H58" s="57"/>
-      <c r="I58" s="97"/>
-      <c r="J58" s="97"/>
-      <c r="K58" s="97"/>
-      <c r="L58" s="97"/>
-      <c r="M58" s="98"/>
-      <c r="N58" s="97"/>
-      <c r="O58" s="97"/>
-      <c r="P58" s="98"/>
-      <c r="Q58" s="97"/>
-      <c r="R58" s="97"/>
+      <c r="I58" s="94"/>
+      <c r="J58" s="94"/>
+      <c r="K58" s="94"/>
+      <c r="L58" s="94"/>
+      <c r="M58" s="95"/>
+      <c r="N58" s="94"/>
+      <c r="O58" s="94"/>
+      <c r="P58" s="95"/>
+      <c r="Q58" s="94"/>
+      <c r="R58" s="94"/>
     </row>
     <row r="59" spans="6:18" ht="55.5" customHeight="1">
-      <c r="F59" s="97"/>
-      <c r="G59" s="97"/>
+      <c r="F59" s="94"/>
+      <c r="G59" s="94"/>
       <c r="H59" s="57"/>
-      <c r="I59" s="97"/>
-      <c r="J59" s="97"/>
-      <c r="K59" s="97"/>
-      <c r="L59" s="97"/>
-      <c r="M59" s="98"/>
-      <c r="N59" s="97"/>
-      <c r="O59" s="97"/>
-      <c r="P59" s="98"/>
-      <c r="Q59" s="97"/>
-      <c r="R59" s="97"/>
+      <c r="I59" s="94"/>
+      <c r="J59" s="94"/>
+      <c r="K59" s="94"/>
+      <c r="L59" s="94"/>
+      <c r="M59" s="95"/>
+      <c r="N59" s="94"/>
+      <c r="O59" s="94"/>
+      <c r="P59" s="95"/>
+      <c r="Q59" s="94"/>
+      <c r="R59" s="94"/>
     </row>
     <row r="60" spans="6:18">
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
+      <c r="F60" s="94"/>
+      <c r="G60" s="94"/>
       <c r="H60" s="59"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="97"/>
-      <c r="L60" s="97"/>
-      <c r="M60" s="98"/>
-      <c r="N60" s="97"/>
-      <c r="O60" s="97"/>
-      <c r="P60" s="98"/>
-      <c r="Q60" s="97"/>
-      <c r="R60" s="97"/>
+      <c r="I60" s="94"/>
+      <c r="J60" s="94"/>
+      <c r="K60" s="94"/>
+      <c r="L60" s="94"/>
+      <c r="M60" s="95"/>
+      <c r="N60" s="94"/>
+      <c r="O60" s="94"/>
+      <c r="P60" s="95"/>
+      <c r="Q60" s="94"/>
+      <c r="R60" s="94"/>
     </row>
     <row r="61" spans="6:18">
-      <c r="F61" s="97"/>
-      <c r="G61" s="97"/>
+      <c r="F61" s="94"/>
+      <c r="G61" s="94"/>
       <c r="H61" s="57"/>
-      <c r="I61" s="97"/>
-      <c r="J61" s="97"/>
-      <c r="K61" s="97"/>
-      <c r="L61" s="97"/>
-      <c r="M61" s="98"/>
-      <c r="N61" s="97"/>
-      <c r="O61" s="97"/>
-      <c r="P61" s="98"/>
-      <c r="Q61" s="97"/>
-      <c r="R61" s="97"/>
+      <c r="I61" s="94"/>
+      <c r="J61" s="94"/>
+      <c r="K61" s="94"/>
+      <c r="L61" s="94"/>
+      <c r="M61" s="95"/>
+      <c r="N61" s="94"/>
+      <c r="O61" s="94"/>
+      <c r="P61" s="95"/>
+      <c r="Q61" s="94"/>
+      <c r="R61" s="94"/>
     </row>
     <row r="62" spans="6:18" ht="84" customHeight="1">
-      <c r="F62" s="97"/>
-      <c r="G62" s="97"/>
+      <c r="F62" s="94"/>
+      <c r="G62" s="94"/>
       <c r="H62" s="57"/>
-      <c r="I62" s="97"/>
-      <c r="J62" s="97"/>
-      <c r="K62" s="97"/>
-      <c r="L62" s="97"/>
-      <c r="M62" s="98"/>
-      <c r="N62" s="97"/>
-      <c r="O62" s="97"/>
-      <c r="P62" s="98"/>
-      <c r="Q62" s="97"/>
-      <c r="R62" s="97"/>
+      <c r="I62" s="94"/>
+      <c r="J62" s="94"/>
+      <c r="K62" s="94"/>
+      <c r="L62" s="94"/>
+      <c r="M62" s="95"/>
+      <c r="N62" s="94"/>
+      <c r="O62" s="94"/>
+      <c r="P62" s="95"/>
+      <c r="Q62" s="94"/>
+      <c r="R62" s="94"/>
     </row>
     <row r="63" spans="6:18">
-      <c r="F63" s="97"/>
-      <c r="G63" s="97"/>
+      <c r="F63" s="94"/>
+      <c r="G63" s="94"/>
       <c r="H63" s="59"/>
-      <c r="I63" s="97"/>
-      <c r="J63" s="97"/>
-      <c r="K63" s="97"/>
-      <c r="L63" s="97"/>
-      <c r="M63" s="98"/>
-      <c r="N63" s="97"/>
-      <c r="O63" s="97"/>
-      <c r="P63" s="98"/>
-      <c r="Q63" s="97"/>
-      <c r="R63" s="97"/>
+      <c r="I63" s="94"/>
+      <c r="J63" s="94"/>
+      <c r="K63" s="94"/>
+      <c r="L63" s="94"/>
+      <c r="M63" s="95"/>
+      <c r="N63" s="94"/>
+      <c r="O63" s="94"/>
+      <c r="P63" s="95"/>
+      <c r="Q63" s="94"/>
+      <c r="R63" s="94"/>
     </row>
     <row r="64" spans="6:18">
-      <c r="F64" s="97"/>
-      <c r="G64" s="97"/>
+      <c r="F64" s="94"/>
+      <c r="G64" s="94"/>
       <c r="H64" s="57"/>
-      <c r="I64" s="97"/>
-      <c r="J64" s="97"/>
-      <c r="K64" s="97"/>
-      <c r="L64" s="97"/>
-      <c r="M64" s="98"/>
-      <c r="N64" s="97"/>
-      <c r="O64" s="97"/>
-      <c r="P64" s="98"/>
-      <c r="Q64" s="97"/>
-      <c r="R64" s="97"/>
+      <c r="I64" s="94"/>
+      <c r="J64" s="94"/>
+      <c r="K64" s="94"/>
+      <c r="L64" s="94"/>
+      <c r="M64" s="95"/>
+      <c r="N64" s="94"/>
+      <c r="O64" s="94"/>
+      <c r="P64" s="95"/>
+      <c r="Q64" s="94"/>
+      <c r="R64" s="94"/>
     </row>
     <row r="65" spans="6:18" ht="69.75" customHeight="1">
-      <c r="F65" s="97"/>
-      <c r="G65" s="97"/>
+      <c r="F65" s="94"/>
+      <c r="G65" s="94"/>
       <c r="H65" s="57"/>
-      <c r="I65" s="97"/>
-      <c r="J65" s="97"/>
-      <c r="K65" s="97"/>
-      <c r="L65" s="97"/>
-      <c r="M65" s="98"/>
-      <c r="N65" s="97"/>
-      <c r="O65" s="97"/>
-      <c r="P65" s="98"/>
-      <c r="Q65" s="97"/>
-      <c r="R65" s="97"/>
+      <c r="I65" s="94"/>
+      <c r="J65" s="94"/>
+      <c r="K65" s="94"/>
+      <c r="L65" s="94"/>
+      <c r="M65" s="95"/>
+      <c r="N65" s="94"/>
+      <c r="O65" s="94"/>
+      <c r="P65" s="95"/>
+      <c r="Q65" s="94"/>
+      <c r="R65" s="94"/>
     </row>
     <row r="66" spans="6:18">
-      <c r="F66" s="97"/>
-      <c r="G66" s="97"/>
+      <c r="F66" s="94"/>
+      <c r="G66" s="94"/>
       <c r="H66" s="59"/>
-      <c r="I66" s="97"/>
-      <c r="J66" s="97"/>
-      <c r="K66" s="97"/>
-      <c r="L66" s="97"/>
-      <c r="M66" s="98"/>
-      <c r="N66" s="97"/>
-      <c r="O66" s="97"/>
-      <c r="P66" s="98"/>
-      <c r="Q66" s="97"/>
-      <c r="R66" s="97"/>
+      <c r="I66" s="94"/>
+      <c r="J66" s="94"/>
+      <c r="K66" s="94"/>
+      <c r="L66" s="94"/>
+      <c r="M66" s="95"/>
+      <c r="N66" s="94"/>
+      <c r="O66" s="94"/>
+      <c r="P66" s="95"/>
+      <c r="Q66" s="94"/>
+      <c r="R66" s="94"/>
     </row>
     <row r="67" spans="6:18">
-      <c r="F67" s="97"/>
-      <c r="G67" s="97"/>
+      <c r="F67" s="94"/>
+      <c r="G67" s="94"/>
       <c r="H67" s="57"/>
-      <c r="I67" s="97"/>
-      <c r="J67" s="97"/>
-      <c r="K67" s="97"/>
-      <c r="L67" s="97"/>
-      <c r="M67" s="98"/>
-      <c r="N67" s="97"/>
-      <c r="O67" s="97"/>
-      <c r="P67" s="98"/>
-      <c r="Q67" s="97"/>
-      <c r="R67" s="97"/>
+      <c r="I67" s="94"/>
+      <c r="J67" s="94"/>
+      <c r="K67" s="94"/>
+      <c r="L67" s="94"/>
+      <c r="M67" s="95"/>
+      <c r="N67" s="94"/>
+      <c r="O67" s="94"/>
+      <c r="P67" s="95"/>
+      <c r="Q67" s="94"/>
+      <c r="R67" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="61">
+    <mergeCell ref="A34:M34"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G31:L31"/>
+    <mergeCell ref="M31:M33"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="N56:N58"/>
+    <mergeCell ref="O56:O58"/>
+    <mergeCell ref="P56:P58"/>
+    <mergeCell ref="F56:F58"/>
+    <mergeCell ref="G56:G58"/>
+    <mergeCell ref="I56:I58"/>
+    <mergeCell ref="J56:J58"/>
+    <mergeCell ref="K56:K58"/>
+    <mergeCell ref="Q56:Q58"/>
+    <mergeCell ref="R56:R58"/>
+    <mergeCell ref="F59:F61"/>
+    <mergeCell ref="G59:G61"/>
+    <mergeCell ref="I59:I61"/>
+    <mergeCell ref="J59:J61"/>
+    <mergeCell ref="K59:K61"/>
+    <mergeCell ref="L59:L61"/>
+    <mergeCell ref="M59:M61"/>
+    <mergeCell ref="N59:N61"/>
+    <mergeCell ref="O59:O61"/>
+    <mergeCell ref="P59:P61"/>
+    <mergeCell ref="Q59:Q61"/>
+    <mergeCell ref="R59:R61"/>
+    <mergeCell ref="L56:L58"/>
+    <mergeCell ref="M56:M58"/>
+    <mergeCell ref="N62:N64"/>
+    <mergeCell ref="O62:O64"/>
+    <mergeCell ref="P62:P64"/>
+    <mergeCell ref="F62:F64"/>
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="I62:I64"/>
+    <mergeCell ref="J62:J64"/>
+    <mergeCell ref="K62:K64"/>
     <mergeCell ref="Q62:Q64"/>
     <mergeCell ref="R62:R64"/>
     <mergeCell ref="F65:F67"/>
@@ -5273,53 +5318,8 @@
     <mergeCell ref="R65:R67"/>
     <mergeCell ref="L62:L64"/>
     <mergeCell ref="M62:M64"/>
-    <mergeCell ref="N62:N64"/>
-    <mergeCell ref="O62:O64"/>
-    <mergeCell ref="P62:P64"/>
-    <mergeCell ref="F62:F64"/>
-    <mergeCell ref="G62:G64"/>
-    <mergeCell ref="I62:I64"/>
-    <mergeCell ref="J62:J64"/>
-    <mergeCell ref="K62:K64"/>
-    <mergeCell ref="Q56:Q58"/>
-    <mergeCell ref="R56:R58"/>
-    <mergeCell ref="F59:F61"/>
-    <mergeCell ref="G59:G61"/>
-    <mergeCell ref="I59:I61"/>
-    <mergeCell ref="J59:J61"/>
-    <mergeCell ref="K59:K61"/>
-    <mergeCell ref="L59:L61"/>
-    <mergeCell ref="M59:M61"/>
-    <mergeCell ref="N59:N61"/>
-    <mergeCell ref="O59:O61"/>
-    <mergeCell ref="P59:P61"/>
-    <mergeCell ref="Q59:Q61"/>
-    <mergeCell ref="R59:R61"/>
-    <mergeCell ref="L56:L58"/>
-    <mergeCell ref="M56:M58"/>
-    <mergeCell ref="N56:N58"/>
-    <mergeCell ref="O56:O58"/>
-    <mergeCell ref="P56:P58"/>
-    <mergeCell ref="F56:F58"/>
-    <mergeCell ref="G56:G58"/>
-    <mergeCell ref="I56:I58"/>
-    <mergeCell ref="J56:J58"/>
-    <mergeCell ref="K56:K58"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="M31:M33"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="A34:M34"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -5350,25 +5350,25 @@
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="28"/>
@@ -5433,62 +5433,62 @@
     <row r="9" spans="1:6" ht="114.75" customHeight="1"/>
     <row r="30" spans="1:13" ht="118.5" customHeight="1"/>
     <row r="31" spans="1:13">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="87" t="s">
+      <c r="B31" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="87" t="s">
+      <c r="C31" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="87" t="s">
+      <c r="D31" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="88" t="s">
+      <c r="E31" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="87" t="s">
+      <c r="F31" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="80" t="s">
+      <c r="G31" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="80"/>
-      <c r="M31" s="80" t="s">
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="87"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="87"/>
-      <c r="G32" s="80" t="s">
+      <c r="A32" s="82"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80" t="s">
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80"/>
-      <c r="M32" s="81"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="85"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="87"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="87"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="87"/>
+      <c r="A33" s="82"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="82"/>
       <c r="G33" s="8" t="s">
         <v>14</v>
       </c>
@@ -5507,7 +5507,7 @@
       <c r="L33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="81"/>
+      <c r="M33" s="85"/>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="102" t="s">
@@ -5668,6 +5668,13 @@
     <row r="44" spans="1:14" ht="225" customHeight="1"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A36:M36"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="A34:M34"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G31:L31"/>
@@ -5675,13 +5682,6 @@
     <mergeCell ref="G32:I32"/>
     <mergeCell ref="J32:L32"/>
     <mergeCell ref="F31:F33"/>
-    <mergeCell ref="A36:M36"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="A34:M34"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="G35:G38 J35:J38" xr:uid="{00000000-0002-0000-0500-000000000000}">
@@ -5689,7 +5689,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -5720,25 +5720,25 @@
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="81" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="28"/>
@@ -5801,62 +5801,62 @@
     </row>
     <row r="14" spans="1:6" ht="75.75" customHeight="1"/>
     <row r="31" spans="1:13">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="87" t="s">
+      <c r="B31" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="87" t="s">
+      <c r="C31" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="87" t="s">
+      <c r="D31" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="88" t="s">
+      <c r="E31" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="87" t="s">
+      <c r="F31" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="80" t="s">
+      <c r="G31" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="80"/>
-      <c r="M31" s="80" t="s">
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="87"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="87"/>
-      <c r="G32" s="80" t="s">
+      <c r="A32" s="82"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80" t="s">
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80"/>
-      <c r="M32" s="81"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="85"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="87"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="87"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="87"/>
+      <c r="A33" s="82"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="82"/>
       <c r="G33" s="8" t="s">
         <v>14</v>
       </c>
@@ -5875,24 +5875,24 @@
       <c r="L33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="81"/>
+      <c r="M33" s="85"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="94" t="s">
+      <c r="A34" s="98" t="s">
         <v>335</v>
       </c>
-      <c r="B34" s="94"/>
-      <c r="C34" s="94"/>
-      <c r="D34" s="94"/>
-      <c r="E34" s="94"/>
-      <c r="F34" s="94"/>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="94"/>
-      <c r="K34" s="94"/>
-      <c r="L34" s="94"/>
-      <c r="M34" s="94"/>
+      <c r="B34" s="98"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98"/>
+      <c r="H34" s="98"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98"/>
+      <c r="K34" s="98"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="98"/>
     </row>
     <row r="35" spans="1:14" ht="127.5" customHeight="1">
       <c r="A35" s="31" t="s">
@@ -6304,6 +6304,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="A34:M34"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G31:L31"/>
@@ -6311,13 +6318,6 @@
     <mergeCell ref="G32:I32"/>
     <mergeCell ref="J32:L32"/>
     <mergeCell ref="F31:F33"/>
-    <mergeCell ref="A39:M39"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="A34:M34"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="G35:G38 J35:J38 G40:G45 J40:J45" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -6325,7 +6325,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -6356,25 +6356,25 @@
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="28"/>
@@ -6439,62 +6439,62 @@
     <row r="9" spans="1:6" ht="330.75" customHeight="1"/>
     <row r="30" spans="1:13" ht="171" customHeight="1"/>
     <row r="31" spans="1:13">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="87" t="s">
+      <c r="B31" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="87" t="s">
+      <c r="C31" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="87" t="s">
+      <c r="D31" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="88" t="s">
+      <c r="E31" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="87" t="s">
+      <c r="F31" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="80" t="s">
+      <c r="G31" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="80"/>
-      <c r="M31" s="80" t="s">
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="87"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="87"/>
-      <c r="G32" s="80" t="s">
+      <c r="A32" s="82"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80" t="s">
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80"/>
-      <c r="M32" s="81"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="85"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="87"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="87"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="87"/>
+      <c r="A33" s="82"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="82"/>
       <c r="G33" s="8" t="s">
         <v>14</v>
       </c>
@@ -6513,7 +6513,7 @@
       <c r="L33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="81"/>
+      <c r="M33" s="85"/>
     </row>
     <row r="34" spans="1:14" ht="38.25" customHeight="1">
       <c r="A34" s="102" t="s">
@@ -6650,21 +6650,21 @@
       <c r="M37" s="37"/>
     </row>
     <row r="38" spans="1:14" ht="50.25" customHeight="1">
-      <c r="A38" s="82" t="s">
+      <c r="A38" s="86" t="s">
         <v>236</v>
       </c>
-      <c r="B38" s="83"/>
-      <c r="C38" s="83"/>
-      <c r="D38" s="83"/>
-      <c r="E38" s="83"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="83"/>
-      <c r="M38" s="84"/>
+      <c r="B38" s="87"/>
+      <c r="C38" s="87"/>
+      <c r="D38" s="87"/>
+      <c r="E38" s="87"/>
+      <c r="F38" s="87"/>
+      <c r="G38" s="87"/>
+      <c r="H38" s="87"/>
+      <c r="I38" s="87"/>
+      <c r="J38" s="87"/>
+      <c r="K38" s="87"/>
+      <c r="L38" s="87"/>
+      <c r="M38" s="88"/>
       <c r="N38" s="1"/>
     </row>
     <row r="39" spans="1:14" ht="193.5" customHeight="1">
@@ -6774,6 +6774,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="A34:M34"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G31:L31"/>
@@ -6781,13 +6788,6 @@
     <mergeCell ref="G32:I32"/>
     <mergeCell ref="J32:L32"/>
     <mergeCell ref="F31:F33"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="A34:M34"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="G35:G37 J35:J37 H41:H42 G39:G40 K41:K42 J39:J40" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -6795,7 +6795,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -6826,13 +6826,13 @@
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14" t="s">
@@ -6908,22 +6908,22 @@
     </row>
     <row r="30" spans="1:13" ht="84.75" customHeight="1"/>
     <row r="31" spans="1:13">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="87" t="s">
+      <c r="B31" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="87" t="s">
+      <c r="C31" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="87" t="s">
+      <c r="D31" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="88" t="s">
+      <c r="E31" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="87" t="s">
+      <c r="F31" s="82" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="107" t="s">
@@ -6939,12 +6939,12 @@
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="87"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="87"/>
+      <c r="A32" s="82"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="82"/>
       <c r="G32" s="107" t="s">
         <v>20</v>
       </c>
@@ -6958,12 +6958,12 @@
       <c r="M32" s="108"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="87"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="87"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="87"/>
+      <c r="A33" s="82"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="82"/>
       <c r="G33" s="8" t="s">
         <v>14</v>
       </c>
@@ -6985,21 +6985,21 @@
       <c r="M33" s="108"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="94" t="s">
+      <c r="A34" s="98" t="s">
         <v>299</v>
       </c>
-      <c r="B34" s="94"/>
-      <c r="C34" s="94"/>
-      <c r="D34" s="94"/>
-      <c r="E34" s="94"/>
-      <c r="F34" s="94"/>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="94"/>
-      <c r="K34" s="94"/>
-      <c r="L34" s="94"/>
-      <c r="M34" s="94"/>
+      <c r="B34" s="98"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98"/>
+      <c r="H34" s="98"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98"/>
+      <c r="K34" s="98"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="98"/>
     </row>
     <row r="35" spans="1:14" ht="84">
       <c r="A35" s="3" t="s">
@@ -7216,6 +7216,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="A34:M34"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G31:L31"/>
@@ -7223,13 +7230,6 @@
     <mergeCell ref="G32:I32"/>
     <mergeCell ref="J32:L32"/>
     <mergeCell ref="F31:F33"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="A34:M34"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="J35:J36 G35:G36 G38:G40 J38:J40" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -7237,7 +7237,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/BaoCao_Final/9.2.TestCaseSprint2.xlsx
+++ b/BaoCao_Final/9.2.TestCaseSprint2.xlsx
@@ -5,22 +5,23 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="e:\Downloads\Document\BaoCao_Final(1)\BaoCao_Final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BaoCao_Final (5) - File Sửa\BaoCao_Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D0A980-714D-447D-9DA1-D6F917AD368A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6531FB8D-4E53-427F-ABE0-5EF72E021E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="803" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="857" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trường hợp kiểm thử" sheetId="12" r:id="rId1"/>
-    <sheet name="Thống kê báo cáo hệ thống" sheetId="13" r:id="rId2"/>
-    <sheet name="Xem lịch học" sheetId="1" r:id="rId3"/>
-    <sheet name="Mở phòng học" sheetId="2" r:id="rId4"/>
-    <sheet name="Xuất báo cáo điểm danh" sheetId="7" r:id="rId5"/>
-    <sheet name="Quản lý lớp học và tương tác" sheetId="3" r:id="rId6"/>
-    <sheet name="Gửi yêu cầu xin phép vắng" sheetId="4" r:id="rId7"/>
-    <sheet name="Tham gia lớp học trực tuyến" sheetId="6" r:id="rId8"/>
+    <sheet name="Tương tác trong lớp" sheetId="14" r:id="rId2"/>
+    <sheet name="Thống kê báo cáo hệ thống" sheetId="13" r:id="rId3"/>
+    <sheet name="Xem lịch học" sheetId="1" r:id="rId4"/>
+    <sheet name="Mở phòng học" sheetId="2" r:id="rId5"/>
+    <sheet name="Xuất báo cáo điểm danh" sheetId="7" r:id="rId6"/>
+    <sheet name="Quản lý lớp học" sheetId="3" r:id="rId7"/>
+    <sheet name="Gửi yêu cầu xin phép vắng" sheetId="4" r:id="rId8"/>
+    <sheet name="Tham gia lớp học trực tuyến" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="357">
   <si>
     <t>Project Name</t>
   </si>
@@ -111,11 +112,6 @@
     <t>Điều kiện tiên quyết</t>
   </si>
   <si>
-    <t>1. Khởi động trang web.
-2. Vào trang đăng nhập
-3. Chọn quên mật khẩu              4.Nhâp địa chỉ email</t>
-  </si>
-  <si>
     <t>Tên dự án</t>
   </si>
   <si>
@@ -198,9 +194,6 @@
   </si>
   <si>
     <t>GUI-XLH01</t>
-  </si>
-  <si>
-    <t>Xuân Vinh</t>
   </si>
   <si>
     <t>GUI-XLH02</t>
@@ -388,9 +381,6 @@
   </si>
   <si>
     <t>Mục "Lịch giảng dạy" trên Sidebar được highlight xanh nhạt. Có avatar.</t>
-  </si>
-  <si>
-    <t>Văn Cường</t>
   </si>
   <si>
     <t>GUI-MPH02</t>
@@ -1080,6 +1070,80 @@
   </si>
   <si>
     <t>FUNCTION_SHOW Quản lý lớp học và tương tác</t>
+  </si>
+  <si>
+    <t>Tương tác trong lớp</t>
+  </si>
+  <si>
+    <t>Tương tác</t>
+  </si>
+  <si>
+    <t>Kiểm tra các chức năng giơ tay, nhắn tin trong phòng học</t>
+  </si>
+  <si>
+    <t>[Sidebar] Kiểm tra hiển thị giao diện Sidebar mặc định</t>
+  </si>
+  <si>
+    <t>1. Vào phòng học trực tuyến.
+2. Quan sát thanh công cụ bên phả</t>
+  </si>
+  <si>
+    <t>Người dùng tham gia phòng học thành công.</t>
+  </si>
+  <si>
+    <t>Hiển thị 3 tab: Chat, Thành viên, Điểm danh. Tab hiện tại được làm nổi bật (gạch chân xanh).</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng số lượng tab và định dạng tab đang chọn.</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị khung hình và trạng thái thiết bị</t>
+  </si>
+  <si>
+    <t>Kiểm tra giao diện trạng thái "Giơ tay"</t>
+  </si>
+  <si>
+    <t>1. Một người dùng bấm nút Giơ tay.
+2. Quan sát giao diện người đó</t>
+  </si>
+  <si>
+    <t>1. Quan sát khung video của người tham gia.</t>
+  </si>
+  <si>
+    <t>Có thành viên trong phòng (VD: Nguyễn Hoàng An).</t>
+  </si>
+  <si>
+    <t>Chức năng Giơ tay được kích hoạt.</t>
+  </si>
+  <si>
+    <t>Khung video của người đó nổi viền vàng nổi bật, xuất hiện icon bàn tay nhỏ màu vàng góc trên phải.</t>
+  </si>
+  <si>
+    <t>Hiển thị Avatar lớn giữa màn hình, tên người dùng góc dưới trái, kèm icon trạng thái Mic/Camera đỏ (nếu tắt).</t>
+  </si>
+  <si>
+    <t>Hiển thị Avatar, tên và các icon mic tắt đúng vị trí.</t>
+  </si>
+  <si>
+    <t>Khung video NA có viền vàng, icon bàn tay góc phải hiển thị đúng.</t>
+  </si>
+  <si>
+    <t>GUI-TT01</t>
+  </si>
+  <si>
+    <t>GUI-TT02</t>
+  </si>
+  <si>
+    <t>GUI-TT03</t>
+  </si>
+  <si>
+    <t>FUNC-TG04</t>
+  </si>
+  <si>
+    <t>1. Khởi động trang web.
+2. Vào trang đăng nhập
+3. Chọn quên mật khẩu              
+4.Nhâp địa chỉ email</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1154,7 @@
     <numFmt numFmtId="164" formatCode="d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1112,46 +1176,6 @@
     <font>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color indexed="9"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color rgb="FF1F1F1F"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1201,13 +1225,77 @@
     </font>
     <font>
       <sz val="13"/>
+      <color rgb="FF333333"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="13"/>
-      <color rgb="FF333333"/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1472,318 +1560,376 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1809,6 +1955,61 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
+      <xdr:colOff>625928</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>92529</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2843893</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>29395</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D8D7151-7207-2970-4A7E-4FB337EBA236}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="625928" y="1113065"/>
+          <a:ext cx="9647465" cy="4835437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>27215</xdr:rowOff>
@@ -1817,7 +2018,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>885265</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>2921901</xdr:rowOff>
+      <xdr:rowOff>3045164</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1861,7 +2062,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>137402</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>3572499</xdr:rowOff>
+      <xdr:rowOff>3695762</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1904,8 +2105,8 @@
     <xdr:to>
       <xdr:col>43</xdr:col>
       <xdr:colOff>20240</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>176196</xdr:rowOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>142579</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1949,7 +2150,7 @@
       <xdr:col>43</xdr:col>
       <xdr:colOff>158334</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>3503382</xdr:rowOff>
+      <xdr:rowOff>3650740</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1985,7 +2186,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2034,7 +2235,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2083,7 +2284,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2176,7 +2377,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2231,7 +2432,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2436,7 +2637,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2773,230 +2974,244 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="14.21875" style="71" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.44140625" style="71" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" style="71" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="83.77734375" style="71" customWidth="1"/>
-    <col min="5" max="16384" width="8.77734375" style="71"/>
+    <col min="1" max="1" width="14.26953125" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.453125" style="30" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" style="30" customWidth="1"/>
+    <col min="4" max="4" width="83.7265625" style="30" customWidth="1"/>
+    <col min="5" max="16384" width="8.7265625" style="30"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="95" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+    </row>
+    <row r="2" spans="1:4" ht="11.25" customHeight="1">
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+    </row>
+    <row r="3" spans="1:4" ht="42.75" customHeight="1">
+      <c r="A3" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-    </row>
-    <row r="2" spans="1:4" ht="11.25" customHeight="1">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-    </row>
-    <row r="3" spans="1:4" ht="42.75" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+    </row>
+    <row r="4" spans="1:4" ht="15">
+      <c r="A4" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B4" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27" customHeight="1">
+      <c r="A5" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.5">
+      <c r="A6" s="35">
+        <v>1</v>
+      </c>
+      <c r="B6" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-    </row>
-    <row r="4" spans="1:4" ht="19.2" thickBot="1">
-      <c r="A4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="27" customHeight="1" thickBot="1">
-      <c r="A5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A6" s="76">
-        <v>1</v>
-      </c>
-      <c r="B6" s="72" t="s">
+      <c r="C6" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="72" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="72" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="15.5">
+      <c r="A7" s="35">
+        <v>2</v>
+      </c>
+      <c r="B7" s="36" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="65.25" customHeight="1" thickBot="1">
-      <c r="A7" s="76">
-        <v>2</v>
-      </c>
-      <c r="B7" s="72" t="s">
+      <c r="C7" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="D7" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="72" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="15.5">
+      <c r="A8" s="35">
+        <v>3</v>
+      </c>
+      <c r="B8" s="36" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="39" thickBot="1">
-      <c r="A8" s="76">
-        <v>3</v>
-      </c>
-      <c r="B8" s="72" t="s">
+      <c r="C8" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="D8" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="72" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="15.5">
+      <c r="A9" s="35">
+        <v>4</v>
+      </c>
+      <c r="B9" s="36" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="39" thickBot="1">
-      <c r="A9" s="76">
-        <v>4</v>
-      </c>
-      <c r="B9" s="72" t="s">
+      <c r="C9" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="72" t="s">
+      <c r="D9" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="72" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="15.5">
+      <c r="A10" s="35">
+        <v>5</v>
+      </c>
+      <c r="B10" s="36" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="39" thickBot="1">
-      <c r="A10" s="76">
-        <v>5</v>
-      </c>
-      <c r="B10" s="72" t="s">
+      <c r="C10" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="D10" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="72" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="15.5">
+      <c r="A11" s="35">
+        <v>6</v>
+      </c>
+      <c r="B11" s="36" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="39" thickBot="1">
-      <c r="A11" s="76">
-        <v>6</v>
-      </c>
-      <c r="B11" s="72" t="s">
+      <c r="C11" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="D11" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="72" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="15.5">
+      <c r="A12" s="35">
+        <v>7</v>
+      </c>
+      <c r="B12" s="36" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="38.4">
-      <c r="A12" s="77">
-        <v>7</v>
-      </c>
-      <c r="B12" s="73" t="s">
+      <c r="C12" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="D12" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="73" t="s">
-        <v>49</v>
+    </row>
+    <row r="13" spans="1:4" ht="15.5">
+      <c r="A13" s="38">
+        <v>8</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>334</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="74"/>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="74"/>
-      <c r="B15" s="74"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="74"/>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="75"/>
-      <c r="B17" s="75"/>
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="75"/>
-      <c r="B18" s="75"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="75"/>
-      <c r="B19" s="75"/>
-      <c r="C19" s="75"/>
-      <c r="D19" s="75"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="75"/>
-      <c r="B20" s="75"/>
-      <c r="C20" s="75"/>
-      <c r="D20" s="75"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="75"/>
-      <c r="B21" s="75"/>
-      <c r="C21" s="75"/>
-      <c r="D21" s="75"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="75"/>
-      <c r="B22" s="75"/>
-      <c r="C22" s="75"/>
-      <c r="D22" s="75"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="75"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="75"/>
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3009,414 +3224,927 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA115786-8740-427A-BE60-697A96F9906E}">
+  <dimension ref="A1:M44"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5"/>
+  <cols>
+    <col min="1" max="1" width="16.1796875" style="40" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" style="40" customWidth="1"/>
+    <col min="3" max="3" width="26.7265625" style="40" customWidth="1"/>
+    <col min="4" max="4" width="27.1796875" style="40" customWidth="1"/>
+    <col min="5" max="5" width="27.81640625" style="40" customWidth="1"/>
+    <col min="6" max="6" width="99" style="40" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" style="40" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" style="40" customWidth="1"/>
+    <col min="9" max="9" width="16.453125" style="40" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" style="40" customWidth="1"/>
+    <col min="11" max="11" width="14" style="40" customWidth="1"/>
+    <col min="12" max="12" width="15.26953125" style="40" customWidth="1"/>
+    <col min="13" max="16384" width="9.1796875" style="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="20">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="103" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+    </row>
+    <row r="3" spans="1:6" ht="16" thickBot="1">
+      <c r="A3" s="41"/>
+      <c r="B3" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" thickBot="1">
+      <c r="A4" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="46">
+        <v>6</v>
+      </c>
+      <c r="C4" s="46">
+        <v>0</v>
+      </c>
+      <c r="D4" s="46">
+        <v>0</v>
+      </c>
+      <c r="E4" s="46">
+        <v>0</v>
+      </c>
+      <c r="F4" s="47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16" thickBot="1">
+      <c r="A5" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="46">
+        <v>6</v>
+      </c>
+      <c r="C5" s="46">
+        <v>0</v>
+      </c>
+      <c r="D5" s="46">
+        <v>0</v>
+      </c>
+      <c r="E5" s="46">
+        <v>0</v>
+      </c>
+      <c r="F5" s="47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="105" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="105" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="105" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="105" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="106" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="105" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="98" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="98"/>
+      <c r="I33" s="98"/>
+      <c r="J33" s="98"/>
+      <c r="K33" s="98"/>
+      <c r="L33" s="98"/>
+      <c r="M33" s="98" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="105"/>
+      <c r="B34" s="105"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="106"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="98" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="98"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" s="98"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="99"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="105"/>
+      <c r="B35" s="105"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="K35" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="L35" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="M35" s="99"/>
+    </row>
+    <row r="36" spans="1:13" ht="16" thickBot="1">
+      <c r="A36" s="100" t="s">
+        <v>331</v>
+      </c>
+      <c r="B36" s="100"/>
+      <c r="C36" s="100"/>
+      <c r="D36" s="100"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="100"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="100"/>
+      <c r="J36" s="100"/>
+      <c r="K36" s="100"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="100"/>
+    </row>
+    <row r="37" spans="1:13" ht="78" thickBot="1">
+      <c r="A37" s="50" t="s">
+        <v>352</v>
+      </c>
+      <c r="B37" s="50" t="s">
+        <v>337</v>
+      </c>
+      <c r="C37" s="50" t="s">
+        <v>338</v>
+      </c>
+      <c r="D37" s="50" t="s">
+        <v>339</v>
+      </c>
+      <c r="E37" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="F37" s="50" t="s">
+        <v>341</v>
+      </c>
+      <c r="G37" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="51">
+        <v>46270</v>
+      </c>
+      <c r="I37" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J37" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="51">
+        <v>46270</v>
+      </c>
+      <c r="L37" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="M37" s="50"/>
+    </row>
+    <row r="38" spans="1:13" ht="62.5" thickBot="1">
+      <c r="A38" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="B38" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="C38" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="D38" s="50" t="s">
+        <v>346</v>
+      </c>
+      <c r="E38" s="50" t="s">
+        <v>349</v>
+      </c>
+      <c r="F38" s="50" t="s">
+        <v>350</v>
+      </c>
+      <c r="G38" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="51">
+        <v>46270</v>
+      </c>
+      <c r="I38" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="51">
+        <v>46270</v>
+      </c>
+      <c r="L38" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="M38" s="50"/>
+    </row>
+    <row r="39" spans="1:13" ht="62.5" thickBot="1">
+      <c r="A39" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="B39" s="50" t="s">
+        <v>343</v>
+      </c>
+      <c r="C39" s="50" t="s">
+        <v>344</v>
+      </c>
+      <c r="D39" s="50" t="s">
+        <v>347</v>
+      </c>
+      <c r="E39" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="F39" s="50" t="s">
+        <v>351</v>
+      </c>
+      <c r="G39" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="51">
+        <v>46270</v>
+      </c>
+      <c r="I39" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J39" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="51">
+        <v>46270</v>
+      </c>
+      <c r="L39" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="M39" s="50"/>
+    </row>
+    <row r="40" spans="1:13" ht="16" thickBot="1">
+      <c r="A40" s="88" t="s">
+        <v>330</v>
+      </c>
+      <c r="B40" s="89"/>
+      <c r="C40" s="89"/>
+      <c r="D40" s="89"/>
+      <c r="E40" s="89"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="89"/>
+      <c r="H40" s="89"/>
+      <c r="I40" s="89"/>
+      <c r="J40" s="89"/>
+      <c r="K40" s="89"/>
+      <c r="L40" s="89"/>
+      <c r="M40" s="90"/>
+    </row>
+    <row r="41" spans="1:13" ht="77.5">
+      <c r="A41" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="B41" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="C41" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="D41" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="E41" s="56" t="s">
+        <v>294</v>
+      </c>
+      <c r="F41" s="56" t="s">
+        <v>295</v>
+      </c>
+      <c r="G41" s="91" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="92">
+        <v>46272</v>
+      </c>
+      <c r="I41" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="J41" s="91" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="92">
+        <v>46272</v>
+      </c>
+      <c r="L41" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="M41" s="94"/>
+    </row>
+    <row r="42" spans="1:13" ht="77.5">
+      <c r="A42" s="55" t="s">
+        <v>285</v>
+      </c>
+      <c r="B42" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="C42" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="D42" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="E42" s="56" t="s">
+        <v>294</v>
+      </c>
+      <c r="F42" s="56" t="s">
+        <v>295</v>
+      </c>
+      <c r="G42" s="91" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="92">
+        <v>46272</v>
+      </c>
+      <c r="I42" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="J42" s="91" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="92">
+        <v>46272</v>
+      </c>
+      <c r="L42" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="M42" s="94"/>
+    </row>
+    <row r="43" spans="1:13" ht="77.5">
+      <c r="A43" s="55" t="s">
+        <v>290</v>
+      </c>
+      <c r="B43" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="C43" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="D43" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="E43" s="56" t="s">
+        <v>294</v>
+      </c>
+      <c r="F43" s="56" t="s">
+        <v>295</v>
+      </c>
+      <c r="G43" s="91" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="92">
+        <v>46272</v>
+      </c>
+      <c r="I43" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="J43" s="91" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="92">
+        <v>46272</v>
+      </c>
+      <c r="L43" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="M43" s="94"/>
+    </row>
+    <row r="44" spans="1:13" ht="77.5">
+      <c r="A44" s="55" t="s">
+        <v>355</v>
+      </c>
+      <c r="B44" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="C44" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="D44" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="E44" s="56" t="s">
+        <v>294</v>
+      </c>
+      <c r="F44" s="56" t="s">
+        <v>295</v>
+      </c>
+      <c r="G44" s="91" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="92">
+        <v>46272</v>
+      </c>
+      <c r="I44" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="J44" s="91" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="92">
+        <v>46272</v>
+      </c>
+      <c r="L44" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="M44" s="94"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="M33:M35"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="A36:M36"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="G41:G44 J41:J44" xr:uid="{93840138-C296-4008-BD79-94267D9889A4}">
+      <formula1>"Passed,Untested,Failed,Blocked"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7629BE57-428C-472B-A0E1-93D00EE6CD29}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="25.21875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="38.77734375" style="27" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" style="27" customWidth="1"/>
-    <col min="4" max="4" width="24.21875" style="27" customWidth="1"/>
-    <col min="5" max="5" width="33" style="27" customWidth="1"/>
-    <col min="6" max="6" width="35" style="27" customWidth="1"/>
-    <col min="7" max="7" width="17" style="27" customWidth="1"/>
-    <col min="8" max="8" width="19.77734375" style="27" customWidth="1"/>
-    <col min="9" max="9" width="20.21875" style="27" customWidth="1"/>
-    <col min="10" max="10" width="17.77734375" style="27" customWidth="1"/>
-    <col min="11" max="11" width="23.77734375" style="27" customWidth="1"/>
-    <col min="12" max="12" width="19" style="27" customWidth="1"/>
-    <col min="13" max="13" width="16.77734375" style="27" customWidth="1"/>
-    <col min="14" max="16384" width="8.77734375" style="27"/>
+    <col min="1" max="1" width="25.26953125" style="61" customWidth="1"/>
+    <col min="2" max="2" width="38.7265625" style="61" customWidth="1"/>
+    <col min="3" max="3" width="25.54296875" style="61" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" style="61" customWidth="1"/>
+    <col min="5" max="5" width="33" style="61" customWidth="1"/>
+    <col min="6" max="6" width="35" style="61" customWidth="1"/>
+    <col min="7" max="7" width="17" style="61" customWidth="1"/>
+    <col min="8" max="8" width="19.7265625" style="61" customWidth="1"/>
+    <col min="9" max="9" width="20.26953125" style="61" customWidth="1"/>
+    <col min="10" max="10" width="17.7265625" style="61" customWidth="1"/>
+    <col min="11" max="11" width="23.7265625" style="61" customWidth="1"/>
+    <col min="12" max="12" width="19" style="61" customWidth="1"/>
+    <col min="13" max="13" width="16.7265625" style="61" customWidth="1"/>
+    <col min="14" max="16384" width="8.7265625" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:6" ht="20">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="97" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="81" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
+      <c r="B2" s="107" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="28"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="41"/>
+      <c r="B3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="42" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="70">
+      <c r="B4" s="63">
         <v>5</v>
       </c>
-      <c r="C4" s="70">
+      <c r="C4" s="63">
         <v>0</v>
       </c>
-      <c r="D4" s="70">
+      <c r="D4" s="63">
         <v>0</v>
       </c>
-      <c r="E4" s="70">
+      <c r="E4" s="63">
         <v>0</v>
       </c>
-      <c r="F4" s="70">
+      <c r="F4" s="63">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="70">
+      <c r="B5" s="63">
         <v>5</v>
       </c>
-      <c r="C5" s="70">
+      <c r="C5" s="63">
         <v>0</v>
       </c>
-      <c r="D5" s="70">
+      <c r="D5" s="63">
         <v>0</v>
       </c>
-      <c r="E5" s="70">
+      <c r="E5" s="63">
         <v>0</v>
       </c>
-      <c r="F5" s="70">
+      <c r="F5" s="63">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="300.75" customHeight="1"/>
     <row r="19" spans="1:13">
-      <c r="A19" s="82" t="s">
+      <c r="A19" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="82" t="s">
+      <c r="B19" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="82" t="s">
+      <c r="C19" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="82" t="s">
+      <c r="D19" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="83" t="s">
+      <c r="E19" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="82" t="s">
+      <c r="F19" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="84" t="s">
+      <c r="G19" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="84"/>
-      <c r="I19" s="84"/>
-      <c r="J19" s="84"/>
-      <c r="K19" s="84"/>
-      <c r="L19" s="84"/>
-      <c r="M19" s="84" t="s">
+      <c r="H19" s="98"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="98"/>
+      <c r="K19" s="98"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="98" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="82"/>
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="84" t="s">
+      <c r="A20" s="105"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="84"/>
-      <c r="I20" s="84"/>
-      <c r="J20" s="84" t="s">
+      <c r="H20" s="98"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="K20" s="84"/>
-      <c r="L20" s="84"/>
-      <c r="M20" s="85"/>
+      <c r="K20" s="98"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="99"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="82"/>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="8" t="s">
+      <c r="A21" s="105"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="K21" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="L21" s="8" t="s">
+      <c r="L21" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="M21" s="85"/>
-    </row>
-    <row r="22" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A22" s="19" t="s">
-        <v>330</v>
-      </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="21"/>
+      <c r="M21" s="99"/>
+    </row>
+    <row r="22" spans="1:13" ht="16" thickBot="1">
+      <c r="A22" s="64" t="s">
+        <v>327</v>
+      </c>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="66"/>
     </row>
     <row r="23" spans="1:13" ht="106.5" customHeight="1" thickBot="1">
-      <c r="A23" s="65" t="s">
+      <c r="A23" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>298</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>299</v>
+      </c>
+      <c r="D23" s="67" t="s">
+        <v>217</v>
+      </c>
+      <c r="E23" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="F23" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="G23" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="68">
+        <v>46279</v>
+      </c>
+      <c r="I23" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J23" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="68">
+        <v>46279</v>
+      </c>
+      <c r="L23" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="67"/>
+    </row>
+    <row r="24" spans="1:13" ht="62.5" thickBot="1">
+      <c r="A24" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>304</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>305</v>
+      </c>
+      <c r="D24" s="67" t="s">
         <v>306</v>
       </c>
-      <c r="B23" s="65" t="s">
-        <v>301</v>
-      </c>
-      <c r="C23" s="65" t="s">
-        <v>302</v>
-      </c>
-      <c r="D23" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="E23" s="65" t="s">
-        <v>303</v>
-      </c>
-      <c r="F23" s="65" t="s">
-        <v>304</v>
-      </c>
-      <c r="G23" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="67">
+      <c r="E24" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="F24" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="G24" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="68">
         <v>46279</v>
       </c>
-      <c r="I23" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="J23" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="67">
+      <c r="I24" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J24" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="68">
         <v>46279</v>
       </c>
-      <c r="L23" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="M23" s="65"/>
-    </row>
-    <row r="24" spans="1:13" ht="67.8" thickBot="1">
-      <c r="A24" s="65" t="s">
-        <v>305</v>
-      </c>
-      <c r="B24" s="65" t="s">
-        <v>307</v>
-      </c>
-      <c r="C24" s="65" t="s">
-        <v>308</v>
-      </c>
-      <c r="D24" s="65" t="s">
+      <c r="L24" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M24" s="67"/>
+    </row>
+    <row r="25" spans="1:13" ht="62.5" thickBot="1">
+      <c r="A25" s="67" t="s">
         <v>309</v>
       </c>
-      <c r="E24" s="65" t="s">
+      <c r="B25" s="67" t="s">
         <v>310</v>
       </c>
-      <c r="F24" s="65" t="s">
+      <c r="C25" s="67" t="s">
         <v>311</v>
       </c>
-      <c r="G24" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="67">
+      <c r="D25" s="67" t="s">
+        <v>312</v>
+      </c>
+      <c r="E25" s="67" t="s">
+        <v>313</v>
+      </c>
+      <c r="F25" s="67" t="s">
+        <v>314</v>
+      </c>
+      <c r="G25" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="68">
         <v>46279</v>
       </c>
-      <c r="I24" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="J24" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="67">
+      <c r="I25" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J25" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="68">
         <v>46279</v>
       </c>
-      <c r="L24" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="M24" s="65"/>
-    </row>
-    <row r="25" spans="1:13" ht="67.8" thickBot="1">
-      <c r="A25" s="65" t="s">
-        <v>312</v>
-      </c>
-      <c r="B25" s="65" t="s">
-        <v>313</v>
-      </c>
-      <c r="C25" s="65" t="s">
-        <v>314</v>
-      </c>
-      <c r="D25" s="65" t="s">
+      <c r="L25" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M25" s="67"/>
+    </row>
+    <row r="26" spans="1:13" ht="16" thickBot="1">
+      <c r="A26" s="108" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" s="109"/>
+      <c r="C26" s="109"/>
+      <c r="D26" s="109"/>
+      <c r="E26" s="109"/>
+      <c r="F26" s="109"/>
+      <c r="G26" s="109"/>
+      <c r="H26" s="109"/>
+      <c r="I26" s="109"/>
+      <c r="J26" s="109"/>
+      <c r="K26" s="109"/>
+      <c r="L26" s="109"/>
+      <c r="M26" s="110"/>
+    </row>
+    <row r="27" spans="1:13" ht="62.5" thickBot="1">
+      <c r="A27" s="67" t="s">
         <v>315</v>
       </c>
-      <c r="E25" s="65" t="s">
+      <c r="B27" s="67" t="s">
         <v>316</v>
       </c>
-      <c r="F25" s="65" t="s">
+      <c r="C27" s="67" t="s">
         <v>317</v>
       </c>
-      <c r="G25" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="67">
+      <c r="D27" s="67" t="s">
+        <v>318</v>
+      </c>
+      <c r="E27" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="F27" s="67" t="s">
+        <v>320</v>
+      </c>
+      <c r="G27" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="68">
         <v>46279</v>
       </c>
-      <c r="I25" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="J25" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="67">
+      <c r="I27" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J27" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="68">
         <v>46279</v>
       </c>
-      <c r="L25" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="M25" s="65"/>
-    </row>
-    <row r="26" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A26" s="86" t="s">
-        <v>331</v>
-      </c>
-      <c r="B26" s="87"/>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="87"/>
-      <c r="G26" s="87"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="88"/>
-    </row>
-    <row r="27" spans="1:13" ht="67.8" thickBot="1">
-      <c r="A27" s="65" t="s">
-        <v>318</v>
-      </c>
-      <c r="B27" s="65" t="s">
-        <v>319</v>
-      </c>
-      <c r="C27" s="65" t="s">
-        <v>320</v>
-      </c>
-      <c r="D27" s="65" t="s">
+      <c r="L27" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27" s="69"/>
+    </row>
+    <row r="28" spans="1:13" ht="62.5" thickBot="1">
+      <c r="A28" s="67" t="s">
         <v>321</v>
       </c>
-      <c r="E27" s="65" t="s">
+      <c r="B28" s="67" t="s">
         <v>322</v>
       </c>
-      <c r="F27" s="65" t="s">
+      <c r="C28" s="67" t="s">
         <v>323</v>
       </c>
-      <c r="G27" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H27" s="67">
+      <c r="D28" s="67" t="s">
+        <v>324</v>
+      </c>
+      <c r="E28" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="F28" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="G28" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="68">
         <v>46279</v>
       </c>
-      <c r="I27" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="J27" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="67">
+      <c r="I28" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J28" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="68">
         <v>46279</v>
       </c>
-      <c r="L27" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="M27" s="44"/>
-    </row>
-    <row r="28" spans="1:13" ht="67.8" thickBot="1">
-      <c r="A28" s="65" t="s">
-        <v>324</v>
-      </c>
-      <c r="B28" s="65" t="s">
-        <v>325</v>
-      </c>
-      <c r="C28" s="65" t="s">
-        <v>326</v>
-      </c>
-      <c r="D28" s="65" t="s">
-        <v>327</v>
-      </c>
-      <c r="E28" s="65" t="s">
-        <v>328</v>
-      </c>
-      <c r="F28" s="65" t="s">
-        <v>329</v>
-      </c>
-      <c r="G28" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H28" s="67">
-        <v>46279</v>
-      </c>
-      <c r="I28" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="J28" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" s="67">
-        <v>46279</v>
-      </c>
-      <c r="L28" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="M28" s="44"/>
+      <c r="L28" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="M28" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -3440,909 +4168,909 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N77"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" style="27" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" style="27" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" style="27" customWidth="1"/>
-    <col min="4" max="4" width="39.44140625" style="27" customWidth="1"/>
-    <col min="5" max="5" width="29.5546875" style="27" customWidth="1"/>
-    <col min="6" max="6" width="28.77734375" style="27" customWidth="1"/>
-    <col min="7" max="7" width="26.21875" style="27" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" style="27" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" style="27" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.21875" style="27"/>
+    <col min="1" max="1" width="23.7265625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="51.54296875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="39.453125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="29.54296875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="28.7265625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="26.26953125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="18.26953125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="18.7265625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.26953125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="101" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="91" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-    </row>
-    <row r="3" spans="1:12" ht="17.399999999999999" thickBot="1">
-      <c r="A3" s="28"/>
-      <c r="B3" s="17" t="s">
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+    </row>
+    <row r="3" spans="1:12" ht="17" thickBot="1">
+      <c r="A3" s="12"/>
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="61"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-    </row>
-    <row r="4" spans="1:12" ht="17.399999999999999" thickBot="1">
-      <c r="A4" s="62" t="s">
+      <c r="G3" s="25"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+    </row>
+    <row r="4" spans="1:12" ht="17" thickBot="1">
+      <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="63">
+      <c r="B4" s="27">
         <v>5</v>
       </c>
-      <c r="C4" s="63">
+      <c r="C4" s="27">
         <v>0</v>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="27">
         <v>0</v>
       </c>
-      <c r="E4" s="63">
+      <c r="E4" s="27">
         <v>0</v>
       </c>
-      <c r="F4" s="64">
+      <c r="F4" s="28">
         <v>5</v>
       </c>
-      <c r="G4" s="60"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-    </row>
-    <row r="5" spans="1:12" ht="17.399999999999999" thickBot="1">
-      <c r="A5" s="62" t="s">
+      <c r="G4" s="24"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+    </row>
+    <row r="5" spans="1:12" ht="17" thickBot="1">
+      <c r="A5" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="63">
+      <c r="B5" s="27">
         <v>5</v>
       </c>
-      <c r="C5" s="63">
+      <c r="C5" s="27">
         <v>0</v>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="27">
         <v>0</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="27">
         <v>0</v>
       </c>
-      <c r="F5" s="64">
+      <c r="F5" s="28">
         <v>5</v>
       </c>
-      <c r="G5" s="60"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="199.5" customHeight="1"/>
     <row r="31" spans="1:13" ht="42.75" customHeight="1">
-      <c r="A31" s="82" t="s">
+      <c r="A31" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="82" t="s">
+      <c r="B31" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="82" t="s">
+      <c r="C31" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="82" t="s">
+      <c r="D31" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="83" t="s">
+      <c r="E31" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="82" t="s">
+      <c r="F31" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="84" t="s">
+      <c r="G31" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="84"/>
-      <c r="I31" s="84"/>
-      <c r="J31" s="84"/>
-      <c r="K31" s="84"/>
-      <c r="L31" s="84"/>
-      <c r="M31" s="84" t="s">
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="98" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="82"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="84" t="s">
+      <c r="A32" s="105"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="84"/>
-      <c r="I32" s="84"/>
-      <c r="J32" s="84" t="s">
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="84"/>
-      <c r="L32" s="84"/>
-      <c r="M32" s="85"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="99"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="82"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="8" t="s">
+      <c r="A33" s="105"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="K33" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="8" t="s">
+      <c r="L33" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="85"/>
+      <c r="M33" s="99"/>
     </row>
     <row r="34" spans="1:14" ht="66.75" customHeight="1" thickBot="1">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="65"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="65"/>
+      <c r="H34" s="65"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
+      <c r="M34" s="66"/>
+    </row>
+    <row r="35" spans="1:14" ht="94.5" customHeight="1" thickBot="1">
+      <c r="A35" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="21"/>
-    </row>
-    <row r="35" spans="1:14" ht="94.5" customHeight="1" thickBot="1">
-      <c r="A35" s="65" t="s">
+      <c r="B35" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" s="67" t="s">
+        <v>82</v>
+      </c>
+      <c r="F35" s="67" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="68">
+        <v>46268</v>
+      </c>
+      <c r="I35" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J35" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="68">
+        <v>46268</v>
+      </c>
+      <c r="L35" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35" s="67"/>
+    </row>
+    <row r="36" spans="1:14" ht="62.5" thickBot="1">
+      <c r="A36" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="66" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65" t="s">
+      <c r="B36" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E35" s="65" t="s">
+      <c r="E36" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="G36" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="68">
+        <v>46268</v>
+      </c>
+      <c r="I36" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J36" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="68">
+        <v>46268</v>
+      </c>
+      <c r="L36" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M36" s="67"/>
+    </row>
+    <row r="37" spans="1:14" ht="47" thickBot="1">
+      <c r="A37" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="67"/>
+      <c r="D37" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="F35" s="65" t="s">
-        <v>84</v>
-      </c>
-      <c r="G35" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="67">
+      <c r="F37" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="G37" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="68">
         <v>46268</v>
       </c>
-      <c r="I35" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="J35" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="67">
+      <c r="I37" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J37" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="68">
         <v>46268</v>
       </c>
-      <c r="L35" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="M35" s="65"/>
-    </row>
-    <row r="36" spans="1:14" ht="67.8" thickBot="1">
-      <c r="A36" s="65" t="s">
+      <c r="L37" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M37" s="67"/>
+    </row>
+    <row r="38" spans="1:14" ht="47" thickBot="1">
+      <c r="A38" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" s="70" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="67"/>
+      <c r="D38" s="67" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="67" t="s">
+        <v>85</v>
+      </c>
+      <c r="F38" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="G38" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="68">
+        <v>46268</v>
+      </c>
+      <c r="I38" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="68">
+        <v>46268</v>
+      </c>
+      <c r="L38" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M38" s="67"/>
+    </row>
+    <row r="39" spans="1:14" ht="47" thickBot="1">
+      <c r="A39" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="67"/>
+      <c r="D39" s="67" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="F39" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="G39" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="68">
+        <v>46268</v>
+      </c>
+      <c r="I39" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J39" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="68">
+        <v>46268</v>
+      </c>
+      <c r="L39" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M39" s="67"/>
+    </row>
+    <row r="40" spans="1:14" ht="47" thickBot="1">
+      <c r="A40" s="67" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="F40" s="67" t="s">
+        <v>75</v>
+      </c>
+      <c r="G40" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="68">
+        <v>46268</v>
+      </c>
+      <c r="I40" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J40" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="68">
+        <v>46268</v>
+      </c>
+      <c r="L40" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M40" s="67"/>
+    </row>
+    <row r="41" spans="1:14" ht="47" thickBot="1">
+      <c r="A41" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="70" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="67"/>
+      <c r="D41" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="E41" s="67" t="s">
+        <v>90</v>
+      </c>
+      <c r="F41" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="G41" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" s="68">
+        <v>46268</v>
+      </c>
+      <c r="I41" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J41" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="68">
+        <v>46269</v>
+      </c>
+      <c r="L41" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M41" s="67" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="17" thickBot="1">
+      <c r="A42" s="108" t="s">
+        <v>329</v>
+      </c>
+      <c r="B42" s="109"/>
+      <c r="C42" s="109"/>
+      <c r="D42" s="109"/>
+      <c r="E42" s="109"/>
+      <c r="F42" s="109"/>
+      <c r="G42" s="109"/>
+      <c r="H42" s="109"/>
+      <c r="I42" s="109"/>
+      <c r="J42" s="109"/>
+      <c r="K42" s="109"/>
+      <c r="L42" s="109"/>
+      <c r="M42" s="110"/>
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" spans="1:14" ht="127.5" customHeight="1" thickBot="1">
+      <c r="A43" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="66" t="s">
+      <c r="B43" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="65"/>
-      <c r="D36" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="E36" s="65" t="s">
-        <v>85</v>
-      </c>
-      <c r="F36" s="65" t="s">
-        <v>85</v>
-      </c>
-      <c r="G36" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="67">
+      <c r="C43" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="67" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="F43" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="G43" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="68">
         <v>46268</v>
       </c>
-      <c r="I36" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="J36" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="67">
+      <c r="I43" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J43" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="68">
         <v>46268</v>
       </c>
-      <c r="L36" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="M36" s="65"/>
-    </row>
-    <row r="37" spans="1:14" ht="51" thickBot="1">
-      <c r="A37" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="65"/>
-      <c r="D37" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="E37" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" s="65" t="s">
-        <v>68</v>
-      </c>
-      <c r="G37" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="67">
+      <c r="L43" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M43" s="69"/>
+    </row>
+    <row r="44" spans="1:14" ht="31.5" thickBot="1">
+      <c r="A44" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="67" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="67" t="s">
+        <v>96</v>
+      </c>
+      <c r="D44" s="67" t="s">
+        <v>97</v>
+      </c>
+      <c r="E44" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="F44" s="67" t="s">
+        <v>99</v>
+      </c>
+      <c r="G44" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="68">
         <v>46268</v>
       </c>
-      <c r="I37" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="J37" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" s="67">
+      <c r="I44" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J44" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="68">
         <v>46268</v>
       </c>
-      <c r="L37" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="M37" s="65"/>
-    </row>
-    <row r="38" spans="1:14" ht="51" thickBot="1">
-      <c r="A38" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="66" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="65"/>
-      <c r="D38" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="E38" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="F38" s="65" t="s">
-        <v>88</v>
-      </c>
-      <c r="G38" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="67">
+      <c r="L44" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M44" s="69"/>
+    </row>
+    <row r="45" spans="1:14" ht="165" customHeight="1" thickBot="1">
+      <c r="A45" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="E45" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="F45" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="G45" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="68">
         <v>46268</v>
       </c>
-      <c r="I38" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="J38" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="67">
+      <c r="I45" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J45" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" s="68">
         <v>46268</v>
       </c>
-      <c r="L38" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="M38" s="65"/>
-    </row>
-    <row r="39" spans="1:14" ht="51" thickBot="1">
-      <c r="A39" s="65" t="s">
-        <v>71</v>
-      </c>
-      <c r="B39" s="66" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" s="65"/>
-      <c r="D39" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="E39" s="65" t="s">
-        <v>89</v>
-      </c>
-      <c r="F39" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="G39" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="67">
+      <c r="L45" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M45" s="69"/>
+    </row>
+    <row r="46" spans="1:14" ht="165" customHeight="1" thickBot="1">
+      <c r="A46" s="67" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="67" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="F46" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="G46" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H46" s="68">
         <v>46268</v>
       </c>
-      <c r="I39" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="J39" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="67">
+      <c r="I46" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J46" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" s="68">
         <v>46268</v>
       </c>
-      <c r="L39" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="M39" s="65"/>
-    </row>
-    <row r="40" spans="1:14" ht="51" thickBot="1">
-      <c r="A40" s="65" t="s">
-        <v>74</v>
-      </c>
-      <c r="B40" s="66" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" s="65"/>
-      <c r="D40" s="65" t="s">
-        <v>76</v>
-      </c>
-      <c r="E40" s="65" t="s">
-        <v>90</v>
-      </c>
-      <c r="F40" s="65" t="s">
-        <v>77</v>
-      </c>
-      <c r="G40" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="67">
-        <v>46268</v>
-      </c>
-      <c r="I40" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="J40" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="67">
-        <v>46268</v>
-      </c>
-      <c r="L40" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="M40" s="65"/>
-    </row>
-    <row r="41" spans="1:14" ht="51" thickBot="1">
-      <c r="A41" s="65" t="s">
-        <v>78</v>
-      </c>
-      <c r="B41" s="66" t="s">
-        <v>91</v>
-      </c>
-      <c r="C41" s="65"/>
-      <c r="D41" s="65" t="s">
-        <v>79</v>
-      </c>
-      <c r="E41" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="F41" s="65" t="s">
-        <v>93</v>
-      </c>
-      <c r="G41" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="H41" s="67">
-        <v>46268</v>
-      </c>
-      <c r="I41" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="J41" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" s="67">
-        <v>46269</v>
-      </c>
-      <c r="L41" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="M41" s="65" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="17.399999999999999" thickBot="1">
-      <c r="A42" s="86" t="s">
-        <v>332</v>
-      </c>
-      <c r="B42" s="87"/>
-      <c r="C42" s="87"/>
-      <c r="D42" s="87"/>
-      <c r="E42" s="87"/>
-      <c r="F42" s="87"/>
-      <c r="G42" s="87"/>
-      <c r="H42" s="87"/>
-      <c r="I42" s="87"/>
-      <c r="J42" s="87"/>
-      <c r="K42" s="87"/>
-      <c r="L42" s="87"/>
-      <c r="M42" s="88"/>
-      <c r="N42" s="1"/>
-    </row>
-    <row r="43" spans="1:14" ht="127.5" customHeight="1" thickBot="1">
-      <c r="A43" s="65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B43" s="65" t="s">
-        <v>56</v>
-      </c>
-      <c r="C43" s="65" t="s">
-        <v>95</v>
-      </c>
-      <c r="D43" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="E43" s="65" t="s">
-        <v>96</v>
-      </c>
-      <c r="F43" s="65" t="s">
-        <v>97</v>
-      </c>
-      <c r="G43" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" s="67">
-        <v>46268</v>
-      </c>
-      <c r="I43" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="J43" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="67">
-        <v>46268</v>
-      </c>
-      <c r="L43" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="M43" s="44"/>
-    </row>
-    <row r="44" spans="1:14" ht="51" thickBot="1">
-      <c r="A44" s="65" t="s">
-        <v>57</v>
-      </c>
-      <c r="B44" s="65" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" s="65" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="65" t="s">
-        <v>99</v>
-      </c>
-      <c r="E44" s="65" t="s">
-        <v>100</v>
-      </c>
-      <c r="F44" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="G44" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" s="67">
-        <v>46268</v>
-      </c>
-      <c r="I44" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="J44" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="67">
-        <v>46268</v>
-      </c>
-      <c r="L44" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="M44" s="44"/>
-    </row>
-    <row r="45" spans="1:14" ht="165" customHeight="1" thickBot="1">
-      <c r="A45" s="65" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45" s="65" t="s">
-        <v>60</v>
-      </c>
-      <c r="C45" s="65" t="s">
-        <v>102</v>
-      </c>
-      <c r="D45" s="65" t="s">
-        <v>103</v>
-      </c>
-      <c r="E45" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="F45" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="G45" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="67">
-        <v>46268</v>
-      </c>
-      <c r="I45" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="J45" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K45" s="67">
-        <v>46268</v>
-      </c>
-      <c r="L45" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="M45" s="44"/>
-    </row>
-    <row r="46" spans="1:14" ht="165" customHeight="1" thickBot="1">
-      <c r="A46" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" s="65" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" s="65" t="s">
-        <v>83</v>
-      </c>
-      <c r="E46" s="65" t="s">
-        <v>107</v>
-      </c>
-      <c r="F46" s="65" t="s">
-        <v>108</v>
-      </c>
-      <c r="G46" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H46" s="67">
-        <v>46268</v>
-      </c>
-      <c r="I46" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="J46" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K46" s="67">
-        <v>46268</v>
-      </c>
-      <c r="L46" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="M46" s="44"/>
+      <c r="L46" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M46" s="69"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="60"/>
-      <c r="D54" s="60"/>
-      <c r="E54" s="60"/>
-      <c r="F54" s="60"/>
-      <c r="G54" s="60"/>
-      <c r="H54" s="60"/>
-      <c r="I54" s="60"/>
-      <c r="J54" s="60"/>
-      <c r="K54" s="60"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="24"/>
     </row>
     <row r="55" spans="3:11">
-      <c r="C55" s="60"/>
-      <c r="D55" s="61"/>
-      <c r="E55" s="61"/>
-      <c r="F55" s="61"/>
-      <c r="G55" s="61"/>
-      <c r="H55" s="61"/>
-      <c r="I55" s="61"/>
-      <c r="J55" s="61"/>
-      <c r="K55" s="61"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
+      <c r="J55" s="25"/>
+      <c r="K55" s="25"/>
     </row>
     <row r="56" spans="3:11" ht="28.5" customHeight="1">
-      <c r="C56" s="93"/>
-      <c r="D56" s="93"/>
-      <c r="E56" s="93"/>
-      <c r="F56" s="93"/>
-      <c r="G56" s="57"/>
-      <c r="H56" s="57"/>
-      <c r="I56" s="93"/>
-      <c r="J56" s="93"/>
-      <c r="K56" s="93"/>
+      <c r="C56" s="113"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="113"/>
+      <c r="F56" s="113"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="113"/>
+      <c r="J56" s="113"/>
+      <c r="K56" s="113"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="93"/>
-      <c r="D57" s="93"/>
-      <c r="E57" s="93"/>
-      <c r="F57" s="93"/>
-      <c r="G57" s="68"/>
-      <c r="H57" s="68"/>
-      <c r="I57" s="93"/>
-      <c r="J57" s="93"/>
-      <c r="K57" s="93"/>
+      <c r="C57" s="113"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="113"/>
+      <c r="F57" s="113"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="113"/>
+      <c r="J57" s="113"/>
+      <c r="K57" s="113"/>
     </row>
     <row r="58" spans="3:11" ht="57" customHeight="1">
-      <c r="C58" s="93"/>
-      <c r="D58" s="93"/>
-      <c r="E58" s="93"/>
-      <c r="F58" s="93"/>
-      <c r="G58" s="57"/>
-      <c r="H58" s="57"/>
-      <c r="I58" s="93"/>
-      <c r="J58" s="93"/>
-      <c r="K58" s="93"/>
+      <c r="C58" s="113"/>
+      <c r="D58" s="113"/>
+      <c r="E58" s="113"/>
+      <c r="F58" s="113"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="113"/>
+      <c r="J58" s="113"/>
+      <c r="K58" s="113"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="61"/>
-      <c r="D59" s="61"/>
-      <c r="E59" s="61"/>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="61"/>
-      <c r="I59" s="61"/>
-      <c r="J59" s="61"/>
-      <c r="K59" s="61"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
+      <c r="H59" s="25"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="25"/>
+      <c r="K59" s="25"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="60"/>
-      <c r="D60" s="61"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="61"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="61"/>
-      <c r="I60" s="61"/>
-      <c r="J60" s="61"/>
-      <c r="K60" s="61"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="25"/>
+      <c r="J60" s="25"/>
+      <c r="K60" s="25"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="93"/>
-      <c r="D61" s="93"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="93"/>
-      <c r="G61" s="57"/>
-      <c r="H61" s="57"/>
-      <c r="I61" s="93"/>
-      <c r="J61" s="93"/>
-      <c r="K61" s="93"/>
+      <c r="C61" s="113"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="113"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="21"/>
+      <c r="I61" s="113"/>
+      <c r="J61" s="113"/>
+      <c r="K61" s="113"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="93"/>
-      <c r="D62" s="93"/>
-      <c r="E62" s="68"/>
-      <c r="F62" s="93"/>
-      <c r="G62" s="68"/>
-      <c r="H62" s="68"/>
-      <c r="I62" s="93"/>
-      <c r="J62" s="93"/>
-      <c r="K62" s="93"/>
+      <c r="C62" s="113"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="29"/>
+      <c r="F62" s="113"/>
+      <c r="G62" s="29"/>
+      <c r="H62" s="29"/>
+      <c r="I62" s="113"/>
+      <c r="J62" s="113"/>
+      <c r="K62" s="113"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="93"/>
-      <c r="D63" s="93"/>
-      <c r="E63" s="57"/>
-      <c r="F63" s="93"/>
-      <c r="G63" s="57"/>
-      <c r="H63" s="57"/>
-      <c r="I63" s="93"/>
-      <c r="J63" s="93"/>
-      <c r="K63" s="93"/>
+      <c r="C63" s="113"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="113"/>
+      <c r="G63" s="21"/>
+      <c r="H63" s="21"/>
+      <c r="I63" s="113"/>
+      <c r="J63" s="113"/>
+      <c r="K63" s="113"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="93"/>
-      <c r="D64" s="93"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="93"/>
-      <c r="G64" s="68"/>
-      <c r="H64" s="68"/>
-      <c r="I64" s="93"/>
-      <c r="J64" s="93"/>
-      <c r="K64" s="93"/>
+      <c r="C64" s="113"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="113"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="113"/>
+      <c r="J64" s="113"/>
+      <c r="K64" s="113"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="93"/>
-      <c r="D65" s="93"/>
-      <c r="E65" s="57"/>
-      <c r="F65" s="93"/>
-      <c r="G65" s="57"/>
-      <c r="H65" s="57"/>
-      <c r="I65" s="93"/>
-      <c r="J65" s="93"/>
-      <c r="K65" s="93"/>
+      <c r="C65" s="113"/>
+      <c r="D65" s="113"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="113"/>
+      <c r="G65" s="21"/>
+      <c r="H65" s="21"/>
+      <c r="I65" s="113"/>
+      <c r="J65" s="113"/>
+      <c r="K65" s="113"/>
     </row>
     <row r="66" spans="3:11" ht="28.5" customHeight="1">
-      <c r="C66" s="93"/>
-      <c r="D66" s="93"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="93"/>
-      <c r="G66" s="68"/>
-      <c r="H66" s="68"/>
-      <c r="I66" s="93"/>
-      <c r="J66" s="93"/>
-      <c r="K66" s="93"/>
+      <c r="C66" s="113"/>
+      <c r="D66" s="113"/>
+      <c r="E66" s="29"/>
+      <c r="F66" s="113"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="29"/>
+      <c r="I66" s="113"/>
+      <c r="J66" s="113"/>
+      <c r="K66" s="113"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="93"/>
-      <c r="D67" s="93"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="93"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="93"/>
-      <c r="J67" s="93"/>
-      <c r="K67" s="93"/>
+      <c r="C67" s="113"/>
+      <c r="D67" s="113"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="113"/>
+      <c r="G67" s="21"/>
+      <c r="H67" s="21"/>
+      <c r="I67" s="113"/>
+      <c r="J67" s="113"/>
+      <c r="K67" s="113"/>
     </row>
     <row r="68" spans="3:11" ht="40.5" customHeight="1">
-      <c r="C68" s="93"/>
-      <c r="D68" s="93"/>
-      <c r="E68" s="57"/>
-      <c r="F68" s="93"/>
-      <c r="G68" s="93"/>
-      <c r="H68" s="93"/>
-      <c r="I68" s="93"/>
-      <c r="J68" s="93"/>
-      <c r="K68" s="93"/>
+      <c r="C68" s="113"/>
+      <c r="D68" s="113"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="113"/>
+      <c r="G68" s="113"/>
+      <c r="H68" s="113"/>
+      <c r="I68" s="113"/>
+      <c r="J68" s="113"/>
+      <c r="K68" s="113"/>
     </row>
     <row r="69" spans="3:11" ht="28.5" customHeight="1">
-      <c r="C69" s="93"/>
-      <c r="D69" s="93"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="93"/>
-      <c r="G69" s="93"/>
-      <c r="H69" s="93"/>
-      <c r="I69" s="93"/>
-      <c r="J69" s="93"/>
-      <c r="K69" s="93"/>
+      <c r="C69" s="113"/>
+      <c r="D69" s="113"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="113"/>
+      <c r="G69" s="113"/>
+      <c r="H69" s="113"/>
+      <c r="I69" s="113"/>
+      <c r="J69" s="113"/>
+      <c r="K69" s="113"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="93"/>
-      <c r="D70" s="93"/>
-      <c r="E70" s="57"/>
-      <c r="F70" s="93"/>
-      <c r="G70" s="93"/>
-      <c r="H70" s="93"/>
-      <c r="I70" s="93"/>
-      <c r="J70" s="93"/>
-      <c r="K70" s="93"/>
+      <c r="C70" s="113"/>
+      <c r="D70" s="113"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="113"/>
+      <c r="G70" s="113"/>
+      <c r="H70" s="113"/>
+      <c r="I70" s="113"/>
+      <c r="J70" s="113"/>
+      <c r="K70" s="113"/>
     </row>
     <row r="71" spans="3:11" ht="42.75" customHeight="1">
-      <c r="C71" s="93"/>
-      <c r="D71" s="93"/>
-      <c r="E71" s="57"/>
-      <c r="F71" s="93"/>
-      <c r="G71" s="93"/>
-      <c r="H71" s="93"/>
-      <c r="I71" s="93"/>
-      <c r="J71" s="93"/>
-      <c r="K71" s="93"/>
+      <c r="C71" s="113"/>
+      <c r="D71" s="113"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="113"/>
+      <c r="G71" s="113"/>
+      <c r="H71" s="113"/>
+      <c r="I71" s="113"/>
+      <c r="J71" s="113"/>
+      <c r="K71" s="113"/>
     </row>
     <row r="72" spans="3:11" ht="28.5" customHeight="1">
-      <c r="C72" s="93"/>
-      <c r="D72" s="93"/>
-      <c r="E72" s="68"/>
-      <c r="F72" s="93"/>
-      <c r="G72" s="93"/>
-      <c r="H72" s="93"/>
-      <c r="I72" s="93"/>
-      <c r="J72" s="93"/>
-      <c r="K72" s="93"/>
+      <c r="C72" s="113"/>
+      <c r="D72" s="113"/>
+      <c r="E72" s="29"/>
+      <c r="F72" s="113"/>
+      <c r="G72" s="113"/>
+      <c r="H72" s="113"/>
+      <c r="I72" s="113"/>
+      <c r="J72" s="113"/>
+      <c r="K72" s="113"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="93"/>
-      <c r="D73" s="93"/>
-      <c r="E73" s="57"/>
-      <c r="F73" s="93"/>
-      <c r="G73" s="93"/>
-      <c r="H73" s="93"/>
-      <c r="I73" s="93"/>
-      <c r="J73" s="93"/>
-      <c r="K73" s="93"/>
+      <c r="C73" s="113"/>
+      <c r="D73" s="113"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="113"/>
+      <c r="G73" s="113"/>
+      <c r="H73" s="113"/>
+      <c r="I73" s="113"/>
+      <c r="J73" s="113"/>
+      <c r="K73" s="113"/>
     </row>
     <row r="74" spans="3:11" ht="42.75" customHeight="1">
-      <c r="C74" s="93"/>
-      <c r="D74" s="93"/>
-      <c r="E74" s="68"/>
-      <c r="F74" s="93"/>
-      <c r="G74" s="93"/>
-      <c r="H74" s="93"/>
-      <c r="I74" s="93"/>
-      <c r="J74" s="93"/>
-      <c r="K74" s="93"/>
+      <c r="C74" s="113"/>
+      <c r="D74" s="113"/>
+      <c r="E74" s="29"/>
+      <c r="F74" s="113"/>
+      <c r="G74" s="113"/>
+      <c r="H74" s="113"/>
+      <c r="I74" s="113"/>
+      <c r="J74" s="113"/>
+      <c r="K74" s="113"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="93"/>
-      <c r="D75" s="93"/>
-      <c r="E75" s="57"/>
-      <c r="F75" s="93"/>
-      <c r="G75" s="93"/>
-      <c r="H75" s="93"/>
-      <c r="I75" s="93"/>
-      <c r="J75" s="93"/>
-      <c r="K75" s="93"/>
+      <c r="C75" s="113"/>
+      <c r="D75" s="113"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="113"/>
+      <c r="G75" s="113"/>
+      <c r="H75" s="113"/>
+      <c r="I75" s="113"/>
+      <c r="J75" s="113"/>
+      <c r="K75" s="113"/>
     </row>
     <row r="77" spans="3:11" ht="28.5" customHeight="1"/>
   </sheetData>
@@ -4396,864 +5124,864 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R67"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" style="27" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" style="27" customWidth="1"/>
-    <col min="3" max="3" width="19.77734375" style="27" customWidth="1"/>
-    <col min="4" max="4" width="21.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5546875" style="27" customWidth="1"/>
-    <col min="6" max="6" width="28.77734375" style="27" customWidth="1"/>
-    <col min="7" max="7" width="26.21875" style="27" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" style="27" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" style="27" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.21875" style="27"/>
+    <col min="1" max="1" width="23.7265625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.54296875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="28.7265625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="26.26953125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="18.26953125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="18.7265625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.26953125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="89" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="96"/>
+      <c r="B1" s="101" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="116"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="91" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="97"/>
+      <c r="B2" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="117"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="28"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="12">
         <v>8</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="12">
         <v>1</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="12">
         <v>0</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="12">
         <v>0</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="12">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="14">
         <v>9</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="12">
         <v>0</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="12">
         <v>0</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="12">
         <v>0</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="12">
         <f>B5</f>
         <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="82" t="s">
+      <c r="A31" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="82" t="s">
+      <c r="B31" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="82" t="s">
+      <c r="C31" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="82" t="s">
+      <c r="D31" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="83" t="s">
+      <c r="E31" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="82" t="s">
+      <c r="F31" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="84" t="s">
+      <c r="G31" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="84"/>
-      <c r="I31" s="84"/>
-      <c r="J31" s="84"/>
-      <c r="K31" s="84"/>
-      <c r="L31" s="84"/>
-      <c r="M31" s="84" t="s">
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="98" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="82"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="84" t="s">
+      <c r="A32" s="105"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="84"/>
-      <c r="I32" s="84"/>
-      <c r="J32" s="84" t="s">
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="84"/>
-      <c r="L32" s="84"/>
-      <c r="M32" s="85"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="99"/>
     </row>
     <row r="33" spans="1:18">
-      <c r="A33" s="82"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="8" t="s">
+      <c r="A33" s="105"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="K33" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="8" t="s">
+      <c r="L33" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="85"/>
-    </row>
-    <row r="34" spans="1:18" ht="17.399999999999999" thickBot="1">
-      <c r="A34" s="98" t="s">
-        <v>334</v>
-      </c>
-      <c r="B34" s="98"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="98"/>
-      <c r="H34" s="98"/>
-      <c r="I34" s="98"/>
-      <c r="J34" s="98"/>
-      <c r="K34" s="98"/>
-      <c r="L34" s="98"/>
-      <c r="M34" s="98"/>
-    </row>
-    <row r="35" spans="1:18" ht="51" thickBot="1">
-      <c r="A35" s="47" t="s">
+      <c r="M33" s="99"/>
+    </row>
+    <row r="34" spans="1:18" ht="17" thickBot="1">
+      <c r="A34" s="100" t="s">
+        <v>331</v>
+      </c>
+      <c r="B34" s="100"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="100"/>
+      <c r="G34" s="100"/>
+      <c r="H34" s="100"/>
+      <c r="I34" s="100"/>
+      <c r="J34" s="100"/>
+      <c r="K34" s="100"/>
+      <c r="L34" s="100"/>
+      <c r="M34" s="100"/>
+    </row>
+    <row r="35" spans="1:18" ht="47" thickBot="1">
+      <c r="A35" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="47" t="s">
+      <c r="E35" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47" t="s">
+      <c r="F35" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="E35" s="47" t="s">
+      <c r="G35" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="51">
+        <v>46270</v>
+      </c>
+      <c r="I35" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J35" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="51">
+        <v>46270</v>
+      </c>
+      <c r="L35" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35" s="50"/>
+    </row>
+    <row r="36" spans="1:18" ht="47" thickBot="1">
+      <c r="A36" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="F35" s="47" t="s">
+      <c r="B36" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="G35" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="48">
+      <c r="C36" s="50"/>
+      <c r="D36" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="F36" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="51">
         <v>46270</v>
       </c>
-      <c r="I35" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="J35" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="48">
+      <c r="I36" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J36" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="51">
         <v>46270</v>
       </c>
-      <c r="L35" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="M35" s="47"/>
-    </row>
-    <row r="36" spans="1:18" ht="51" thickBot="1">
-      <c r="A36" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="B36" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47" t="s">
+      <c r="L36" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M36" s="50"/>
+    </row>
+    <row r="37" spans="1:18" ht="47" thickBot="1">
+      <c r="A37" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="E36" s="47" t="s">
+      <c r="B37" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="F36" s="47" t="s">
+      <c r="C37" s="50"/>
+      <c r="D37" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="G36" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="48">
+      <c r="E37" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="F37" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="G37" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="51">
         <v>46270</v>
       </c>
-      <c r="I36" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="J36" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="48">
+      <c r="I37" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J37" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="51">
         <v>46270</v>
       </c>
-      <c r="L36" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="M36" s="47"/>
-    </row>
-    <row r="37" spans="1:18" ht="67.8" thickBot="1">
-      <c r="A37" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="B37" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47" t="s">
+      <c r="L37" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="M37" s="50"/>
+    </row>
+    <row r="38" spans="1:18" ht="47" thickBot="1">
+      <c r="A38" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="E37" s="47" t="s">
+      <c r="B38" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="F37" s="47" t="s">
+      <c r="C38" s="50"/>
+      <c r="D38" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="48">
+      <c r="F38" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="G38" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="51">
         <v>46270</v>
       </c>
-      <c r="I37" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="J37" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" s="48">
+      <c r="I38" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="51">
         <v>46270</v>
       </c>
-      <c r="L37" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="M37" s="47"/>
-    </row>
-    <row r="38" spans="1:18" ht="67.8" thickBot="1">
-      <c r="A38" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="B38" s="47" t="s">
+      <c r="L38" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="M38" s="50"/>
+    </row>
+    <row r="39" spans="1:18" ht="47" thickBot="1">
+      <c r="A39" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47" t="s">
-        <v>64</v>
-      </c>
-      <c r="E38" s="47" t="s">
+      <c r="B39" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="F38" s="47" t="s">
+      <c r="C39" s="50"/>
+      <c r="D39" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="G38" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="48">
+      <c r="E39" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="F39" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="G39" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="51">
         <v>46270</v>
       </c>
-      <c r="I38" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="J38" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="48">
+      <c r="I39" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J39" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="51">
         <v>46270</v>
       </c>
-      <c r="L38" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="M38" s="47"/>
-    </row>
-    <row r="39" spans="1:18" ht="51" thickBot="1">
-      <c r="A39" s="47" t="s">
-        <v>129</v>
-      </c>
-      <c r="B39" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="C39" s="47"/>
-      <c r="D39" s="47" t="s">
+      <c r="L39" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M39" s="50"/>
+    </row>
+    <row r="40" spans="1:18" ht="17" thickBot="1">
+      <c r="A40" s="52" t="s">
+        <v>330</v>
+      </c>
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="53"/>
+      <c r="M40" s="54"/>
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" spans="1:18" ht="77.25" customHeight="1" thickBot="1">
+      <c r="A41" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="E39" s="47" t="s">
+      <c r="B41" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="F39" s="47" t="s">
+      <c r="C41" s="71" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" s="71" t="s">
         <v>133</v>
       </c>
-      <c r="G39" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="48">
+      <c r="E41" s="71" t="s">
+        <v>134</v>
+      </c>
+      <c r="F41" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="G41" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="72">
         <v>46270</v>
       </c>
-      <c r="I39" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="J39" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="48">
+      <c r="I41" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J41" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="72">
         <v>46270</v>
       </c>
-      <c r="L39" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="M39" s="47"/>
-    </row>
-    <row r="40" spans="1:18" ht="17.399999999999999" thickBot="1">
-      <c r="A40" s="49" t="s">
-        <v>333</v>
-      </c>
-      <c r="B40" s="50"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="50"/>
-      <c r="I40" s="50"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="50"/>
-      <c r="L40" s="50"/>
-      <c r="M40" s="51"/>
-      <c r="N40" s="1"/>
-    </row>
-    <row r="41" spans="1:18" ht="77.25" customHeight="1" thickBot="1">
-      <c r="A41" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="B41" s="52" t="s">
-        <v>135</v>
-      </c>
-      <c r="C41" s="52" t="s">
+      <c r="L41" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="M41" s="71"/>
+    </row>
+    <row r="42" spans="1:18" ht="65.25" customHeight="1" thickBot="1">
+      <c r="A42" s="71" t="s">
+        <v>136</v>
+      </c>
+      <c r="B42" s="71" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="71" t="s">
+        <v>153</v>
+      </c>
+      <c r="D42" s="71" t="s">
+        <v>138</v>
+      </c>
+      <c r="E42" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="F42" s="71" t="s">
+        <v>140</v>
+      </c>
+      <c r="G42" s="71" t="s">
+        <v>78</v>
+      </c>
+      <c r="H42" s="72">
+        <v>46270</v>
+      </c>
+      <c r="I42" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J42" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="72">
+        <v>46271</v>
+      </c>
+      <c r="L42" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M42" s="71" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="66" customHeight="1" thickBot="1">
+      <c r="A43" s="71" t="s">
+        <v>142</v>
+      </c>
+      <c r="B43" s="71" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" s="73" t="s">
+        <v>154</v>
+      </c>
+      <c r="D43" s="71" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" s="71" t="s">
+        <v>145</v>
+      </c>
+      <c r="F43" s="71" t="s">
+        <v>146</v>
+      </c>
+      <c r="G43" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="72">
+        <v>46270</v>
+      </c>
+      <c r="I43" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="J43" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="72">
+        <v>46270</v>
+      </c>
+      <c r="L43" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="M43" s="71"/>
+    </row>
+    <row r="44" spans="1:18" ht="58.5" customHeight="1" thickBot="1">
+      <c r="A44" s="74" t="s">
+        <v>147</v>
+      </c>
+      <c r="B44" s="74" t="s">
+        <v>148</v>
+      </c>
+      <c r="C44" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="D41" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="E41" s="52" t="s">
-        <v>137</v>
-      </c>
-      <c r="F41" s="52" t="s">
-        <v>138</v>
-      </c>
-      <c r="G41" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="H41" s="53">
+      <c r="D44" s="74" t="s">
+        <v>149</v>
+      </c>
+      <c r="E44" s="74" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" s="74" t="s">
+        <v>151</v>
+      </c>
+      <c r="G44" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="75">
         <v>46270</v>
       </c>
-      <c r="I41" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="J41" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" s="53">
+      <c r="I44" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J44" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="75">
         <v>46270</v>
       </c>
-      <c r="L41" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="M41" s="52"/>
-    </row>
-    <row r="42" spans="1:18" ht="65.25" customHeight="1" thickBot="1">
-      <c r="A42" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="B42" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="C42" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="D42" s="52" t="s">
-        <v>141</v>
-      </c>
-      <c r="E42" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="F42" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="G42" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="H42" s="53">
-        <v>46270</v>
-      </c>
-      <c r="I42" s="52" t="s">
-        <v>114</v>
-      </c>
-      <c r="J42" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="K42" s="53">
-        <v>46271</v>
-      </c>
-      <c r="L42" s="52" t="s">
-        <v>114</v>
-      </c>
-      <c r="M42" s="52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="66" customHeight="1" thickBot="1">
-      <c r="A43" s="52" t="s">
-        <v>145</v>
-      </c>
-      <c r="B43" s="52" t="s">
-        <v>146</v>
-      </c>
-      <c r="C43" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="D43" s="52" t="s">
-        <v>147</v>
-      </c>
-      <c r="E43" s="52" t="s">
-        <v>148</v>
-      </c>
-      <c r="F43" s="52" t="s">
-        <v>149</v>
-      </c>
-      <c r="G43" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" s="53">
-        <v>46270</v>
-      </c>
-      <c r="I43" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="J43" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="53">
-        <v>46270</v>
-      </c>
-      <c r="L43" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="M43" s="52"/>
-    </row>
-    <row r="44" spans="1:18" ht="58.5" customHeight="1">
-      <c r="A44" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="B44" s="54" t="s">
-        <v>151</v>
-      </c>
-      <c r="C44" s="54" t="s">
-        <v>158</v>
-      </c>
-      <c r="D44" s="54" t="s">
-        <v>152</v>
-      </c>
-      <c r="E44" s="54" t="s">
-        <v>153</v>
-      </c>
-      <c r="F44" s="54" t="s">
-        <v>154</v>
-      </c>
-      <c r="G44" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" s="55">
-        <v>46270</v>
-      </c>
-      <c r="I44" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="J44" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="55">
-        <v>46270</v>
-      </c>
-      <c r="L44" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="M44" s="54"/>
+      <c r="L44" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="M44" s="74"/>
     </row>
     <row r="48" spans="1:18">
-      <c r="F48" s="56"/>
-      <c r="G48" s="56"/>
-      <c r="H48" s="56"/>
-      <c r="I48" s="56"/>
-      <c r="J48" s="56"/>
-      <c r="K48" s="56"/>
-      <c r="L48" s="56"/>
-      <c r="M48" s="56"/>
-      <c r="N48" s="56"/>
-      <c r="O48" s="56"/>
-      <c r="P48" s="56"/>
-      <c r="Q48" s="56"/>
-      <c r="R48" s="56"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="20"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="20"/>
+      <c r="R48" s="20"/>
     </row>
     <row r="49" spans="6:18">
-      <c r="F49" s="56"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="57"/>
-      <c r="K49" s="57"/>
-      <c r="L49" s="57"/>
-      <c r="M49" s="57"/>
-      <c r="N49" s="57"/>
-      <c r="O49" s="57"/>
-      <c r="P49" s="57"/>
-      <c r="Q49" s="57"/>
-      <c r="R49" s="57"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="21"/>
+      <c r="L49" s="21"/>
+      <c r="M49" s="21"/>
+      <c r="N49" s="21"/>
+      <c r="O49" s="21"/>
+      <c r="P49" s="21"/>
+      <c r="Q49" s="21"/>
+      <c r="R49" s="21"/>
     </row>
     <row r="50" spans="6:18">
-      <c r="F50" s="57"/>
-      <c r="G50" s="57"/>
-      <c r="H50" s="57"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="57"/>
-      <c r="K50" s="57"/>
-      <c r="L50" s="57"/>
-      <c r="M50" s="58"/>
-      <c r="N50" s="57"/>
-      <c r="O50" s="57"/>
-      <c r="P50" s="58"/>
-      <c r="Q50" s="57"/>
-      <c r="R50" s="57"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="21"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="21"/>
+      <c r="K50" s="21"/>
+      <c r="L50" s="21"/>
+      <c r="M50" s="22"/>
+      <c r="N50" s="21"/>
+      <c r="O50" s="21"/>
+      <c r="P50" s="22"/>
+      <c r="Q50" s="21"/>
+      <c r="R50" s="21"/>
     </row>
     <row r="51" spans="6:18">
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="57"/>
-      <c r="K51" s="57"/>
-      <c r="L51" s="57"/>
-      <c r="M51" s="58"/>
-      <c r="N51" s="57"/>
-      <c r="O51" s="57"/>
-      <c r="P51" s="58"/>
-      <c r="Q51" s="57"/>
-      <c r="R51" s="57"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+      <c r="M51" s="22"/>
+      <c r="N51" s="21"/>
+      <c r="O51" s="21"/>
+      <c r="P51" s="22"/>
+      <c r="Q51" s="21"/>
+      <c r="R51" s="21"/>
     </row>
     <row r="52" spans="6:18">
-      <c r="F52" s="57"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="57"/>
-      <c r="K52" s="57"/>
-      <c r="L52" s="57"/>
-      <c r="M52" s="58"/>
-      <c r="N52" s="57"/>
-      <c r="O52" s="57"/>
-      <c r="P52" s="58"/>
-      <c r="Q52" s="57"/>
-      <c r="R52" s="57"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="22"/>
+      <c r="N52" s="21"/>
+      <c r="O52" s="21"/>
+      <c r="P52" s="22"/>
+      <c r="Q52" s="21"/>
+      <c r="R52" s="21"/>
     </row>
     <row r="53" spans="6:18">
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="57"/>
-      <c r="K53" s="57"/>
-      <c r="L53" s="57"/>
-      <c r="M53" s="58"/>
-      <c r="N53" s="57"/>
-      <c r="O53" s="57"/>
-      <c r="P53" s="58"/>
-      <c r="Q53" s="57"/>
-      <c r="R53" s="57"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="21"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="22"/>
+      <c r="N53" s="21"/>
+      <c r="O53" s="21"/>
+      <c r="P53" s="22"/>
+      <c r="Q53" s="21"/>
+      <c r="R53" s="21"/>
     </row>
     <row r="54" spans="6:18">
-      <c r="F54" s="57"/>
-      <c r="G54" s="57"/>
-      <c r="H54" s="57"/>
-      <c r="I54" s="57"/>
-      <c r="J54" s="57"/>
-      <c r="K54" s="57"/>
-      <c r="L54" s="57"/>
-      <c r="M54" s="58"/>
-      <c r="N54" s="57"/>
-      <c r="O54" s="57"/>
-      <c r="P54" s="58"/>
-      <c r="Q54" s="57"/>
-      <c r="R54" s="57"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="22"/>
+      <c r="N54" s="21"/>
+      <c r="O54" s="21"/>
+      <c r="P54" s="22"/>
+      <c r="Q54" s="21"/>
+      <c r="R54" s="21"/>
     </row>
     <row r="55" spans="6:18">
-      <c r="F55" s="56"/>
-      <c r="G55" s="57"/>
-      <c r="H55" s="57"/>
-      <c r="I55" s="57"/>
-      <c r="J55" s="57"/>
-      <c r="K55" s="57"/>
-      <c r="L55" s="57"/>
-      <c r="M55" s="57"/>
-      <c r="N55" s="57"/>
-      <c r="O55" s="57"/>
-      <c r="P55" s="57"/>
-      <c r="Q55" s="57"/>
-      <c r="R55" s="57"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="21"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="21"/>
+      <c r="P55" s="21"/>
+      <c r="Q55" s="21"/>
+      <c r="R55" s="21"/>
     </row>
     <row r="56" spans="6:18" ht="84" customHeight="1">
-      <c r="F56" s="94"/>
-      <c r="G56" s="94"/>
-      <c r="H56" s="57"/>
-      <c r="I56" s="94"/>
-      <c r="J56" s="94"/>
-      <c r="K56" s="94"/>
-      <c r="L56" s="94"/>
-      <c r="M56" s="95"/>
-      <c r="N56" s="94"/>
-      <c r="O56" s="94"/>
-      <c r="P56" s="95"/>
-      <c r="Q56" s="94"/>
-      <c r="R56" s="94"/>
+      <c r="F56" s="114"/>
+      <c r="G56" s="114"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="114"/>
+      <c r="J56" s="114"/>
+      <c r="K56" s="114"/>
+      <c r="L56" s="114"/>
+      <c r="M56" s="115"/>
+      <c r="N56" s="114"/>
+      <c r="O56" s="114"/>
+      <c r="P56" s="115"/>
+      <c r="Q56" s="114"/>
+      <c r="R56" s="114"/>
     </row>
     <row r="57" spans="6:18">
-      <c r="F57" s="94"/>
-      <c r="G57" s="94"/>
-      <c r="H57" s="59"/>
-      <c r="I57" s="94"/>
-      <c r="J57" s="94"/>
-      <c r="K57" s="94"/>
-      <c r="L57" s="94"/>
-      <c r="M57" s="95"/>
-      <c r="N57" s="94"/>
-      <c r="O57" s="94"/>
-      <c r="P57" s="95"/>
-      <c r="Q57" s="94"/>
-      <c r="R57" s="94"/>
+      <c r="F57" s="114"/>
+      <c r="G57" s="114"/>
+      <c r="H57" s="23"/>
+      <c r="I57" s="114"/>
+      <c r="J57" s="114"/>
+      <c r="K57" s="114"/>
+      <c r="L57" s="114"/>
+      <c r="M57" s="115"/>
+      <c r="N57" s="114"/>
+      <c r="O57" s="114"/>
+      <c r="P57" s="115"/>
+      <c r="Q57" s="114"/>
+      <c r="R57" s="114"/>
     </row>
     <row r="58" spans="6:18">
-      <c r="F58" s="94"/>
-      <c r="G58" s="94"/>
-      <c r="H58" s="57"/>
-      <c r="I58" s="94"/>
-      <c r="J58" s="94"/>
-      <c r="K58" s="94"/>
-      <c r="L58" s="94"/>
-      <c r="M58" s="95"/>
-      <c r="N58" s="94"/>
-      <c r="O58" s="94"/>
-      <c r="P58" s="95"/>
-      <c r="Q58" s="94"/>
-      <c r="R58" s="94"/>
+      <c r="F58" s="114"/>
+      <c r="G58" s="114"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="114"/>
+      <c r="J58" s="114"/>
+      <c r="K58" s="114"/>
+      <c r="L58" s="114"/>
+      <c r="M58" s="115"/>
+      <c r="N58" s="114"/>
+      <c r="O58" s="114"/>
+      <c r="P58" s="115"/>
+      <c r="Q58" s="114"/>
+      <c r="R58" s="114"/>
     </row>
     <row r="59" spans="6:18" ht="55.5" customHeight="1">
-      <c r="F59" s="94"/>
-      <c r="G59" s="94"/>
-      <c r="H59" s="57"/>
-      <c r="I59" s="94"/>
-      <c r="J59" s="94"/>
-      <c r="K59" s="94"/>
-      <c r="L59" s="94"/>
-      <c r="M59" s="95"/>
-      <c r="N59" s="94"/>
-      <c r="O59" s="94"/>
-      <c r="P59" s="95"/>
-      <c r="Q59" s="94"/>
-      <c r="R59" s="94"/>
+      <c r="F59" s="114"/>
+      <c r="G59" s="114"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="114"/>
+      <c r="J59" s="114"/>
+      <c r="K59" s="114"/>
+      <c r="L59" s="114"/>
+      <c r="M59" s="115"/>
+      <c r="N59" s="114"/>
+      <c r="O59" s="114"/>
+      <c r="P59" s="115"/>
+      <c r="Q59" s="114"/>
+      <c r="R59" s="114"/>
     </row>
     <row r="60" spans="6:18">
-      <c r="F60" s="94"/>
-      <c r="G60" s="94"/>
-      <c r="H60" s="59"/>
-      <c r="I60" s="94"/>
-      <c r="J60" s="94"/>
-      <c r="K60" s="94"/>
-      <c r="L60" s="94"/>
-      <c r="M60" s="95"/>
-      <c r="N60" s="94"/>
-      <c r="O60" s="94"/>
-      <c r="P60" s="95"/>
-      <c r="Q60" s="94"/>
-      <c r="R60" s="94"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="23"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="114"/>
+      <c r="L60" s="114"/>
+      <c r="M60" s="115"/>
+      <c r="N60" s="114"/>
+      <c r="O60" s="114"/>
+      <c r="P60" s="115"/>
+      <c r="Q60" s="114"/>
+      <c r="R60" s="114"/>
     </row>
     <row r="61" spans="6:18">
-      <c r="F61" s="94"/>
-      <c r="G61" s="94"/>
-      <c r="H61" s="57"/>
-      <c r="I61" s="94"/>
-      <c r="J61" s="94"/>
-      <c r="K61" s="94"/>
-      <c r="L61" s="94"/>
-      <c r="M61" s="95"/>
-      <c r="N61" s="94"/>
-      <c r="O61" s="94"/>
-      <c r="P61" s="95"/>
-      <c r="Q61" s="94"/>
-      <c r="R61" s="94"/>
+      <c r="F61" s="114"/>
+      <c r="G61" s="114"/>
+      <c r="H61" s="21"/>
+      <c r="I61" s="114"/>
+      <c r="J61" s="114"/>
+      <c r="K61" s="114"/>
+      <c r="L61" s="114"/>
+      <c r="M61" s="115"/>
+      <c r="N61" s="114"/>
+      <c r="O61" s="114"/>
+      <c r="P61" s="115"/>
+      <c r="Q61" s="114"/>
+      <c r="R61" s="114"/>
     </row>
     <row r="62" spans="6:18" ht="84" customHeight="1">
-      <c r="F62" s="94"/>
-      <c r="G62" s="94"/>
-      <c r="H62" s="57"/>
-      <c r="I62" s="94"/>
-      <c r="J62" s="94"/>
-      <c r="K62" s="94"/>
-      <c r="L62" s="94"/>
-      <c r="M62" s="95"/>
-      <c r="N62" s="94"/>
-      <c r="O62" s="94"/>
-      <c r="P62" s="95"/>
-      <c r="Q62" s="94"/>
-      <c r="R62" s="94"/>
+      <c r="F62" s="114"/>
+      <c r="G62" s="114"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="114"/>
+      <c r="J62" s="114"/>
+      <c r="K62" s="114"/>
+      <c r="L62" s="114"/>
+      <c r="M62" s="115"/>
+      <c r="N62" s="114"/>
+      <c r="O62" s="114"/>
+      <c r="P62" s="115"/>
+      <c r="Q62" s="114"/>
+      <c r="R62" s="114"/>
     </row>
     <row r="63" spans="6:18">
-      <c r="F63" s="94"/>
-      <c r="G63" s="94"/>
-      <c r="H63" s="59"/>
-      <c r="I63" s="94"/>
-      <c r="J63" s="94"/>
-      <c r="K63" s="94"/>
-      <c r="L63" s="94"/>
-      <c r="M63" s="95"/>
-      <c r="N63" s="94"/>
-      <c r="O63" s="94"/>
-      <c r="P63" s="95"/>
-      <c r="Q63" s="94"/>
-      <c r="R63" s="94"/>
+      <c r="F63" s="114"/>
+      <c r="G63" s="114"/>
+      <c r="H63" s="23"/>
+      <c r="I63" s="114"/>
+      <c r="J63" s="114"/>
+      <c r="K63" s="114"/>
+      <c r="L63" s="114"/>
+      <c r="M63" s="115"/>
+      <c r="N63" s="114"/>
+      <c r="O63" s="114"/>
+      <c r="P63" s="115"/>
+      <c r="Q63" s="114"/>
+      <c r="R63" s="114"/>
     </row>
     <row r="64" spans="6:18">
-      <c r="F64" s="94"/>
-      <c r="G64" s="94"/>
-      <c r="H64" s="57"/>
-      <c r="I64" s="94"/>
-      <c r="J64" s="94"/>
-      <c r="K64" s="94"/>
-      <c r="L64" s="94"/>
-      <c r="M64" s="95"/>
-      <c r="N64" s="94"/>
-      <c r="O64" s="94"/>
-      <c r="P64" s="95"/>
-      <c r="Q64" s="94"/>
-      <c r="R64" s="94"/>
+      <c r="F64" s="114"/>
+      <c r="G64" s="114"/>
+      <c r="H64" s="21"/>
+      <c r="I64" s="114"/>
+      <c r="J64" s="114"/>
+      <c r="K64" s="114"/>
+      <c r="L64" s="114"/>
+      <c r="M64" s="115"/>
+      <c r="N64" s="114"/>
+      <c r="O64" s="114"/>
+      <c r="P64" s="115"/>
+      <c r="Q64" s="114"/>
+      <c r="R64" s="114"/>
     </row>
     <row r="65" spans="6:18" ht="69.75" customHeight="1">
-      <c r="F65" s="94"/>
-      <c r="G65" s="94"/>
-      <c r="H65" s="57"/>
-      <c r="I65" s="94"/>
-      <c r="J65" s="94"/>
-      <c r="K65" s="94"/>
-      <c r="L65" s="94"/>
-      <c r="M65" s="95"/>
-      <c r="N65" s="94"/>
-      <c r="O65" s="94"/>
-      <c r="P65" s="95"/>
-      <c r="Q65" s="94"/>
-      <c r="R65" s="94"/>
+      <c r="F65" s="114"/>
+      <c r="G65" s="114"/>
+      <c r="H65" s="21"/>
+      <c r="I65" s="114"/>
+      <c r="J65" s="114"/>
+      <c r="K65" s="114"/>
+      <c r="L65" s="114"/>
+      <c r="M65" s="115"/>
+      <c r="N65" s="114"/>
+      <c r="O65" s="114"/>
+      <c r="P65" s="115"/>
+      <c r="Q65" s="114"/>
+      <c r="R65" s="114"/>
     </row>
     <row r="66" spans="6:18">
-      <c r="F66" s="94"/>
-      <c r="G66" s="94"/>
-      <c r="H66" s="59"/>
-      <c r="I66" s="94"/>
-      <c r="J66" s="94"/>
-      <c r="K66" s="94"/>
-      <c r="L66" s="94"/>
-      <c r="M66" s="95"/>
-      <c r="N66" s="94"/>
-      <c r="O66" s="94"/>
-      <c r="P66" s="95"/>
-      <c r="Q66" s="94"/>
-      <c r="R66" s="94"/>
+      <c r="F66" s="114"/>
+      <c r="G66" s="114"/>
+      <c r="H66" s="23"/>
+      <c r="I66" s="114"/>
+      <c r="J66" s="114"/>
+      <c r="K66" s="114"/>
+      <c r="L66" s="114"/>
+      <c r="M66" s="115"/>
+      <c r="N66" s="114"/>
+      <c r="O66" s="114"/>
+      <c r="P66" s="115"/>
+      <c r="Q66" s="114"/>
+      <c r="R66" s="114"/>
     </row>
     <row r="67" spans="6:18">
-      <c r="F67" s="94"/>
-      <c r="G67" s="94"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="94"/>
-      <c r="J67" s="94"/>
-      <c r="K67" s="94"/>
-      <c r="L67" s="94"/>
-      <c r="M67" s="95"/>
-      <c r="N67" s="94"/>
-      <c r="O67" s="94"/>
-      <c r="P67" s="95"/>
-      <c r="Q67" s="94"/>
-      <c r="R67" s="94"/>
+      <c r="F67" s="114"/>
+      <c r="G67" s="114"/>
+      <c r="H67" s="21"/>
+      <c r="I67" s="114"/>
+      <c r="J67" s="114"/>
+      <c r="K67" s="114"/>
+      <c r="L67" s="114"/>
+      <c r="M67" s="115"/>
+      <c r="N67" s="114"/>
+      <c r="O67" s="114"/>
+      <c r="P67" s="115"/>
+      <c r="Q67" s="114"/>
+      <c r="R67" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="61">
@@ -5325,107 +6053,107 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N44"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" style="27" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" style="27" customWidth="1"/>
-    <col min="3" max="3" width="19.77734375" style="27" customWidth="1"/>
-    <col min="4" max="4" width="21.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5546875" style="27" customWidth="1"/>
-    <col min="6" max="6" width="28.77734375" style="27" customWidth="1"/>
-    <col min="7" max="7" width="26.21875" style="27" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" style="27" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" style="27" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.21875" style="27"/>
+    <col min="1" max="1" width="23.7265625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.54296875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="28.7265625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="26.26953125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="18.26953125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="18.7265625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.26953125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="97" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="81" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
+      <c r="B2" s="118" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="28"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="12">
         <v>3</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="12">
         <v>0</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="12">
         <v>0</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="12">
         <v>0</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="12">
         <f>B4</f>
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="14">
         <v>3</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="14">
         <v>0</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="14">
         <v>0</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="14">
         <v>0</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="12">
         <f>B5</f>
         <v>3</v>
       </c>
@@ -5433,232 +6161,232 @@
     <row r="9" spans="1:6" ht="114.75" customHeight="1"/>
     <row r="30" spans="1:13" ht="118.5" customHeight="1"/>
     <row r="31" spans="1:13">
-      <c r="A31" s="82" t="s">
+      <c r="A31" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="82" t="s">
+      <c r="B31" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="82" t="s">
+      <c r="C31" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="82" t="s">
+      <c r="D31" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="83" t="s">
+      <c r="E31" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="82" t="s">
+      <c r="F31" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="84" t="s">
+      <c r="G31" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="84"/>
-      <c r="I31" s="84"/>
-      <c r="J31" s="84"/>
-      <c r="K31" s="84"/>
-      <c r="L31" s="84"/>
-      <c r="M31" s="84" t="s">
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="98" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="82"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="84" t="s">
+      <c r="A32" s="105"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="84"/>
-      <c r="I32" s="84"/>
-      <c r="J32" s="84" t="s">
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="84"/>
-      <c r="L32" s="84"/>
-      <c r="M32" s="85"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="99"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="82"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="8" t="s">
+      <c r="A33" s="105"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="K33" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="8" t="s">
+      <c r="L33" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="85"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="102" t="s">
-        <v>268</v>
-      </c>
-      <c r="B34" s="103"/>
-      <c r="C34" s="103"/>
-      <c r="D34" s="103"/>
-      <c r="E34" s="103"/>
-      <c r="F34" s="103"/>
-      <c r="G34" s="103"/>
-      <c r="H34" s="103"/>
-      <c r="I34" s="103"/>
-      <c r="J34" s="103"/>
-      <c r="K34" s="103"/>
-      <c r="L34" s="103"/>
-      <c r="M34" s="104"/>
-    </row>
-    <row r="35" spans="1:14" ht="117.6">
-      <c r="A35" s="31" t="s">
+      <c r="M33" s="99"/>
+    </row>
+    <row r="34" spans="1:14" ht="17" thickBot="1">
+      <c r="A34" s="122" t="s">
+        <v>265</v>
+      </c>
+      <c r="B34" s="123"/>
+      <c r="C34" s="123"/>
+      <c r="D34" s="123"/>
+      <c r="E34" s="123"/>
+      <c r="F34" s="123"/>
+      <c r="G34" s="123"/>
+      <c r="H34" s="123"/>
+      <c r="I34" s="123"/>
+      <c r="J34" s="123"/>
+      <c r="K34" s="123"/>
+      <c r="L34" s="123"/>
+      <c r="M34" s="124"/>
+    </row>
+    <row r="35" spans="1:14" ht="109" thickBot="1">
+      <c r="A35" s="76" t="s">
+        <v>247</v>
+      </c>
+      <c r="B35" s="76" t="s">
+        <v>248</v>
+      </c>
+      <c r="C35" s="77" t="s">
+        <v>249</v>
+      </c>
+      <c r="D35" s="77" t="s">
         <v>250</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="E35" s="78" t="s">
         <v>251</v>
       </c>
-      <c r="C35" s="32" t="s">
+      <c r="F35" s="78" t="s">
         <v>252</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="G35" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="79">
+        <v>46277</v>
+      </c>
+      <c r="I35" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="J35" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="79">
+        <v>46280</v>
+      </c>
+      <c r="L35" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35" s="69"/>
+    </row>
+    <row r="36" spans="1:14" ht="17" thickBot="1">
+      <c r="A36" s="119" t="s">
+        <v>266</v>
+      </c>
+      <c r="B36" s="120"/>
+      <c r="C36" s="120"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="120"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="120"/>
+      <c r="H36" s="120"/>
+      <c r="I36" s="120"/>
+      <c r="J36" s="120"/>
+      <c r="K36" s="120"/>
+      <c r="L36" s="120"/>
+      <c r="M36" s="121"/>
+    </row>
+    <row r="37" spans="1:14" ht="78" thickBot="1">
+      <c r="A37" s="78" t="s">
+        <v>256</v>
+      </c>
+      <c r="B37" s="78" t="s">
+        <v>257</v>
+      </c>
+      <c r="C37" s="78" t="s">
+        <v>264</v>
+      </c>
+      <c r="D37" s="78" t="s">
+        <v>255</v>
+      </c>
+      <c r="E37" s="77" t="s">
+        <v>254</v>
+      </c>
+      <c r="F37" s="77" t="s">
         <v>253</v>
       </c>
-      <c r="E35" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="F35" s="33" t="s">
-        <v>255</v>
-      </c>
-      <c r="G35" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="35">
+      <c r="G37" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="79">
         <v>46277</v>
       </c>
-      <c r="I35" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="J35" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="35">
+      <c r="I37" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="J37" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="79">
         <v>46280</v>
       </c>
-      <c r="L35" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="M35" s="37"/>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" s="99" t="s">
-        <v>269</v>
-      </c>
-      <c r="B36" s="100"/>
-      <c r="C36" s="100"/>
-      <c r="D36" s="100"/>
-      <c r="E36" s="100"/>
-      <c r="F36" s="100"/>
-      <c r="G36" s="100"/>
-      <c r="H36" s="100"/>
-      <c r="I36" s="100"/>
-      <c r="J36" s="100"/>
-      <c r="K36" s="100"/>
-      <c r="L36" s="100"/>
-      <c r="M36" s="101"/>
-    </row>
-    <row r="37" spans="1:14" ht="100.8">
-      <c r="A37" s="33" t="s">
+      <c r="L37" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="M37" s="69"/>
+    </row>
+    <row r="38" spans="1:14" ht="112.5" customHeight="1" thickBot="1">
+      <c r="A38" s="78" t="s">
+        <v>258</v>
+      </c>
+      <c r="B38" s="78" t="s">
         <v>259</v>
       </c>
-      <c r="B37" s="33" t="s">
+      <c r="C38" s="78" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="D37" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="E37" s="38" t="s">
-        <v>257</v>
-      </c>
-      <c r="F37" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="G37" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="35">
+      <c r="D38" s="78" t="s">
+        <v>261</v>
+      </c>
+      <c r="E38" s="77" t="s">
+        <v>262</v>
+      </c>
+      <c r="F38" s="77" t="s">
+        <v>263</v>
+      </c>
+      <c r="G38" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="79">
         <v>46277</v>
       </c>
-      <c r="I37" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="J37" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" s="35">
+      <c r="I38" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="79">
         <v>46280</v>
       </c>
-      <c r="L37" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="M37" s="37"/>
-    </row>
-    <row r="38" spans="1:14" ht="112.5" customHeight="1">
-      <c r="A38" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="B38" s="33" t="s">
-        <v>262</v>
-      </c>
-      <c r="C38" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="D38" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="E38" s="38" t="s">
-        <v>265</v>
-      </c>
-      <c r="F38" s="38" t="s">
-        <v>266</v>
-      </c>
-      <c r="G38" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="35">
-        <v>46277</v>
-      </c>
-      <c r="I38" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="J38" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="35">
-        <v>46280</v>
-      </c>
-      <c r="L38" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M38" s="37"/>
+      <c r="L38" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="M38" s="69"/>
     </row>
     <row r="39" spans="1:14">
       <c r="N39" s="1"/>
@@ -5695,610 +6423,610 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N45"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" style="27" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" style="27" customWidth="1"/>
-    <col min="3" max="3" width="44" style="27" customWidth="1"/>
-    <col min="4" max="4" width="34.77734375" style="27" customWidth="1"/>
-    <col min="5" max="5" width="29.5546875" style="27" customWidth="1"/>
-    <col min="6" max="6" width="28.77734375" style="27" customWidth="1"/>
-    <col min="7" max="7" width="26.21875" style="27" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" style="27" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" style="27" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.21875" style="27"/>
+    <col min="1" max="1" width="23.7265625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="44" style="11" customWidth="1"/>
+    <col min="4" max="4" width="34.7265625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="29.54296875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="28.7265625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="26.26953125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="18.26953125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="18.7265625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.26953125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="97" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="81" t="s">
-        <v>249</v>
-      </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
+      <c r="B2" s="118" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="28"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="12">
         <v>7</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="12">
         <v>1</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="12">
         <v>0</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="12">
         <v>0</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="12">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="14">
         <v>8</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="12">
         <v>0</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="12">
         <v>0</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="12">
         <v>0</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="12">
         <f>B5</f>
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="75.75" customHeight="1"/>
     <row r="31" spans="1:13">
-      <c r="A31" s="82" t="s">
+      <c r="A31" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="82" t="s">
+      <c r="B31" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="82" t="s">
+      <c r="C31" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="82" t="s">
+      <c r="D31" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="83" t="s">
+      <c r="E31" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="82" t="s">
+      <c r="F31" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="84" t="s">
+      <c r="G31" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="84"/>
-      <c r="I31" s="84"/>
-      <c r="J31" s="84"/>
-      <c r="K31" s="84"/>
-      <c r="L31" s="84"/>
-      <c r="M31" s="84" t="s">
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="98" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="82"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="84" t="s">
+      <c r="A32" s="105"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="84"/>
-      <c r="I32" s="84"/>
-      <c r="J32" s="84" t="s">
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="84"/>
-      <c r="L32" s="84"/>
-      <c r="M32" s="85"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="99"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="82"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="8" t="s">
+      <c r="A33" s="105"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="K33" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="8" t="s">
+      <c r="L33" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="85"/>
+      <c r="M33" s="99"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="98" t="s">
-        <v>335</v>
-      </c>
-      <c r="B34" s="98"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="98"/>
-      <c r="H34" s="98"/>
-      <c r="I34" s="98"/>
-      <c r="J34" s="98"/>
-      <c r="K34" s="98"/>
-      <c r="L34" s="98"/>
-      <c r="M34" s="98"/>
+      <c r="A34" s="100" t="s">
+        <v>332</v>
+      </c>
+      <c r="B34" s="100"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="100"/>
+      <c r="G34" s="100"/>
+      <c r="H34" s="100"/>
+      <c r="I34" s="100"/>
+      <c r="J34" s="100"/>
+      <c r="K34" s="100"/>
+      <c r="L34" s="100"/>
+      <c r="M34" s="100"/>
     </row>
     <row r="35" spans="1:14" ht="127.5" customHeight="1">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="76" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" s="76" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="D35" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="E35" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="F35" s="78" t="s">
+        <v>160</v>
+      </c>
+      <c r="G35" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="79">
+        <v>46273</v>
+      </c>
+      <c r="I35" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J35" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="79">
+        <v>46273</v>
+      </c>
+      <c r="L35" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35" s="37"/>
+    </row>
+    <row r="36" spans="1:14" ht="96" customHeight="1">
+      <c r="A36" s="76" t="s">
+        <v>167</v>
+      </c>
+      <c r="B36" s="76" t="s">
+        <v>161</v>
+      </c>
+      <c r="C36" s="77" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36" s="82" t="s">
+        <v>163</v>
+      </c>
+      <c r="E36" s="78" t="s">
+        <v>164</v>
+      </c>
+      <c r="F36" s="78" t="s">
+        <v>165</v>
+      </c>
+      <c r="G36" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="79">
+        <v>46273</v>
+      </c>
+      <c r="I36" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J36" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="79">
+        <v>46273</v>
+      </c>
+      <c r="L36" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M36" s="37"/>
+    </row>
+    <row r="37" spans="1:14" ht="46.5">
+      <c r="A37" s="76" t="s">
+        <v>166</v>
+      </c>
+      <c r="B37" s="76" t="s">
+        <v>169</v>
+      </c>
+      <c r="C37" s="82" t="s">
+        <v>170</v>
+      </c>
+      <c r="D37" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="B35" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D35" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="E35" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="F35" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="G35" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="35">
+      <c r="E37" s="78" t="s">
+        <v>172</v>
+      </c>
+      <c r="F37" s="78" t="s">
+        <v>173</v>
+      </c>
+      <c r="G37" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="79">
         <v>46273</v>
       </c>
-      <c r="I35" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="J35" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="35">
+      <c r="I37" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J37" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="79">
         <v>46273</v>
       </c>
-      <c r="L35" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M35" s="37"/>
-    </row>
-    <row r="36" spans="1:14" ht="96" customHeight="1">
-      <c r="A36" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="B36" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>165</v>
-      </c>
-      <c r="D36" s="45" t="s">
-        <v>166</v>
-      </c>
-      <c r="E36" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="F36" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="G36" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="35">
+      <c r="L37" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M37" s="37"/>
+    </row>
+    <row r="38" spans="1:14" ht="120.75" customHeight="1">
+      <c r="A38" s="76" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38" s="76" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" s="82" t="s">
+        <v>176</v>
+      </c>
+      <c r="D38" s="83" t="s">
+        <v>177</v>
+      </c>
+      <c r="E38" s="78" t="s">
+        <v>178</v>
+      </c>
+      <c r="F38" s="78" t="s">
+        <v>179</v>
+      </c>
+      <c r="G38" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="79">
         <v>46273</v>
       </c>
-      <c r="I36" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="J36" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="35">
+      <c r="I38" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="79">
+        <v>46274</v>
+      </c>
+      <c r="L38" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M38" s="37"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="125" t="s">
+        <v>333</v>
+      </c>
+      <c r="B39" s="125"/>
+      <c r="C39" s="125"/>
+      <c r="D39" s="125"/>
+      <c r="E39" s="125"/>
+      <c r="F39" s="125"/>
+      <c r="G39" s="125"/>
+      <c r="H39" s="125"/>
+      <c r="I39" s="125"/>
+      <c r="J39" s="125"/>
+      <c r="K39" s="125"/>
+      <c r="L39" s="125"/>
+      <c r="M39" s="125"/>
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="1:14" ht="198" customHeight="1">
+      <c r="A40" s="78" t="s">
+        <v>180</v>
+      </c>
+      <c r="B40" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="C40" s="78" t="s">
+        <v>182</v>
+      </c>
+      <c r="D40" s="78" t="s">
+        <v>183</v>
+      </c>
+      <c r="E40" s="77" t="s">
+        <v>184</v>
+      </c>
+      <c r="F40" s="77" t="s">
+        <v>185</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="79">
         <v>46273</v>
       </c>
-      <c r="L36" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M36" s="37"/>
-    </row>
-    <row r="37" spans="1:14" ht="50.4">
-      <c r="A37" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="C37" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="E37" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="F37" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="G37" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="35">
+      <c r="I40" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J40" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="79">
         <v>46273</v>
       </c>
-      <c r="I37" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="J37" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" s="35">
+      <c r="L40" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M40" s="37"/>
+    </row>
+    <row r="41" spans="1:14" ht="230.25" customHeight="1">
+      <c r="A41" s="78" t="s">
+        <v>189</v>
+      </c>
+      <c r="B41" s="78" t="s">
+        <v>186</v>
+      </c>
+      <c r="C41" s="78" t="s">
+        <v>186</v>
+      </c>
+      <c r="D41" s="78" t="s">
+        <v>171</v>
+      </c>
+      <c r="E41" s="77" t="s">
+        <v>187</v>
+      </c>
+      <c r="F41" s="77" t="s">
+        <v>188</v>
+      </c>
+      <c r="G41" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="79">
         <v>46273</v>
       </c>
-      <c r="L37" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M37" s="37"/>
-    </row>
-    <row r="38" spans="1:14" ht="120.75" customHeight="1">
-      <c r="A38" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="C38" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="E38" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="F38" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="G38" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="H38" s="35">
+      <c r="I41" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J41" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="79">
         <v>46273</v>
       </c>
-      <c r="I38" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="J38" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="35">
-        <v>46274</v>
-      </c>
-      <c r="L38" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M38" s="37"/>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="105" t="s">
-        <v>336</v>
-      </c>
-      <c r="B39" s="105"/>
-      <c r="C39" s="105"/>
-      <c r="D39" s="105"/>
-      <c r="E39" s="105"/>
-      <c r="F39" s="105"/>
-      <c r="G39" s="105"/>
-      <c r="H39" s="105"/>
-      <c r="I39" s="105"/>
-      <c r="J39" s="105"/>
-      <c r="K39" s="105"/>
-      <c r="L39" s="105"/>
-      <c r="M39" s="105"/>
-      <c r="N39" s="1"/>
-    </row>
-    <row r="40" spans="1:14" ht="198" customHeight="1">
-      <c r="A40" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="B40" s="33" t="s">
-        <v>184</v>
-      </c>
-      <c r="C40" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="D40" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="E40" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="F40" s="38" t="s">
-        <v>188</v>
-      </c>
-      <c r="G40" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="35">
-        <v>46273</v>
-      </c>
-      <c r="I40" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="J40" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="35">
-        <v>46273</v>
-      </c>
-      <c r="L40" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="M40" s="37"/>
-    </row>
-    <row r="41" spans="1:14" ht="230.25" customHeight="1">
-      <c r="A41" s="33" t="s">
+      <c r="L41" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M41" s="37"/>
+    </row>
+    <row r="42" spans="1:14" ht="234" customHeight="1">
+      <c r="A42" s="78" t="s">
+        <v>190</v>
+      </c>
+      <c r="B42" s="78" t="s">
+        <v>191</v>
+      </c>
+      <c r="C42" s="78" t="s">
         <v>192</v>
       </c>
-      <c r="B41" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="C41" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="D41" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E41" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="F41" s="38" t="s">
-        <v>191</v>
-      </c>
-      <c r="G41" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H41" s="35">
-        <v>46273</v>
-      </c>
-      <c r="I41" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="J41" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" s="35">
-        <v>46273</v>
-      </c>
-      <c r="L41" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="M41" s="37"/>
-    </row>
-    <row r="42" spans="1:14" ht="234" customHeight="1">
-      <c r="A42" s="33" t="s">
+      <c r="D42" s="78" t="s">
         <v>193</v>
       </c>
-      <c r="B42" s="33" t="s">
+      <c r="E42" s="77" t="s">
         <v>194</v>
       </c>
-      <c r="C42" s="33" t="s">
+      <c r="F42" s="77" t="s">
         <v>195</v>
       </c>
-      <c r="D42" s="33" t="s">
+      <c r="G42" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="79">
+        <v>46275</v>
+      </c>
+      <c r="I42" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J42" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="79">
+        <v>46275</v>
+      </c>
+      <c r="L42" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M42" s="37"/>
+    </row>
+    <row r="43" spans="1:14" ht="218.25" customHeight="1">
+      <c r="A43" s="78" t="s">
         <v>196</v>
       </c>
-      <c r="E42" s="38" t="s">
+      <c r="B43" s="78" t="s">
         <v>197</v>
       </c>
-      <c r="F42" s="38" t="s">
+      <c r="C43" s="78" t="s">
         <v>198</v>
       </c>
-      <c r="G42" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H42" s="35">
+      <c r="D43" s="78" t="s">
+        <v>199</v>
+      </c>
+      <c r="E43" s="77" t="s">
+        <v>200</v>
+      </c>
+      <c r="F43" s="77" t="s">
+        <v>201</v>
+      </c>
+      <c r="G43" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="79">
         <v>46275</v>
       </c>
-      <c r="I42" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="J42" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K42" s="35">
+      <c r="I43" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J43" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="79">
         <v>46275</v>
       </c>
-      <c r="L42" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M42" s="37"/>
-    </row>
-    <row r="43" spans="1:14" ht="218.25" customHeight="1">
-      <c r="A43" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="B43" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="C43" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="D43" s="33" t="s">
+      <c r="L43" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M43" s="37"/>
+    </row>
+    <row r="44" spans="1:14" ht="248.25" customHeight="1">
+      <c r="A44" s="78" t="s">
         <v>202</v>
       </c>
-      <c r="E43" s="38" t="s">
+      <c r="B44" s="78" t="s">
         <v>203</v>
       </c>
-      <c r="F43" s="38" t="s">
+      <c r="C44" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="G43" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" s="35">
+      <c r="D44" s="78" t="s">
+        <v>205</v>
+      </c>
+      <c r="E44" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="F44" s="77" t="s">
+        <v>207</v>
+      </c>
+      <c r="G44" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="79">
         <v>46275</v>
       </c>
-      <c r="I43" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="J43" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="35">
+      <c r="I44" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J44" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="79">
         <v>46275</v>
       </c>
-      <c r="L43" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="M43" s="37"/>
-    </row>
-    <row r="44" spans="1:14" ht="248.25" customHeight="1">
-      <c r="A44" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="B44" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="C44" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="D44" s="33" t="s">
+      <c r="L44" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M44" s="37"/>
+    </row>
+    <row r="45" spans="1:14" ht="77.5">
+      <c r="A45" s="78" t="s">
+        <v>209</v>
+      </c>
+      <c r="B45" s="78" t="s">
         <v>208</v>
       </c>
-      <c r="E44" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="F44" s="38" t="s">
+      <c r="C45" s="84" t="s">
         <v>210</v>
       </c>
-      <c r="G44" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" s="35">
+      <c r="D45" s="84" t="s">
+        <v>211</v>
+      </c>
+      <c r="E45" s="77" t="s">
+        <v>212</v>
+      </c>
+      <c r="F45" s="77" t="s">
+        <v>213</v>
+      </c>
+      <c r="G45" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="79">
         <v>46275</v>
       </c>
-      <c r="I44" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="J44" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="35">
+      <c r="I45" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J45" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" s="79">
         <v>46275</v>
       </c>
-      <c r="L44" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="M44" s="37"/>
-    </row>
-    <row r="45" spans="1:14" ht="100.8">
-      <c r="A45" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="B45" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="C45" s="46" t="s">
-        <v>213</v>
-      </c>
-      <c r="D45" s="46" t="s">
-        <v>214</v>
-      </c>
-      <c r="E45" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="F45" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="G45" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="35">
-        <v>46275</v>
-      </c>
-      <c r="I45" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="J45" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K45" s="35">
-        <v>46275</v>
-      </c>
-      <c r="L45" s="36" t="s">
-        <v>114</v>
+      <c r="L45" s="81" t="s">
+        <v>61</v>
       </c>
       <c r="M45" s="37"/>
     </row>
@@ -6331,107 +7059,107 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N42"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" style="27" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" style="27" customWidth="1"/>
-    <col min="3" max="3" width="19.77734375" style="27" customWidth="1"/>
-    <col min="4" max="4" width="21.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5546875" style="27" customWidth="1"/>
-    <col min="6" max="6" width="28.77734375" style="27" customWidth="1"/>
-    <col min="7" max="7" width="26.21875" style="27" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" style="27" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" style="27" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.21875" style="27"/>
+    <col min="1" max="1" width="23.7265625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.54296875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="28.7265625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="26.26953125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="18.26953125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="18.7265625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.26953125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="97" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="81" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
+      <c r="B2" s="118" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="28"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="12">
         <v>5</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="12">
         <v>0</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="12">
         <v>0</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="12">
         <v>0</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="12">
         <f>B4</f>
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="14">
         <v>5</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="14">
         <v>0</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="14">
         <v>0</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="14">
         <v>0</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="12">
         <f>B5</f>
         <v>5</v>
       </c>
@@ -6439,338 +7167,338 @@
     <row r="9" spans="1:6" ht="330.75" customHeight="1"/>
     <row r="30" spans="1:13" ht="171" customHeight="1"/>
     <row r="31" spans="1:13">
-      <c r="A31" s="82" t="s">
+      <c r="A31" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="82" t="s">
+      <c r="B31" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="82" t="s">
+      <c r="C31" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="82" t="s">
+      <c r="D31" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="83" t="s">
+      <c r="E31" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="82" t="s">
+      <c r="F31" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="84" t="s">
+      <c r="G31" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="84"/>
-      <c r="I31" s="84"/>
-      <c r="J31" s="84"/>
-      <c r="K31" s="84"/>
-      <c r="L31" s="84"/>
-      <c r="M31" s="84" t="s">
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="98" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="82"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="84" t="s">
+      <c r="A32" s="105"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="84"/>
-      <c r="I32" s="84"/>
-      <c r="J32" s="84" t="s">
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="84"/>
-      <c r="L32" s="84"/>
-      <c r="M32" s="85"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="99"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="82"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="8" t="s">
+      <c r="A33" s="105"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="K33" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="8" t="s">
+      <c r="L33" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="85"/>
+      <c r="M33" s="99"/>
     </row>
     <row r="34" spans="1:14" ht="38.25" customHeight="1">
-      <c r="A34" s="102" t="s">
+      <c r="A34" s="122" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34" s="123"/>
+      <c r="C34" s="123"/>
+      <c r="D34" s="123"/>
+      <c r="E34" s="123"/>
+      <c r="F34" s="123"/>
+      <c r="G34" s="123"/>
+      <c r="H34" s="123"/>
+      <c r="I34" s="123"/>
+      <c r="J34" s="123"/>
+      <c r="K34" s="123"/>
+      <c r="L34" s="123"/>
+      <c r="M34" s="124"/>
+    </row>
+    <row r="35" spans="1:14" ht="77.5">
+      <c r="A35" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="B35" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" s="83" t="s">
         <v>219</v>
       </c>
-      <c r="B34" s="103"/>
-      <c r="C34" s="103"/>
-      <c r="D34" s="103"/>
-      <c r="E34" s="103"/>
-      <c r="F34" s="103"/>
-      <c r="G34" s="103"/>
-      <c r="H34" s="103"/>
-      <c r="I34" s="103"/>
-      <c r="J34" s="103"/>
-      <c r="K34" s="103"/>
-      <c r="L34" s="103"/>
-      <c r="M34" s="104"/>
-    </row>
-    <row r="35" spans="1:14" ht="100.8">
-      <c r="A35" s="31" t="s">
+      <c r="D35" s="83" t="s">
         <v>217</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="E35" s="78" t="s">
         <v>218</v>
       </c>
-      <c r="C35" s="32" t="s">
+      <c r="F35" s="78" t="s">
+        <v>220</v>
+      </c>
+      <c r="G35" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="79">
+        <v>46276</v>
+      </c>
+      <c r="I35" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J35" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="79">
+        <v>46276</v>
+      </c>
+      <c r="L35" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35" s="37"/>
+    </row>
+    <row r="36" spans="1:14" ht="77.5">
+      <c r="A36" s="76" t="s">
+        <v>221</v>
+      </c>
+      <c r="B36" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="D35" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E35" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="F35" s="33" t="s">
+      <c r="C36" s="83" t="s">
         <v>223</v>
       </c>
-      <c r="G35" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="35">
+      <c r="D36" s="83" t="s">
+        <v>224</v>
+      </c>
+      <c r="E36" s="78" t="s">
+        <v>225</v>
+      </c>
+      <c r="F36" s="78" t="s">
+        <v>226</v>
+      </c>
+      <c r="G36" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="79">
         <v>46276</v>
       </c>
-      <c r="I35" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="J35" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="35">
+      <c r="I36" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J36" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="79">
         <v>46276</v>
       </c>
-      <c r="L35" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M35" s="37"/>
-    </row>
-    <row r="36" spans="1:14" ht="84">
-      <c r="A36" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="B36" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="C36" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="D36" s="32" t="s">
+      <c r="L36" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M36" s="37"/>
+    </row>
+    <row r="37" spans="1:14" ht="93">
+      <c r="A37" s="76" t="s">
         <v>227</v>
       </c>
-      <c r="E36" s="33" t="s">
+      <c r="B37" s="76" t="s">
         <v>228</v>
       </c>
-      <c r="F36" s="33" t="s">
+      <c r="C37" s="83" t="s">
         <v>229</v>
       </c>
-      <c r="G36" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="35">
+      <c r="D37" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="E37" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="F37" s="78" t="s">
+        <v>232</v>
+      </c>
+      <c r="G37" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="79">
         <v>46276</v>
       </c>
-      <c r="I36" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="J36" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="35">
+      <c r="I37" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J37" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="79">
         <v>46276</v>
       </c>
-      <c r="L36" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M36" s="37"/>
-    </row>
-    <row r="37" spans="1:14" ht="100.8">
-      <c r="A37" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="C37" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="D37" s="37" t="s">
+      <c r="L37" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M37" s="37"/>
+    </row>
+    <row r="38" spans="1:14" ht="50.25" customHeight="1">
+      <c r="A38" s="108" t="s">
         <v>233</v>
       </c>
-      <c r="E37" s="33" t="s">
+      <c r="B38" s="109"/>
+      <c r="C38" s="109"/>
+      <c r="D38" s="109"/>
+      <c r="E38" s="109"/>
+      <c r="F38" s="109"/>
+      <c r="G38" s="109"/>
+      <c r="H38" s="109"/>
+      <c r="I38" s="109"/>
+      <c r="J38" s="109"/>
+      <c r="K38" s="109"/>
+      <c r="L38" s="109"/>
+      <c r="M38" s="110"/>
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" spans="1:14" ht="193.5" customHeight="1">
+      <c r="A39" s="78" t="s">
         <v>234</v>
       </c>
-      <c r="F37" s="33" t="s">
+      <c r="B39" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="C39" s="78" t="s">
+        <v>237</v>
+      </c>
+      <c r="D39" s="78" t="s">
+        <v>238</v>
+      </c>
+      <c r="E39" s="77" t="s">
+        <v>239</v>
+      </c>
+      <c r="F39" s="77" t="s">
+        <v>240</v>
+      </c>
+      <c r="G39" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="79">
+        <v>46276</v>
+      </c>
+      <c r="I39" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J39" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="79">
+        <v>46276</v>
+      </c>
+      <c r="L39" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="M39" s="37"/>
+    </row>
+    <row r="40" spans="1:14" ht="168.75" customHeight="1">
+      <c r="A40" s="78" t="s">
         <v>235</v>
       </c>
-      <c r="G37" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="35">
+      <c r="B40" s="78" t="s">
+        <v>241</v>
+      </c>
+      <c r="C40" s="78" t="s">
+        <v>245</v>
+      </c>
+      <c r="D40" s="78" t="s">
+        <v>242</v>
+      </c>
+      <c r="E40" s="77" t="s">
+        <v>243</v>
+      </c>
+      <c r="F40" s="77" t="s">
+        <v>244</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="79">
         <v>46276</v>
       </c>
-      <c r="I37" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="J37" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" s="35">
+      <c r="I40" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J40" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="79">
         <v>46276</v>
       </c>
-      <c r="L37" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="M37" s="37"/>
-    </row>
-    <row r="38" spans="1:14" ht="50.25" customHeight="1">
-      <c r="A38" s="86" t="s">
-        <v>236</v>
-      </c>
-      <c r="B38" s="87"/>
-      <c r="C38" s="87"/>
-      <c r="D38" s="87"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="87"/>
-      <c r="G38" s="87"/>
-      <c r="H38" s="87"/>
-      <c r="I38" s="87"/>
-      <c r="J38" s="87"/>
-      <c r="K38" s="87"/>
-      <c r="L38" s="87"/>
-      <c r="M38" s="88"/>
-      <c r="N38" s="1"/>
-    </row>
-    <row r="39" spans="1:14" ht="193.5" customHeight="1">
-      <c r="A39" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="B39" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="C39" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="D39" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="E39" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="F39" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="G39" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="35">
-        <v>46276</v>
-      </c>
-      <c r="I39" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="J39" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="35">
-        <v>46276</v>
-      </c>
-      <c r="L39" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="M39" s="37"/>
-    </row>
-    <row r="40" spans="1:14" ht="168.75" customHeight="1">
-      <c r="A40" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="B40" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="C40" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="D40" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="E40" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="F40" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="G40" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="35">
-        <v>46276</v>
-      </c>
-      <c r="I40" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="J40" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="35">
-        <v>46276</v>
-      </c>
-      <c r="L40" s="36" t="s">
-        <v>114</v>
+      <c r="L40" s="81" t="s">
+        <v>61</v>
       </c>
       <c r="M40" s="37"/>
     </row>
     <row r="41" spans="1:14" ht="168.75" customHeight="1">
-      <c r="B41" s="39"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="42"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="41"/>
-      <c r="L41" s="42"/>
-      <c r="M41" s="43"/>
+      <c r="B41" s="15"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="19"/>
     </row>
     <row r="42" spans="1:14" ht="171" customHeight="1">
-      <c r="B42" s="40"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="39"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="41"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="43"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -6801,418 +7529,418 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" style="15" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" style="15" customWidth="1"/>
-    <col min="3" max="3" width="19.77734375" style="15" customWidth="1"/>
-    <col min="4" max="4" width="21.21875" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5546875" style="15" customWidth="1"/>
-    <col min="6" max="6" width="28.77734375" style="15" customWidth="1"/>
-    <col min="7" max="7" width="26.21875" style="15" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" style="15" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" style="15" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" style="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.21875" style="15"/>
+    <col min="1" max="1" width="23.7265625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.54296875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="28.7265625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="26.26953125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18.26953125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.7265625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.26953125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="97" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="106" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
+      <c r="B2" s="126" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="4">
         <v>5</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="4">
         <v>0</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="4">
         <v>0</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="4">
         <v>0</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="4">
         <f>B4</f>
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="9">
         <v>5</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="9">
         <v>0</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="9">
         <v>0</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="9">
         <v>0</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="4">
         <f>B5</f>
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="84.75" customHeight="1"/>
     <row r="31" spans="1:13">
-      <c r="A31" s="82" t="s">
+      <c r="A31" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="82" t="s">
+      <c r="B31" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="82" t="s">
+      <c r="C31" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="82" t="s">
+      <c r="D31" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="83" t="s">
+      <c r="E31" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="82" t="s">
+      <c r="F31" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="107" t="s">
+      <c r="G31" s="127" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="107"/>
-      <c r="I31" s="107"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="107"/>
-      <c r="L31" s="107"/>
-      <c r="M31" s="107" t="s">
+      <c r="H31" s="127"/>
+      <c r="I31" s="127"/>
+      <c r="J31" s="127"/>
+      <c r="K31" s="127"/>
+      <c r="L31" s="127"/>
+      <c r="M31" s="127" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="82"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="107" t="s">
+      <c r="A32" s="105"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="107"/>
-      <c r="I32" s="107"/>
-      <c r="J32" s="107" t="s">
+      <c r="H32" s="127"/>
+      <c r="I32" s="127"/>
+      <c r="J32" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="107"/>
-      <c r="L32" s="107"/>
-      <c r="M32" s="108"/>
+      <c r="K32" s="127"/>
+      <c r="L32" s="127"/>
+      <c r="M32" s="128"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="82"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="8" t="s">
+      <c r="A33" s="105"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="K33" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="8" t="s">
+      <c r="L33" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="108"/>
+      <c r="M33" s="128"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="98" t="s">
-        <v>299</v>
-      </c>
-      <c r="B34" s="98"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="98"/>
-      <c r="H34" s="98"/>
-      <c r="I34" s="98"/>
-      <c r="J34" s="98"/>
-      <c r="K34" s="98"/>
-      <c r="L34" s="98"/>
-      <c r="M34" s="98"/>
-    </row>
-    <row r="35" spans="1:14" ht="84">
-      <c r="A35" s="3" t="s">
+      <c r="A34" s="100" t="s">
+        <v>296</v>
+      </c>
+      <c r="B34" s="100"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="100"/>
+      <c r="G34" s="100"/>
+      <c r="H34" s="100"/>
+      <c r="I34" s="100"/>
+      <c r="J34" s="100"/>
+      <c r="K34" s="100"/>
+      <c r="L34" s="100"/>
+      <c r="M34" s="100"/>
+    </row>
+    <row r="35" spans="1:14" ht="77.5">
+      <c r="A35" s="85" t="s">
+        <v>267</v>
+      </c>
+      <c r="B35" s="85" t="s">
+        <v>268</v>
+      </c>
+      <c r="C35" s="86" t="s">
+        <v>271</v>
+      </c>
+      <c r="D35" s="87" t="s">
+        <v>269</v>
+      </c>
+      <c r="E35" s="55" t="s">
         <v>270</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C35" s="13" t="s">
+      <c r="F35" s="55" t="s">
+        <v>272</v>
+      </c>
+      <c r="G35" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="58">
+        <v>46272</v>
+      </c>
+      <c r="I35" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="J35" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="58">
+        <v>46272</v>
+      </c>
+      <c r="L35" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35" s="60"/>
+    </row>
+    <row r="36" spans="1:14" ht="62">
+      <c r="A36" s="85" t="s">
+        <v>273</v>
+      </c>
+      <c r="B36" s="85" t="s">
         <v>274</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="F35" s="4" t="s">
+      <c r="C36" s="87" t="s">
         <v>275</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="6">
+      <c r="D36" s="87" t="s">
+        <v>276</v>
+      </c>
+      <c r="E36" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="F36" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="G36" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="58">
         <v>46272</v>
       </c>
-      <c r="I35" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="6">
+      <c r="I36" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="J36" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="58">
         <v>46272</v>
       </c>
-      <c r="L35" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="M35" s="25"/>
-    </row>
-    <row r="36" spans="1:14" ht="67.2">
-      <c r="A36" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="D36" s="12" t="s">
+      <c r="L36" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="M36" s="60"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="125" t="s">
+        <v>297</v>
+      </c>
+      <c r="B37" s="125"/>
+      <c r="C37" s="125"/>
+      <c r="D37" s="125"/>
+      <c r="E37" s="125"/>
+      <c r="F37" s="125"/>
+      <c r="G37" s="125"/>
+      <c r="H37" s="125"/>
+      <c r="I37" s="125"/>
+      <c r="J37" s="125"/>
+      <c r="K37" s="125"/>
+      <c r="L37" s="125"/>
+      <c r="M37" s="125"/>
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:14" ht="186" customHeight="1">
+      <c r="A38" s="55" t="s">
         <v>279</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="B38" s="55" t="s">
         <v>280</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="C38" s="55" t="s">
         <v>281</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="6">
+      <c r="D38" s="55" t="s">
+        <v>282</v>
+      </c>
+      <c r="E38" s="56" t="s">
+        <v>284</v>
+      </c>
+      <c r="F38" s="56" t="s">
+        <v>283</v>
+      </c>
+      <c r="G38" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="58">
         <v>46272</v>
       </c>
-      <c r="I36" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="6">
+      <c r="I38" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="58">
         <v>46272</v>
       </c>
-      <c r="L36" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M36" s="25"/>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="105" t="s">
-        <v>300</v>
-      </c>
-      <c r="B37" s="105"/>
-      <c r="C37" s="105"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="105"/>
-      <c r="F37" s="105"/>
-      <c r="G37" s="105"/>
-      <c r="H37" s="105"/>
-      <c r="I37" s="105"/>
-      <c r="J37" s="105"/>
-      <c r="K37" s="105"/>
-      <c r="L37" s="105"/>
-      <c r="M37" s="105"/>
-      <c r="N37" s="1"/>
-    </row>
-    <row r="38" spans="1:14" ht="186" customHeight="1">
-      <c r="A38" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="D38" s="4" t="s">
+      <c r="L38" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="M38" s="60"/>
+    </row>
+    <row r="39" spans="1:14" ht="134.25" customHeight="1">
+      <c r="A39" s="55" t="s">
         <v>285</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="B39" s="55" t="s">
+        <v>286</v>
+      </c>
+      <c r="C39" s="55" t="s">
+        <v>356</v>
+      </c>
+      <c r="D39" s="55" t="s">
         <v>287</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="6">
+      <c r="E39" s="56" t="s">
+        <v>288</v>
+      </c>
+      <c r="F39" s="56" t="s">
+        <v>289</v>
+      </c>
+      <c r="G39" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="58">
         <v>46272</v>
       </c>
-      <c r="I38" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="6">
+      <c r="I39" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="J39" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="58">
         <v>46272</v>
       </c>
-      <c r="L38" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="M38" s="25"/>
-    </row>
-    <row r="39" spans="1:14" ht="134.25" customHeight="1">
-      <c r="A39" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="L39" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="M39" s="60"/>
+    </row>
+    <row r="40" spans="1:14" ht="156" customHeight="1">
+      <c r="A40" s="55" t="s">
         <v>290</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="B40" s="55" t="s">
         <v>291</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="C40" s="55" t="s">
         <v>292</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="6">
+      <c r="D40" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="E40" s="56" t="s">
+        <v>294</v>
+      </c>
+      <c r="F40" s="56" t="s">
+        <v>295</v>
+      </c>
+      <c r="G40" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="58">
         <v>46272</v>
       </c>
-      <c r="I39" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="6">
+      <c r="I40" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="J40" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="58">
         <v>46272</v>
       </c>
-      <c r="L39" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M39" s="25"/>
-    </row>
-    <row r="40" spans="1:14" ht="156" customHeight="1">
-      <c r="A40" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="6">
-        <v>46272</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="6">
-        <v>46272</v>
-      </c>
-      <c r="L40" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M40" s="25"/>
+      <c r="L40" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="M40" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="14">
